--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -49460,10 +49460,10 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.779584166723938</v>
+        <v>-4.779483801813694</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.590547068251845</v>
+        <v>2.590587214215943</v>
       </c>
       <c r="F2083" t="n">
         <v>1.00143798535321</v>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>421.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.5%</t>
+          <t>-641.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.2%</t>
+          <t>-117.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.9%</t>
+          <t>-319.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-123.8%</t>
+          <t>-132.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.72429435884665</v>
+        <v>-2.74995449124401</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.2866221028787</v>
+        <v>2.276358049919756</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.274523671818466</v>
+        <v>1.185468895897491</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.141410473822187</v>
+        <v>4.087977608269602</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.813170990015124</v>
+        <v>-2.838831122412484</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.253962544956611</v>
+        <v>2.243698491997668</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.185647040649992</v>
+        <v>1.096592264729017</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.090975589666404</v>
+        <v>4.037542724113819</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.889500967616029</v>
+        <v>-2.915161100013389</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.221542366810024</v>
+        <v>2.21127831385108</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.185647040649992</v>
+        <v>1.096592264729017</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.089087402560179</v>
+        <v>4.035654537007594</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.983164912293571</v>
+        <v>-3.008825044690931</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.17889701854187</v>
+        <v>2.168632965582926</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.091983095972451</v>
+        <v>1.002928320051476</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.027709265356516</v>
+        <v>3.974276399803931</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.144733337820826</v>
+        <v>-3.170393470218186</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.11270365854112</v>
+        <v>2.102439605582176</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9652001721745714</v>
+        <v>0.8761453962535964</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.950073521287941</v>
+        <v>3.896640655735356</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.253033999690945</v>
+        <v>-3.278694132088305</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.082456800658991</v>
+        <v>2.072192747700047</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9652001721745714</v>
+        <v>0.8761453962535964</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.96314692815386</v>
+        <v>3.909714062601275</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.27083797141169</v>
+        <v>-3.29649810380905</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.067340408753633</v>
+        <v>2.057076355794689</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8946655492693703</v>
+        <v>0.8056107733483953</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.912831351193679</v>
+        <v>3.859398485641094</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.298738758521162</v>
+        <v>-3.324398890918522</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.054704135036846</v>
+        <v>2.044440082077903</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8600686251264354</v>
+        <v>0.7710138492054605</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.89059723783492</v>
+        <v>3.837164372282335</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.421264861224056</v>
+        <v>-3.446924993621416</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.002458137932887</v>
+        <v>1.992194084973943</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7375425224235416</v>
+        <v>0.6484877465025666</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.813846020190383</v>
+        <v>3.760413154637797</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.651779357409645</v>
+        <v>-3.677439489807005</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.976958299049156</v>
+        <v>1.966694246090212</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5070280262379528</v>
+        <v>0.4179732503169779</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.742243282069533</v>
+        <v>3.688810416516948</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.000524442634089</v>
+        <v>-4.026184575031449</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.977771983961225</v>
+        <v>1.967507931002281</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.398280072319055</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.817306228720041</v>
+        <v>3.763873363167456</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.154510860410229</v>
+        <v>-4.180170992807589</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.985157685996409</v>
+        <v>1.974893633037465</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.398280072319055</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.886286497865681</v>
+        <v>3.832853632313096</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.103988956582564</v>
+        <v>-4.129649088979924</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.991417649647596</v>
+        <v>1.981153596688652</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.398280072319055</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.872337699985802</v>
+        <v>3.818904834433217</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.356464110590288</v>
+        <v>-4.382124242987648</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.90229807709992</v>
+        <v>1.892034024140976</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.398280072319055</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.884208189041216</v>
+        <v>3.830775323488631</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.6493598670697</v>
+        <v>-4.67501999946706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.786350309027099</v>
+        <v>1.776086256068155</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.398280072319055</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.88541872356016</v>
+        <v>3.831985858007575</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.836023995204508</v>
+        <v>-4.861684127601868</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715806400000497</v>
+        <v>1.705542347041553</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3715411014944952</v>
+        <v>0.2824863255735202</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.873497083292745</v>
+        <v>3.82006421774016</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.98204468211847</v>
+        <v>-5.00770481451583</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.652475977971102</v>
+        <v>1.642211925012158</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3624580097006382</v>
+        <v>0.2734032337796632</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.86312508095262</v>
+        <v>3.809692215400036</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.073758691228056</v>
+        <v>-5.099418823625415</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777994431026312</v>
+        <v>1.767730378067368</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3624580097006382</v>
+        <v>0.2734032337796632</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.025329137651664</v>
+        <v>3.971896272099079</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.105410350288025</v>
+        <v>-5.131070482685384</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.760180405366138</v>
+        <v>1.749916352407194</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.357289552456198</v>
+        <v>0.268234776535223</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.017074701268815</v>
+        <v>3.96364183571623</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.187345168556909</v>
+        <v>-5.213005300954268</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737635895627076</v>
+        <v>1.727371842668132</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3473548068691178</v>
+        <v>0.2583000309481428</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.021343271485057</v>
+        <v>3.967910405932472</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.289321290805316</v>
+        <v>-5.314981423202675</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.705771085183616</v>
+        <v>1.695507032224672</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2453786846207102</v>
+        <v>0.1563239086997352</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.969083236591915</v>
+        <v>3.91565037103933</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.179315007328094</v>
+        <v>-5.204975139725454</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741926485818679</v>
+        <v>1.731662432859736</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2685832565379854</v>
+        <v>0.1795284806170104</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.975158866986456</v>
+        <v>3.921726001433871</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.036255431587168</v>
+        <v>-5.061915563984527</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.803400326837024</v>
+        <v>1.793136273878081</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2765966831279647</v>
+        <v>0.1875419072069897</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.984216933662418</v>
+        <v>3.930784068109832</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.734808706115331</v>
+        <v>-4.76046883851269</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.931239899908295</v>
+        <v>1.920975846949352</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.578043408599802</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.172345851828056</v>
+        <v>4.118912986275471</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.759398950350515</v>
+        <v>-4.785059082747874</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.922374979966932</v>
+        <v>1.912110927007989</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.578043408599802</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.173317029580767</v>
+        <v>4.119884164028182</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.708360574343994</v>
+        <v>-4.734020706741354</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.943633234749296</v>
+        <v>1.933369181790352</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.578043408599802</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.174159933960523</v>
+        <v>4.120727068407938</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.667221279477364</v>
+        <v>-4.692881411874723</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.979127051570094</v>
+        <v>1.96886299861115</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6191827034664328</v>
+        <v>0.5301279275454578</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.217881609754646</v>
+        <v>4.164448744202061</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.570586367458723</v>
+        <v>-4.596246499856083</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833965012501484</v>
+        <v>1.823700959542541</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7158176154850727</v>
+        <v>0.6267628395640977</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.092046553089765</v>
+        <v>4.03861368753718</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.701167101989566</v>
+        <v>-4.726827234386925</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.785234762763111</v>
+        <v>1.774970709804168</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5852368809542302</v>
+        <v>0.4961821050332552</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.017200156445224</v>
+        <v>3.963767290892639</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.536670767798604</v>
+        <v>-4.562330900195963</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.835460115515579</v>
+        <v>1.825196062556635</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7497332151451921</v>
+        <v>0.6606784392242171</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.100324776035883</v>
+        <v>4.046891910483298</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.459572166256732</v>
+        <v>-4.485232298654091</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.865487266568757</v>
+        <v>1.855223213609814</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7497332151451921</v>
+        <v>0.6606784392242171</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.099512486472313</v>
+        <v>4.046079620919728</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.469957361146621</v>
+        <v>-4.49561749354398</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.871201967737874</v>
+        <v>1.86093791477893</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7393480202553028</v>
+        <v>0.6502932443343278</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.103150148663452</v>
+        <v>4.049717283110867</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.488545519868846</v>
+        <v>-4.514205652266205</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.934603710025409</v>
+        <v>1.924339657066466</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7207598615330775</v>
+        <v>0.6317050856121025</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.162834259206542</v>
+        <v>4.109401393653957</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.488844066564882</v>
+        <v>-4.514504198962241</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.931353302165293</v>
+        <v>1.92108924920635</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7204613148370416</v>
+        <v>0.6314065389160666</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.159524142007219</v>
+        <v>4.106091276454634</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.388020932874454</v>
+        <v>-4.413681065271813</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.976213450580856</v>
+        <v>1.965949397621912</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7329255303213954</v>
+        <v>0.6438707544004204</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.171533566237223</v>
+        <v>4.118100700684638</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.197239572122047</v>
+        <v>-4.222899704519406</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.052655248360362</v>
+        <v>2.042391195401418</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9237068910738028</v>
+        <v>0.8346521151528278</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.28613163616721</v>
+        <v>4.232698770614626</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.090276214272626</v>
+        <v>-4.115936346669985</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.075277437237727</v>
+        <v>2.065013384278783</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9821714990336042</v>
+        <v>0.8931167231126292</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.301047246680687</v>
+        <v>4.247614381128103</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.034945626370863</v>
+        <v>-4.060605758768222</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.132376609010491</v>
+        <v>2.122112556051547</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.037502086935366</v>
+        <v>0.9484473110143914</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.369212536033803</v>
+        <v>4.315779670481218</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.0228914994579</v>
+        <v>-4.048551631855259</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.130884827677114</v>
+        <v>2.12062077471817</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.049556213848329</v>
+        <v>0.9605014379273542</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.370131580083019</v>
+        <v>4.316698714530434</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.064046619026121</v>
+        <v>-4.08970675142348</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.116303410033961</v>
+        <v>2.106039357075018</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.008401094280108</v>
+        <v>0.9193463183591333</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.347319138526222</v>
+        <v>4.293886272973637</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.995998056334591</v>
+        <v>-4.02165818873195</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.156373860988455</v>
+        <v>2.146109808029512</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.076449656971638</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.400999302019022</v>
+        <v>4.347566436466437</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.227598449504092</v>
+        <v>-4.253258581901451</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.083936373894249</v>
+        <v>2.073672320935306</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.076449656971638</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.421201972192616</v>
+        <v>4.367769106640031</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498973</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.277649995033311</v>
+        <v>-4.30331012743067</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.047521991749444</v>
+        <v>2.0372579387905</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.076449656971638</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.404808208259499</v>
+        <v>4.351375342706914</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800102</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.452756827609756</v>
+        <v>-4.478416960007115</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.937731172312333</v>
+        <v>1.927467119353389</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.076449656971638</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.365060121852965</v>
+        <v>4.31162725630038</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660855</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.256656674179233</v>
+        <v>-4.282316806576592</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.023193852681482</v>
+        <v>2.012929799722538</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.272549810402161</v>
+        <v>1.183495034481186</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.489742832908219</v>
+        <v>4.436309967355634</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395091</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.103631282065948</v>
+        <v>-4.129291414463307</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.1835750090997</v>
+        <v>2.173310956140756</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.425575202515445</v>
+        <v>1.33652042659447</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.680729067749094</v>
+        <v>4.627296202196509</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.131938595939219</v>
+        <v>-4.157598728336578</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.359718308458684</v>
+        <v>2.349454255499741</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.425575202515445</v>
+        <v>1.33652042659447</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.868195292657386</v>
+        <v>4.814762427104801</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.298531821052741</v>
+        <v>-4.3241919534501</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.262483969767358</v>
+        <v>2.252219916808414</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.258981977401923</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.737642308943355</v>
+        <v>4.68420944339077</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.275496027691175</v>
+        <v>-4.301156160088534</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.275374689773701</v>
+        <v>2.265110636814758</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.258981977401923</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.741318711605073</v>
+        <v>4.687885846052488</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.246250047235478</v>
+        <v>-4.271910179632838</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.284691137079475</v>
+        <v>2.274427084120532</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.258981977401923</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.738936766728568</v>
+        <v>4.685503901175983</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.35317559511333</v>
+        <v>-4.378835727510689</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.23921415708597</v>
+        <v>2.228950104127026</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.152056429524071</v>
+        <v>1.063001653603096</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.672074677159492</v>
+        <v>4.618641811606907</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.498194153620578</v>
+        <v>-4.523854286017937</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.182635535826305</v>
+        <v>2.172371482867361</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.007037871016823</v>
+        <v>0.9179830950958479</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.586492344198377</v>
+        <v>4.533059478645793</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.616535919405296</v>
+        <v>-4.642196051802655</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.235230068770171</v>
+        <v>2.224966015811227</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.017723909579713</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.692835206593864</v>
+        <v>4.639402341041279</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.667946341726004</v>
+        <v>-4.693606474123363</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.212451596967826</v>
+        <v>2.202187544008883</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.017723909579713</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.690620903719803</v>
+        <v>4.637188038167218</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.747365792933755</v>
+        <v>-4.773025925331114</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.180586944559015</v>
+        <v>2.170322891600072</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.017723909579713</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.690524031794093</v>
+        <v>4.637091166241508</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.842828790850973</v>
+        <v>-4.868488923248332</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.142395638950171</v>
+        <v>2.132131585991228</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.017723909579713</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.690517925352136</v>
+        <v>4.637085059799551</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.778452880000258</v>
+        <v>-4.804113012397617</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.166242399853068</v>
+        <v>2.155978346894125</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.082099820430428</v>
+        <v>0.993045044509453</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.727239868425176</v>
+        <v>4.673807002872591</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.833822042132452</v>
+        <v>-4.859482174529811</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.149828552747918</v>
+        <v>2.139564499788974</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.082099820430428</v>
+        <v>0.993045044509453</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.732973686172903</v>
+        <v>4.679540820620318</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.879259821963279</v>
+        <v>-4.904919954360638</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.131191804158519</v>
+        <v>2.120927751199575</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.039254829752269</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.706805055108939</v>
+        <v>4.653372189556354</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.791052987815701</v>
+        <v>-4.81671312021306</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.186348930667869</v>
+        <v>2.176084877708925</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.039254829752269</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.726679447959258</v>
+        <v>4.673246582406673</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.685017992610391</v>
+        <v>-4.710678125007751</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.212463629274721</v>
+        <v>2.202199576315777</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.039254829752269</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.710380148483986</v>
+        <v>4.656947282931401</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307674</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.501806329477296</v>
+        <v>-4.527466461874655</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.288179243992004</v>
+        <v>2.277915191033061</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.039254829752269</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.712811097948031</v>
+        <v>4.659378232395446</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.430084882463445</v>
+        <v>-4.455745014860804</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.282659008645434</v>
+        <v>2.27239495568649</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.110976276766119</v>
+        <v>1.021921500845144</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.721635152004231</v>
+        <v>4.668202286451645</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394115</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.407711856855739</v>
+        <v>-4.433371989253098</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.238523964809688</v>
+        <v>2.228259911850745</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.122232027879021</v>
+        <v>1.033177251958045</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.675304348593143</v>
+        <v>4.621871483040558</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.440728152766484</v>
+        <v>-4.466388285163843</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.410515651330746</v>
+        <v>2.400251598371802</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.052794651212269</v>
+        <v>0.9637398752912938</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.818840127478448</v>
+        <v>4.765407261925863</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.429200517116875</v>
+        <v>-4.454860649514234</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.407047931418838</v>
+        <v>2.396783878459894</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.111795309413632</v>
+        <v>1.022740533492656</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.846161748227515</v>
+        <v>4.79272888267493</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.526542018459244</v>
+        <v>-4.552202150856603</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.371779443403679</v>
+        <v>2.361515390444736</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.067375127248143</v>
+        <v>0.9783203513271679</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.82317775145001</v>
+        <v>4.769744885897425</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427685</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.612398047799211</v>
+        <v>-4.63805818019657</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.338688113860531</v>
+        <v>2.328424060901587</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.024999058022008</v>
+        <v>0.9359442821010329</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.799003192107167</v>
+        <v>4.745570326554582</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.62123484521533</v>
+        <v>-4.646894977612689</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.317572596714585</v>
+        <v>2.307308543755641</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.017556885380658</v>
+        <v>0.9285021094596821</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.776957090342859</v>
+        <v>4.723524224790274</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.712617407780789</v>
+        <v>-4.738277540178148</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.291184082733451</v>
+        <v>2.280920029774507</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9261743228151993</v>
+        <v>0.8371195468942239</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.732292063848633</v>
+        <v>4.678859198296048</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.700910689793782</v>
+        <v>-4.726570822191142</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.397995027752521</v>
+        <v>2.387730974793578</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9378810408022057</v>
+        <v>0.8488262648812303</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.841444352465105</v>
+        <v>4.78801148691252</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.60124718571012</v>
+        <v>-4.626907318107479</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.440892768117391</v>
+        <v>2.430628715158448</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.001068124005892</v>
+        <v>0.9120133480849167</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.882388941118722</v>
+        <v>4.828956075566137</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.611563283876472</v>
+        <v>-4.637223416273831</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.649671162128909</v>
+        <v>2.639407109169965</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.001068124005892</v>
+        <v>0.9120133480849167</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.09529377439678</v>
+        <v>5.041860908844195</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.611469315859099</v>
+        <v>-4.637129448256458</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.648887416247947</v>
+        <v>2.638623363289004</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.00143798535321</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.094694358117261</v>
+        <v>5.041261492564676</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.618688140058944</v>
+        <v>-4.644348272456303</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.640231872512364</v>
+        <v>2.62996781955342</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.00143798535321</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.088926344061615</v>
+        <v>5.03549347850903</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740924</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.617739716940905</v>
+        <v>-4.643399849338264</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.640611241759579</v>
+        <v>2.630347188800635</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.00143798535321</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.088926344061615</v>
+        <v>5.03549347850903</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.774808175196529</v>
+        <v>-4.800468307593889</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.590511466438421</v>
+        <v>2.580247413479477</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.00143798535321</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.101653952042707</v>
+        <v>5.048221086490122</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.821568277625375</v>
+        <v>3.567501766537622</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.779483801813694</v>
+        <v>-4.794476060805077</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.590587214215943</v>
+        <v>2.58459031061939</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.00143798535321</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.103599950467094</v>
+        <v>5.050167084914509</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>138.6%</t>
+          <t>139.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.3%</t>
+          <t>421.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.0%</t>
+          <t>-638.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.8%</t>
+          <t>-116.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.6%</t>
+          <t>-319.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-132.8%</t>
+          <t>-131.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2083"/>
+  <dimension ref="A1:G2084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.74995449124401</v>
+        <v>-2.730593902569135</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.276358049919756</v>
+        <v>2.284102285389706</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.185468895897491</v>
+        <v>1.195230628398241</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.087977608269602</v>
+        <v>4.093834647770052</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.838831122412484</v>
+        <v>-2.819470533737609</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.243698491997668</v>
+        <v>2.251442727467617</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.096592264729017</v>
+        <v>1.106353997229767</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.037542724113819</v>
+        <v>4.043399763614269</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.915161100013389</v>
+        <v>-2.895800511338515</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.21127831385108</v>
+        <v>2.21902254932103</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.096592264729017</v>
+        <v>1.106353997229767</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.035654537007594</v>
+        <v>4.041511576508044</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.008825044690931</v>
+        <v>-2.989464456016056</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.168632965582926</v>
+        <v>2.176377201052876</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.002928320051476</v>
+        <v>1.012690052552226</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.974276399803931</v>
+        <v>3.980133439304382</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.170393470218186</v>
+        <v>-3.151032881543312</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.102439605582176</v>
+        <v>2.110183841052126</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8761453962535964</v>
+        <v>0.8859071287543464</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.896640655735356</v>
+        <v>3.902497695235806</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.278694132088305</v>
+        <v>-3.259333543413431</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.072192747700047</v>
+        <v>2.079936983169997</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8761453962535964</v>
+        <v>0.8859071287543464</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.909714062601275</v>
+        <v>3.915571102101724</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.29649810380905</v>
+        <v>-3.277137515134175</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.057076355794689</v>
+        <v>2.064820591264639</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8056107733483953</v>
+        <v>0.8153725058491452</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.859398485641094</v>
+        <v>3.865255525141544</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.324398890918522</v>
+        <v>-3.305038302243648</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.044440082077903</v>
+        <v>2.052184317547852</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7710138492054605</v>
+        <v>0.7807755817062104</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.837164372282335</v>
+        <v>3.843021411782785</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.446924993621416</v>
+        <v>-3.427564404946542</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.992194084973943</v>
+        <v>1.999938320443893</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6484877465025666</v>
+        <v>0.6582494790033165</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.760413154637797</v>
+        <v>3.766270194138247</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.677439489807005</v>
+        <v>-3.65807890113213</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.966694246090212</v>
+        <v>1.974438481560162</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4179732503169779</v>
+        <v>0.4277349828177278</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.688810416516948</v>
+        <v>3.694667456017398</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.026184575031449</v>
+        <v>-4.006823986356574</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.967507931002281</v>
+        <v>1.975252166472231</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.31898702889883</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.763873363167456</v>
+        <v>3.769730402667906</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.180170992807589</v>
+        <v>-4.160810404132715</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.974893633037465</v>
+        <v>1.982637868507415</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.31898702889883</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.832853632313096</v>
+        <v>3.838710671813546</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.129649088979924</v>
+        <v>-4.110288500305049</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.981153596688652</v>
+        <v>1.988897832158602</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.31898702889883</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.818904834433217</v>
+        <v>3.824761873933667</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.382124242987648</v>
+        <v>-4.362763654312773</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.892034024140976</v>
+        <v>1.899778259610926</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.31898702889883</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.830775323488631</v>
+        <v>3.836632362989081</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.67501999946706</v>
+        <v>-4.655659410792185</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.776086256068155</v>
+        <v>1.783830491538105</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.31898702889883</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.831985858007575</v>
+        <v>3.837842897508025</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.861684127601868</v>
+        <v>-4.842323538926993</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.705542347041553</v>
+        <v>1.713286582511503</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2824863255735202</v>
+        <v>0.2922480580742701</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.82006421774016</v>
+        <v>3.82592125724061</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.00770481451583</v>
+        <v>-4.988344225840955</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.642211925012158</v>
+        <v>1.649956160482108</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2734032337796632</v>
+        <v>0.2831649662804132</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.809692215400036</v>
+        <v>3.815549254900485</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.099418823625415</v>
+        <v>-5.08005823495054</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767730378067368</v>
+        <v>1.775474613537318</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2734032337796632</v>
+        <v>0.2831649662804132</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.971896272099079</v>
+        <v>3.977753311599529</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.131070482685384</v>
+        <v>-5.111709894010509</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.749916352407194</v>
+        <v>1.757660587877144</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.268234776535223</v>
+        <v>0.2779965090359729</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.96364183571623</v>
+        <v>3.969498875216679</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.213005300954268</v>
+        <v>-5.193644712279393</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.727371842668132</v>
+        <v>1.735116078138082</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2583000309481428</v>
+        <v>0.2680617634488928</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.967910405932472</v>
+        <v>3.973767445432923</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.314981423202675</v>
+        <v>-5.2956208345278</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.695507032224672</v>
+        <v>1.703251267694622</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1563239086997352</v>
+        <v>0.1660856412004852</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.91565037103933</v>
+        <v>3.921507410539781</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.204975139725454</v>
+        <v>-5.185614551050579</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.731662432859736</v>
+        <v>1.739406668329686</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1795284806170104</v>
+        <v>0.1892902131177604</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.921726001433871</v>
+        <v>3.927583040934321</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.061915563984527</v>
+        <v>-5.042554975309653</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.793136273878081</v>
+        <v>1.800880509348031</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1875419072069897</v>
+        <v>0.1973036397077397</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.930784068109832</v>
+        <v>3.936641107610283</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.76046883851269</v>
+        <v>-4.741108249837815</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.920975846949352</v>
+        <v>1.928720082419302</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.488988632678827</v>
+        <v>0.4987503651795769</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.118912986275471</v>
+        <v>4.124770025775922</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.785059082747874</v>
+        <v>-4.765698494072999</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.912110927007989</v>
+        <v>1.919855162477939</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.488988632678827</v>
+        <v>0.4987503651795769</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.119884164028182</v>
+        <v>4.125741203528632</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.734020706741354</v>
+        <v>-4.714660118066479</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.933369181790352</v>
+        <v>1.941113417260302</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.488988632678827</v>
+        <v>0.4987503651795769</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.120727068407938</v>
+        <v>4.126584107908387</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.692881411874723</v>
+        <v>-4.673520823199848</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.96886299861115</v>
+        <v>1.9766072340811</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5301279275454578</v>
+        <v>0.5398896600462078</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.164448744202061</v>
+        <v>4.170305783702512</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.596246499856083</v>
+        <v>-4.576885911181208</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.823700959542541</v>
+        <v>1.831445195012491</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6267628395640977</v>
+        <v>0.6365245720648477</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.03861368753718</v>
+        <v>4.04447072703763</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.726827234386925</v>
+        <v>-4.70746664571205</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.774970709804168</v>
+        <v>1.782714945274118</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4961821050332552</v>
+        <v>0.5059438375340052</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.963767290892639</v>
+        <v>3.969624330393088</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.562330900195963</v>
+        <v>-4.542970311521088</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.825196062556635</v>
+        <v>1.832940298026585</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6606784392242171</v>
+        <v>0.6704401717249671</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.046891910483298</v>
+        <v>4.052748949983748</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.485232298654091</v>
+        <v>-4.465871709979216</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.855223213609814</v>
+        <v>1.862967449079764</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6606784392242171</v>
+        <v>0.6704401717249671</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.046079620919728</v>
+        <v>4.051936660420178</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.49561749354398</v>
+        <v>-4.476256904869105</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.86093791477893</v>
+        <v>1.86868215024888</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6502932443343278</v>
+        <v>0.6600549768350777</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.049717283110867</v>
+        <v>4.055574322611316</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.514205652266205</v>
+        <v>-4.49484506359133</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.924339657066466</v>
+        <v>1.932083892536416</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6317050856121025</v>
+        <v>0.6414668181128524</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.109401393653957</v>
+        <v>4.115258433154406</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.514504198962241</v>
+        <v>-4.495143610287366</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.92108924920635</v>
+        <v>1.9288334846763</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6314065389160666</v>
+        <v>0.6411682714168165</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.106091276454634</v>
+        <v>4.111948315955083</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.413681065271813</v>
+        <v>-4.394320476596938</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.965949397621912</v>
+        <v>1.973693633091862</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6438707544004204</v>
+        <v>0.6536324869011704</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.118100700684638</v>
+        <v>4.123957740185087</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.222899704519406</v>
+        <v>-4.203539115844531</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.042391195401418</v>
+        <v>2.050135430871368</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8346521151528278</v>
+        <v>0.8444138476535777</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.232698770614626</v>
+        <v>4.238555810115075</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.115936346669985</v>
+        <v>-4.09657575799511</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.065013384278783</v>
+        <v>2.072757619748733</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8931167231126292</v>
+        <v>0.9028784556133792</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.247614381128103</v>
+        <v>4.253471420628553</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.060605758768222</v>
+        <v>-4.041245170093347</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.122112556051547</v>
+        <v>2.129856791521497</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9484473110143914</v>
+        <v>0.9582090435151414</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.315779670481218</v>
+        <v>4.321636709981668</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.048551631855259</v>
+        <v>-4.029191043180385</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.12062077471817</v>
+        <v>2.12836501018812</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9605014379273542</v>
+        <v>0.9702631704281042</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.316698714530434</v>
+        <v>4.322555754030883</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.08970675142348</v>
+        <v>-4.070346162748606</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.106039357075018</v>
+        <v>2.113783592544968</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9193463183591333</v>
+        <v>0.9291080508598832</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.293886272973637</v>
+        <v>4.299743312474087</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.02165818873195</v>
+        <v>-4.002297600057076</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.146109808029512</v>
+        <v>2.153854043499462</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9873948810506631</v>
+        <v>0.9971566135514132</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.347566436466437</v>
+        <v>4.353423475966888</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.253258581901451</v>
+        <v>-4.233897993226576</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.073672320935306</v>
+        <v>2.081416556405256</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9873948810506631</v>
+        <v>0.9971566135514132</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.367769106640031</v>
+        <v>4.373626146140482</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498973</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.30331012743067</v>
+        <v>-4.283949538755795</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.0372579387905</v>
+        <v>2.04500217426045</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9873948810506631</v>
+        <v>0.9971566135514132</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.351375342706914</v>
+        <v>4.357232382207363</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800102</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.478416960007115</v>
+        <v>-4.45905637133224</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.927467119353389</v>
+        <v>1.935211354823339</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9873948810506631</v>
+        <v>0.9971566135514132</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.31162725630038</v>
+        <v>4.31748429580083</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660855</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.282316806576592</v>
+        <v>-4.262956217901717</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.012929799722538</v>
+        <v>2.020674035192488</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.183495034481186</v>
+        <v>1.193256766981936</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.436309967355634</v>
+        <v>4.442167006856084</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395091</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.129291414463307</v>
+        <v>-4.109930825788433</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.173310956140756</v>
+        <v>2.181055191610706</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.33652042659447</v>
+        <v>1.34628215909522</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.627296202196509</v>
+        <v>4.633153241696959</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.157598728336578</v>
+        <v>-4.138238139661703</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.349454255499741</v>
+        <v>2.357198490969691</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.33652042659447</v>
+        <v>1.34628215909522</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.814762427104801</v>
+        <v>4.820619466605251</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.3241919534501</v>
+        <v>-4.304831364775225</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.252219916808414</v>
+        <v>2.259964152278364</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.169927201480948</v>
+        <v>1.179688933981698</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.68420944339077</v>
+        <v>4.69006648289122</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.301156160088534</v>
+        <v>-4.281795571413659</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.265110636814758</v>
+        <v>2.272854872284708</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.169927201480948</v>
+        <v>1.179688933981698</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.687885846052488</v>
+        <v>4.693742885552938</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.271910179632838</v>
+        <v>-4.252549590957963</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.274427084120532</v>
+        <v>2.282171319590482</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.169927201480948</v>
+        <v>1.179688933981698</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.685503901175983</v>
+        <v>4.691360940676433</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.378835727510689</v>
+        <v>-4.359475138835814</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.228950104127026</v>
+        <v>2.236694339596976</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.063001653603096</v>
+        <v>1.072763386103846</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.618641811606907</v>
+        <v>4.624498851107357</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.523854286017937</v>
+        <v>-4.504493697343062</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.172371482867361</v>
+        <v>2.180115718337311</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9179830950958479</v>
+        <v>0.9277448275965978</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.533059478645793</v>
+        <v>4.538916518146243</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.642196051802655</v>
+        <v>-4.62283546312778</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.224966015811227</v>
+        <v>2.232710251281177</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9286691336587379</v>
+        <v>0.9384308661594879</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.639402341041279</v>
+        <v>4.645259380541729</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.693606474123363</v>
+        <v>-4.674245885448488</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.202187544008883</v>
+        <v>2.209931779478833</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9286691336587379</v>
+        <v>0.9384308661594879</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.637188038167218</v>
+        <v>4.643045077667669</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.773025925331114</v>
+        <v>-4.75366533665624</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.170322891600072</v>
+        <v>2.178067127070022</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9286691336587379</v>
+        <v>0.9384308661594879</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.637091166241508</v>
+        <v>4.642948205741957</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.868488923248332</v>
+        <v>-4.849128334573457</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.132131585991228</v>
+        <v>2.139875821461178</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9286691336587379</v>
+        <v>0.9384308661594879</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.637085059799551</v>
+        <v>4.642942099300001</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.804113012397617</v>
+        <v>-4.784752423722742</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.155978346894125</v>
+        <v>2.163722582364075</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.993045044509453</v>
+        <v>1.002806777010203</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.673807002872591</v>
+        <v>4.679664042373041</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353537</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.859482174529811</v>
+        <v>-4.840121585854936</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.139564499788974</v>
+        <v>2.147308735258924</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.993045044509453</v>
+        <v>1.002806777010203</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.679540820620318</v>
+        <v>4.685397860120768</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011328</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.904919954360638</v>
+        <v>-4.885559365685763</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.120927751199575</v>
+        <v>2.128671986669525</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9502000538312934</v>
+        <v>0.9599617863320433</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.653372189556354</v>
+        <v>4.659229229056804</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113689</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.81671312021306</v>
+        <v>-4.797352531538185</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.176084877708925</v>
+        <v>2.183829113178875</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9502000538312934</v>
+        <v>0.9599617863320433</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.673246582406673</v>
+        <v>4.679103621907123</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.710678125007751</v>
+        <v>-4.691317536332876</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.202199576315777</v>
+        <v>2.209943811785727</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9502000538312934</v>
+        <v>0.9599617863320433</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.656947282931401</v>
+        <v>4.662804322431851</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307674</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.527466461874655</v>
+        <v>-4.508105873199781</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.277915191033061</v>
+        <v>2.285659426503011</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9502000538312934</v>
+        <v>0.9599617863320433</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.659378232395446</v>
+        <v>4.665235271895896</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.455745014860804</v>
+        <v>-4.43638442618593</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.27239495568649</v>
+        <v>2.28013919115644</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.021921500845144</v>
+        <v>1.031683233345894</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.668202286451645</v>
+        <v>4.674059325952096</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394115</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.433371989253098</v>
+        <v>-4.414011400578223</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.228259911850745</v>
+        <v>2.236004147320695</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.033177251958045</v>
+        <v>1.042938984458795</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.621871483040558</v>
+        <v>4.627728522541008</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.466388285163843</v>
+        <v>-4.447027696488968</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.400251598371802</v>
+        <v>2.407995833841752</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9637398752912938</v>
+        <v>0.9735016077920438</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.765407261925863</v>
+        <v>4.771264301426313</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.454860649514234</v>
+        <v>-4.43550006083936</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.396783878459894</v>
+        <v>2.404528113929844</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.022740533492656</v>
+        <v>1.032502265993406</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.79272888267493</v>
+        <v>4.79858592217538</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.552202150856603</v>
+        <v>-4.532841562181728</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.361515390444736</v>
+        <v>2.369259625914686</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9783203513271679</v>
+        <v>0.9880820838279178</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.769744885897425</v>
+        <v>4.775601925397875</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427685</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.63805818019657</v>
+        <v>-4.618697591521695</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.328424060901587</v>
+        <v>2.336168296371537</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9359442821010329</v>
+        <v>0.9457060146017828</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.745570326554582</v>
+        <v>4.751427366055032</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.646894977612689</v>
+        <v>-4.627534388937814</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.307308543755641</v>
+        <v>2.315052779225591</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9285021094596821</v>
+        <v>0.9382638419604321</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.723524224790274</v>
+        <v>4.729381264290724</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.738277540178148</v>
+        <v>-4.718916951503273</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.280920029774507</v>
+        <v>2.288664265244457</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8371195468942239</v>
+        <v>0.8468812793949738</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.678859198296048</v>
+        <v>4.684716237796498</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.726570822191142</v>
+        <v>-4.707210233516267</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.387730974793578</v>
+        <v>2.395475210263528</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8488262648812303</v>
+        <v>0.8585879973819802</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.78801148691252</v>
+        <v>4.79386852641297</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.626907318107479</v>
+        <v>-4.607546729432604</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.430628715158448</v>
+        <v>2.438372950628398</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9120133480849167</v>
+        <v>0.9217750805856667</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.828956075566137</v>
+        <v>4.834813115066587</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.637223416273831</v>
+        <v>-4.617862827598956</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.639407109169965</v>
+        <v>2.647151344639915</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9120133480849167</v>
+        <v>0.9217750805856667</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.041860908844195</v>
+        <v>5.047717948344645</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.637129448256458</v>
+        <v>-4.617768859581584</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.638623363289004</v>
+        <v>2.646367598758954</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9123832094322347</v>
+        <v>0.9221449419329847</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.041261492564676</v>
+        <v>5.047118532065126</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.644348272456303</v>
+        <v>-4.624987683781428</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.62996781955342</v>
+        <v>2.637712055023369</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9123832094322347</v>
+        <v>0.9221449419329847</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.03549347850903</v>
+        <v>5.041350518009479</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740924</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.643399849338264</v>
+        <v>-4.624039260663389</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.630347188800635</v>
+        <v>2.638091424270585</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9123832094322347</v>
+        <v>0.9221449419329847</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.03549347850903</v>
+        <v>5.041350518009479</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.800468307593889</v>
+        <v>-4.781107718919014</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.580247413479477</v>
+        <v>2.587991648949427</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9123832094322347</v>
+        <v>0.9221449419329847</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.048221086490122</v>
+        <v>5.054078125990571</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,45 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.567501766537622</v>
+        <v>3.71707115842477</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.794476060805077</v>
+        <v>-4.770932598363922</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.58459031061939</v>
+        <v>2.594007695595852</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9123832094322347</v>
+        <v>0.9221449419329847</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.050167084914509</v>
+        <v>5.056024124414959</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="2" t="n">
+        <v>45546</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>3.538161642053999</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>4.510629019593973</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>-4.770932598363922</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>2.594007695595852</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0.9221449419329847</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>4.503692816580341</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-638.7%</t>
+          <t>-641.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-116.8%</t>
+          <t>-117.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.8%</t>
+          <t>-319.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-131.8%</t>
+          <t>-132.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.730593902569135</v>
+        <v>-2.74995449124401</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.284102285389706</v>
+        <v>2.276358049919756</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.195230628398241</v>
+        <v>1.185468895897491</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.093834647770052</v>
+        <v>4.087977608269602</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.819470533737609</v>
+        <v>-2.838831122412484</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.251442727467617</v>
+        <v>2.243698491997668</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.106353997229767</v>
+        <v>1.096592264729017</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.043399763614269</v>
+        <v>4.037542724113819</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.895800511338515</v>
+        <v>-2.915161100013389</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.21902254932103</v>
+        <v>2.21127831385108</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.106353997229767</v>
+        <v>1.096592264729017</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.041511576508044</v>
+        <v>4.035654537007594</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.989464456016056</v>
+        <v>-3.008825044690931</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.176377201052876</v>
+        <v>2.168632965582926</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.012690052552226</v>
+        <v>1.002928320051476</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.980133439304382</v>
+        <v>3.974276399803931</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.151032881543312</v>
+        <v>-3.170393470218186</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.110183841052126</v>
+        <v>2.102439605582176</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8859071287543464</v>
+        <v>0.8761453962535964</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.902497695235806</v>
+        <v>3.896640655735356</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.259333543413431</v>
+        <v>-3.278694132088305</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.079936983169997</v>
+        <v>2.072192747700047</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8859071287543464</v>
+        <v>0.8761453962535964</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.915571102101724</v>
+        <v>3.909714062601275</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.277137515134175</v>
+        <v>-3.29649810380905</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.064820591264639</v>
+        <v>2.057076355794689</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8153725058491452</v>
+        <v>0.8056107733483953</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.865255525141544</v>
+        <v>3.859398485641094</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.305038302243648</v>
+        <v>-3.324398890918522</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.052184317547852</v>
+        <v>2.044440082077903</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7807755817062104</v>
+        <v>0.7710138492054605</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.843021411782785</v>
+        <v>3.837164372282335</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.427564404946542</v>
+        <v>-3.446924993621416</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.999938320443893</v>
+        <v>1.992194084973943</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6582494790033165</v>
+        <v>0.6484877465025666</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.766270194138247</v>
+        <v>3.760413154637797</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.65807890113213</v>
+        <v>-3.677439489807005</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.974438481560162</v>
+        <v>1.966694246090212</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4277349828177278</v>
+        <v>0.4179732503169779</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.694667456017398</v>
+        <v>3.688810416516948</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.006823986356574</v>
+        <v>-4.026184575031449</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.975252166472231</v>
+        <v>1.967507931002281</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.31898702889883</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.769730402667906</v>
+        <v>3.763873363167456</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.160810404132715</v>
+        <v>-4.180170992807589</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.982637868507415</v>
+        <v>1.974893633037465</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.31898702889883</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.838710671813546</v>
+        <v>3.832853632313096</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.110288500305049</v>
+        <v>-4.129649088979924</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.988897832158602</v>
+        <v>1.981153596688652</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.31898702889883</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.824761873933667</v>
+        <v>3.818904834433217</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.362763654312773</v>
+        <v>-4.382124242987648</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.899778259610926</v>
+        <v>1.892034024140976</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.31898702889883</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.836632362989081</v>
+        <v>3.830775323488631</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.655659410792185</v>
+        <v>-4.67501999946706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.783830491538105</v>
+        <v>1.776086256068155</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.31898702889883</v>
+        <v>0.3092252963980801</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.837842897508025</v>
+        <v>3.831985858007575</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.842323538926993</v>
+        <v>-4.861684127601868</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.713286582511503</v>
+        <v>1.705542347041553</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2922480580742701</v>
+        <v>0.2824863255735202</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.82592125724061</v>
+        <v>3.82006421774016</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.988344225840955</v>
+        <v>-5.00770481451583</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.649956160482108</v>
+        <v>1.642211925012158</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2831649662804132</v>
+        <v>0.2734032337796632</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.815549254900485</v>
+        <v>3.809692215400036</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.08005823495054</v>
+        <v>-5.099418823625415</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.775474613537318</v>
+        <v>1.767730378067368</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2831649662804132</v>
+        <v>0.2734032337796632</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.977753311599529</v>
+        <v>3.971896272099079</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.111709894010509</v>
+        <v>-5.131070482685384</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.757660587877144</v>
+        <v>1.749916352407194</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2779965090359729</v>
+        <v>0.268234776535223</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.969498875216679</v>
+        <v>3.96364183571623</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.193644712279393</v>
+        <v>-5.213005300954268</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.735116078138082</v>
+        <v>1.727371842668132</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2680617634488928</v>
+        <v>0.2583000309481428</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.973767445432923</v>
+        <v>3.967910405932472</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.2956208345278</v>
+        <v>-5.314981423202675</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.703251267694622</v>
+        <v>1.695507032224672</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1660856412004852</v>
+        <v>0.1563239086997352</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.921507410539781</v>
+        <v>3.91565037103933</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.185614551050579</v>
+        <v>-5.204975139725454</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.739406668329686</v>
+        <v>1.731662432859736</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1892902131177604</v>
+        <v>0.1795284806170104</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.927583040934321</v>
+        <v>3.921726001433871</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.042554975309653</v>
+        <v>-5.061915563984527</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.800880509348031</v>
+        <v>1.793136273878081</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1973036397077397</v>
+        <v>0.1875419072069897</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.936641107610283</v>
+        <v>3.930784068109832</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.741108249837815</v>
+        <v>-4.76046883851269</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.928720082419302</v>
+        <v>1.920975846949352</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4987503651795769</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.124770025775922</v>
+        <v>4.118912986275471</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.765698494072999</v>
+        <v>-4.785059082747874</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.919855162477939</v>
+        <v>1.912110927007989</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4987503651795769</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.125741203528632</v>
+        <v>4.119884164028182</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.714660118066479</v>
+        <v>-4.734020706741354</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.941113417260302</v>
+        <v>1.933369181790352</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4987503651795769</v>
+        <v>0.488988632678827</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.126584107908387</v>
+        <v>4.120727068407938</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.673520823199848</v>
+        <v>-4.692881411874723</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.9766072340811</v>
+        <v>1.96886299861115</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5398896600462078</v>
+        <v>0.5301279275454578</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.170305783702512</v>
+        <v>4.164448744202061</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.576885911181208</v>
+        <v>-4.596246499856083</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.831445195012491</v>
+        <v>1.823700959542541</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6365245720648477</v>
+        <v>0.6267628395640977</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.04447072703763</v>
+        <v>4.03861368753718</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.70746664571205</v>
+        <v>-4.726827234386925</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.782714945274118</v>
+        <v>1.774970709804168</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5059438375340052</v>
+        <v>0.4961821050332552</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.969624330393088</v>
+        <v>3.963767290892639</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.542970311521088</v>
+        <v>-4.562330900195963</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.832940298026585</v>
+        <v>1.825196062556635</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6704401717249671</v>
+        <v>0.6606784392242171</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.052748949983748</v>
+        <v>4.046891910483298</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.465871709979216</v>
+        <v>-4.485232298654091</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.862967449079764</v>
+        <v>1.855223213609814</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6704401717249671</v>
+        <v>0.6606784392242171</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.051936660420178</v>
+        <v>4.046079620919728</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.476256904869105</v>
+        <v>-4.49561749354398</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.86868215024888</v>
+        <v>1.86093791477893</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6600549768350777</v>
+        <v>0.6502932443343278</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.055574322611316</v>
+        <v>4.049717283110867</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.49484506359133</v>
+        <v>-4.514205652266205</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.932083892536416</v>
+        <v>1.924339657066466</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6414668181128524</v>
+        <v>0.6317050856121025</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.115258433154406</v>
+        <v>4.109401393653957</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.495143610287366</v>
+        <v>-4.514504198962241</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.9288334846763</v>
+        <v>1.92108924920635</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6411682714168165</v>
+        <v>0.6314065389160666</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.111948315955083</v>
+        <v>4.106091276454634</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.394320476596938</v>
+        <v>-4.413681065271813</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.973693633091862</v>
+        <v>1.965949397621912</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6536324869011704</v>
+        <v>0.6438707544004204</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.123957740185087</v>
+        <v>4.118100700684638</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.203539115844531</v>
+        <v>-4.222899704519406</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.050135430871368</v>
+        <v>2.042391195401418</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8444138476535777</v>
+        <v>0.8346521151528278</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.238555810115075</v>
+        <v>4.232698770614626</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.09657575799511</v>
+        <v>-4.115936346669985</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.072757619748733</v>
+        <v>2.065013384278783</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9028784556133792</v>
+        <v>0.8931167231126292</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.253471420628553</v>
+        <v>4.247614381128103</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.041245170093347</v>
+        <v>-4.060605758768222</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.129856791521497</v>
+        <v>2.122112556051547</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9582090435151414</v>
+        <v>0.9484473110143914</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.321636709981668</v>
+        <v>4.315779670481218</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.029191043180385</v>
+        <v>-4.048551631855259</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.12836501018812</v>
+        <v>2.12062077471817</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9702631704281042</v>
+        <v>0.9605014379273542</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.322555754030883</v>
+        <v>4.316698714530434</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.070346162748606</v>
+        <v>-4.08970675142348</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.113783592544968</v>
+        <v>2.106039357075018</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9291080508598832</v>
+        <v>0.9193463183591333</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.299743312474087</v>
+        <v>4.293886272973637</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.002297600057076</v>
+        <v>-4.02165818873195</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.153854043499462</v>
+        <v>2.146109808029512</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9971566135514132</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.353423475966888</v>
+        <v>4.347566436466437</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.233897993226576</v>
+        <v>-4.253258581901451</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.081416556405256</v>
+        <v>2.073672320935306</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9971566135514132</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.373626146140482</v>
+        <v>4.367769106640031</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.283949538755795</v>
+        <v>-4.30331012743067</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.04500217426045</v>
+        <v>2.0372579387905</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9971566135514132</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.357232382207363</v>
+        <v>4.351375342706914</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.45905637133224</v>
+        <v>-4.478416960007115</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.935211354823339</v>
+        <v>1.927467119353389</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9971566135514132</v>
+        <v>0.9873948810506631</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.31748429580083</v>
+        <v>4.31162725630038</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.262956217901717</v>
+        <v>-4.282316806576592</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.020674035192488</v>
+        <v>2.012929799722538</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.193256766981936</v>
+        <v>1.183495034481186</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.442167006856084</v>
+        <v>4.436309967355634</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.109930825788433</v>
+        <v>-4.129291414463307</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.181055191610706</v>
+        <v>2.173310956140756</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.34628215909522</v>
+        <v>1.33652042659447</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.633153241696959</v>
+        <v>4.627296202196509</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.138238139661703</v>
+        <v>-4.157598728336578</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.357198490969691</v>
+        <v>2.349454255499741</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.34628215909522</v>
+        <v>1.33652042659447</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.820619466605251</v>
+        <v>4.814762427104801</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.304831364775225</v>
+        <v>-4.3241919534501</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.259964152278364</v>
+        <v>2.252219916808414</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.179688933981698</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.69006648289122</v>
+        <v>4.68420944339077</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.281795571413659</v>
+        <v>-4.301156160088534</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.272854872284708</v>
+        <v>2.265110636814758</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.179688933981698</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.693742885552938</v>
+        <v>4.687885846052488</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.252549590957963</v>
+        <v>-4.271910179632838</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.282171319590482</v>
+        <v>2.274427084120532</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.179688933981698</v>
+        <v>1.169927201480948</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.691360940676433</v>
+        <v>4.685503901175983</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.359475138835814</v>
+        <v>-4.378835727510689</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.236694339596976</v>
+        <v>2.228950104127026</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.072763386103846</v>
+        <v>1.063001653603096</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.624498851107357</v>
+        <v>4.618641811606907</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.504493697343062</v>
+        <v>-4.523854286017937</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.180115718337311</v>
+        <v>2.172371482867361</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9277448275965978</v>
+        <v>0.9179830950958479</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.538916518146243</v>
+        <v>4.533059478645793</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62283546312778</v>
+        <v>-4.642196051802655</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.232710251281177</v>
+        <v>2.224966015811227</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9384308661594879</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.645259380541729</v>
+        <v>4.639402341041279</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.674245885448488</v>
+        <v>-4.693606474123363</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.209931779478833</v>
+        <v>2.202187544008883</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9384308661594879</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.643045077667669</v>
+        <v>4.637188038167218</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.75366533665624</v>
+        <v>-4.773025925331114</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.178067127070022</v>
+        <v>2.170322891600072</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9384308661594879</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.642948205741957</v>
+        <v>4.637091166241508</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.849128334573457</v>
+        <v>-4.868488923248332</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.139875821461178</v>
+        <v>2.132131585991228</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9384308661594879</v>
+        <v>0.9286691336587379</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.642942099300001</v>
+        <v>4.637085059799551</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.784752423722742</v>
+        <v>-4.804113012397617</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.163722582364075</v>
+        <v>2.155978346894125</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.002806777010203</v>
+        <v>0.993045044509453</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.679664042373041</v>
+        <v>4.673807002872591</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.840121585854936</v>
+        <v>-4.859482174529811</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.147308735258924</v>
+        <v>2.139564499788974</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.002806777010203</v>
+        <v>0.993045044509453</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.685397860120768</v>
+        <v>4.679540820620318</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.885559365685763</v>
+        <v>-4.904919954360638</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.128671986669525</v>
+        <v>2.120927751199575</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9599617863320433</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.659229229056804</v>
+        <v>4.653372189556354</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.797352531538185</v>
+        <v>-4.81671312021306</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.183829113178875</v>
+        <v>2.176084877708925</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9599617863320433</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.679103621907123</v>
+        <v>4.673246582406673</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.691317536332876</v>
+        <v>-4.710678125007751</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.209943811785727</v>
+        <v>2.202199576315777</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9599617863320433</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.662804322431851</v>
+        <v>4.656947282931401</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.508105873199781</v>
+        <v>-4.527466461874655</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.285659426503011</v>
+        <v>2.277915191033061</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9599617863320433</v>
+        <v>0.9502000538312934</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.665235271895896</v>
+        <v>4.659378232395446</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.43638442618593</v>
+        <v>-4.455745014860804</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.28013919115644</v>
+        <v>2.27239495568649</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.031683233345894</v>
+        <v>1.021921500845144</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.674059325952096</v>
+        <v>4.668202286451645</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.414011400578223</v>
+        <v>-4.433371989253098</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.236004147320695</v>
+        <v>2.228259911850745</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.042938984458795</v>
+        <v>1.033177251958045</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.627728522541008</v>
+        <v>4.621871483040558</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.447027696488968</v>
+        <v>-4.466388285163843</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.407995833841752</v>
+        <v>2.400251598371802</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9735016077920438</v>
+        <v>0.9637398752912938</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.771264301426313</v>
+        <v>4.765407261925863</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.43550006083936</v>
+        <v>-4.454860649514234</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.404528113929844</v>
+        <v>2.396783878459894</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.032502265993406</v>
+        <v>1.022740533492656</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.79858592217538</v>
+        <v>4.79272888267493</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.532841562181728</v>
+        <v>-4.552202150856603</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.369259625914686</v>
+        <v>2.361515390444736</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9880820838279178</v>
+        <v>0.9783203513271679</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.775601925397875</v>
+        <v>4.769744885897425</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.618697591521695</v>
+        <v>-4.63805818019657</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.336168296371537</v>
+        <v>2.328424060901587</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9457060146017828</v>
+        <v>0.9359442821010329</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.751427366055032</v>
+        <v>4.745570326554582</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.627534388937814</v>
+        <v>-4.646894977612689</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.315052779225591</v>
+        <v>2.307308543755641</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9382638419604321</v>
+        <v>0.9285021094596821</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.729381264290724</v>
+        <v>4.723524224790274</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.718916951503273</v>
+        <v>-4.738277540178148</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.288664265244457</v>
+        <v>2.280920029774507</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8468812793949738</v>
+        <v>0.8371195468942239</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.684716237796498</v>
+        <v>4.678859198296048</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.707210233516267</v>
+        <v>-4.726570822191142</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.395475210263528</v>
+        <v>2.387730974793578</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8585879973819802</v>
+        <v>0.8488262648812303</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.79386852641297</v>
+        <v>4.78801148691252</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.607546729432604</v>
+        <v>-4.626907318107479</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.438372950628398</v>
+        <v>2.430628715158448</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9217750805856667</v>
+        <v>0.9120133480849167</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.834813115066587</v>
+        <v>4.828956075566137</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.617862827598956</v>
+        <v>-4.637223416273831</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.647151344639915</v>
+        <v>2.639407109169965</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9217750805856667</v>
+        <v>0.9120133480849167</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.047717948344645</v>
+        <v>5.041860908844195</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.617768859581584</v>
+        <v>-4.637129448256458</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.646367598758954</v>
+        <v>2.638623363289004</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.047118532065126</v>
+        <v>5.041261492564676</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.624987683781428</v>
+        <v>-4.644348272456303</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.637712055023369</v>
+        <v>2.62996781955342</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.041350518009479</v>
+        <v>5.03549347850903</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.624039260663389</v>
+        <v>-4.643399849338264</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.638091424270585</v>
+        <v>2.630347188800635</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.041350518009479</v>
+        <v>5.03549347850903</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.781107718919014</v>
+        <v>-4.800468307593889</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.587991648949427</v>
+        <v>2.580247413479477</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.054078125990571</v>
+        <v>5.048221086490122</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.71707115842477</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.770932598363922</v>
+        <v>-4.794476060805077</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.594007695595852</v>
+        <v>2.58459031061939</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.056024124414959</v>
+        <v>5.050167084914509</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,19 +49477,19 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.538161642053999</v>
+        <v>3.538161642054</v>
       </c>
       <c r="C2084" t="n">
         <v>4.510629019593973</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.770932598363922</v>
+        <v>-4.794476060805077</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.594007695595852</v>
+        <v>2.58459031061939</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9221449419329847</v>
+        <v>0.9123832094322347</v>
       </c>
       <c r="G2084" t="n">
         <v>4.503692816580341</v>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.4%</t>
+          <t>155.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.0%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.0%</t>
+          <t>-635.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.8%</t>
+          <t>-115.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.6%</t>
+          <t>-325.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-132.8%</t>
+          <t>-120.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.013413206963508</v>
+        <v>-8.983192886917529</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4448834937941015</v>
+        <v>-0.4327953657757102</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.533325782085339</v>
+        <v>-1.50310546203936</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.240842744053846</v>
+        <v>2.258974936081433</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.145706352616113</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.4966849622165874</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.600738892458046</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.201510667668777</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.271743145984402</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.5444059509347885</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.575487269648304</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.219355369983738</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.214671374088471</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.5175869064900152</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.575487269648304</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.223345705670138</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.356343215812592</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.575730870078405</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.575487269648304</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.221870478771397</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.306752371387757</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.5408411221435991</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.52589642522347</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.266678395591169</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.157834036915901</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.4943249220015393</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.494646834488297</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.27237701638559</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-8.931988884196489</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.394407787877566</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.452720158901133</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.307112094774097</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.807410227858897</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.3434371807864705</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.452720158901133</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.308251239330156</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.782373546290387</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.3307887339969589</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.427391071350398</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.326082466022705</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.710240371002506</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.2962017596431696</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.427391071350398</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.331816170261342</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.638873978392859</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.2773924649931763</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.35602467874075</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.364898743433265</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.545414944407634</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.249892332711994</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.35602467874075</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.355015262120357</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.534761762854203</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.247465620589995</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.35602467874075</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.353180701620984</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.436854724177712</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.2086031200928598</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.288038928880193</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.393671836563857</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.412901183201754</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.1983531975569828</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.264085387904236</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.408712467294925</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.148841244878957</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.1059895383896161</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.00002544958144</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.553888114126851</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.441761621374119</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.1740552773520183</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.00002544958144</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.55110108046655</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.401577323007928</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.1904726205863359</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.9598411512152488</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.575555283374106</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.238177452068566</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.2551993901828378</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.7964412802758863</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.67296202715848</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-7.004696229838967</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.3565163079125293</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.5629600580462878</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.820975189334091</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-6.855029838831452</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.4134906540025765</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.4700565668037519</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.873825073766654</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.722754365200566</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.3676616294620856</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.3377810931728652</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.85445114395234</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581113469681644</v>
+        <v>-6.550893149635663</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.427133048357291</v>
+        <v>0.4392211763756833</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.1659198776079623</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.960382933978919</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.496148802952325</v>
+        <v>-6.465928482906344</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4740252562726774</v>
+        <v>0.4861133842910697</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.08095521087864277</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>3.024268075240169</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.601738792725429</v>
+        <v>-6.571518472679449</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3038133307642168</v>
+        <v>0.3159014587826094</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.1865452006517471</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.832938151777088</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.533504208100002</v>
+        <v>-6.503283888054021</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3796515064914745</v>
+        <v>0.3917396345098667</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.1681298777792111</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.892531687377696</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.385564166692403</v>
+        <v>-6.355343846646422</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3222067144161072</v>
+        <v>0.3342948424344994</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1478089618706536</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.788103428284423</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.332594644438414</v>
+        <v>-6.302374324392433</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3346805370642243</v>
+        <v>0.3467686650826165</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.09483943961666469</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.811171155383339</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.166806448478123</v>
+        <v>-6.136586128432143</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3940352033532473</v>
+        <v>0.4061233313716395</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.09483943961666469</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.804210543288245</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.133443241999355</v>
+        <v>-6.103222921953374</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.421842840325898</v>
+        <v>0.4339309683442902</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.09483943961666469</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.818672897669388</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.025184104876833</v>
+        <v>-5.994963784830852</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4596786156341017</v>
+        <v>0.4717667436524939</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.09483943961666469</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.813205018128583</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.901892970059702</v>
+        <v>-5.871672650013721</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5064931635715308</v>
+        <v>0.5185812915899231</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.02845169520046581</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.884677793029439</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849196102928411</v>
+        <v>-5.81897578288243</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5352728886613725</v>
+        <v>0.5473610166797651</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.08114856233175699</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.923996891545539</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605430660944966</v>
+        <v>-5.575210340898986</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6285597738018009</v>
+        <v>0.6406479018201932</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.08114856233175699</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.919777599892589</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.515654988568494</v>
+        <v>-5.485434668522513</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6665943566724057</v>
+        <v>0.6786824846907984</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.142748007246067</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.958861580761191</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.26580459461942</v>
+        <v>-5.235584274573439</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7592765892357378</v>
+        <v>0.77136471725413</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.142748007246067</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.951603655744893</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.089912502151988</v>
+        <v>-5.059692182106007</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8332325497433595</v>
+        <v>0.8453206777617517</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.142748007246067</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.955202779265542</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.918466039129524</v>
+        <v>-4.888245719083543</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9151386410068985</v>
+        <v>0.9272267690252909</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.3141944702685301</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.071398163133574</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838443752020403</v>
+        <v>-4.808223431974422</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9461680334668439</v>
+        <v>0.9582561614852363</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3942167573776511</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.118432013015343</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774808009786469</v>
+        <v>-4.744587689740488</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.976317131414735</v>
+        <v>0.9884052594331272</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4578524996115856</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.161308259410021</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.681110691570074</v>
+        <v>-4.650890371524093</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9949903174850887</v>
+        <v>1.007078445503481</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4578524996115856</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.142502518193817</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.691613314635362</v>
+        <v>-4.661392994589382</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9925323448838506</v>
+        <v>1.004620472902243</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4473498765462968</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.137944020979521</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.579127053966488</v>
+        <v>-4.548906733920507</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145616298622</v>
+        <v>1.053544291004613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4473498765462968</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.141873334814341</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.561413367088623</v>
+        <v>-4.531193047042642</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.049220221654707</v>
+        <v>1.061308349673099</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4505312054432136</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.144460716069831</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437939095775604</v>
+        <v>-4.407718775729624</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.095608001399907</v>
+        <v>1.1076961294183</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4505312054432136</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.141458787289825</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217918297738594</v>
+        <v>-4.187697977692613</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.185195357625326</v>
+        <v>1.197283485643718</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5917510505111938</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.227769731341227</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085050608675316</v>
+        <v>-4.054830288629335</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.25423661605246</v>
+        <v>1.266324744070852</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5917510505111938</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.24366391414305</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964877525310817</v>
+        <v>-3.934657205264837</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.303451693838561</v>
+        <v>1.315539821856954</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.7119241338756928</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.316913608602052</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.82962416398084</v>
+        <v>-3.79940384393486</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.367641140931992</v>
+        <v>1.379729268950384</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.8471774952056699</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.408153727961478</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889498991338533</v>
+        <v>-3.859278671292552</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.329728701390341</v>
+        <v>1.341816829408733</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7873026678479778</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.358266322948288</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769678760427695</v>
+        <v>-3.739458440381715</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.392945962988885</v>
+        <v>1.405034091007277</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7873026678479778</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.373555492182497</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772148466889501</v>
+        <v>-3.741928146843521</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.299602279726604</v>
+        <v>1.311690407744996</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.7848329613861715</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.279717867627855</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840518653213511</v>
+        <v>-3.81029833316753</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191516066682301</v>
+        <v>1.203604194700693</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7941086604223865</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.204545148534885</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.952390932839662</v>
+        <v>-3.922170612793681</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.137203863463732</v>
+        <v>1.149291991482124</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7941086604223865</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.194981857166777</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.007911008732251</v>
+        <v>-3.977690688686271</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.252026669798899</v>
+        <v>1.264114797817291</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7941086604223865</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.332012693858979</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.832436748939782</v>
+        <v>-3.802216428893801</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.326783605707674</v>
+        <v>1.338871733726066</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7941086604223865</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.336579925850767</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.824512374354868</v>
+        <v>-3.794292054308887</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.305695384302847</v>
+        <v>1.317783512321239</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7941086604223865</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.312321954611974</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.818234171785019</v>
+        <v>-3.788013851739038</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.236744978732236</v>
+        <v>1.248833106750629</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8003868629922355</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.244627189555333</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.758381552581296</v>
+        <v>-3.728161232535315</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.270858412845858</v>
+        <v>1.28294654086425</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8003868629922355</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.254799575987465</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.672138089554918</v>
+        <v>-3.641917769508938</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.300302068630269</v>
+        <v>1.312390196648662</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8003868629922355</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.249745846561325</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.717444908953898</v>
+        <v>-3.687224588907918</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.273955116315203</v>
+        <v>1.286043244333595</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7595766999830047</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.217035524200313</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7464780136562</v>
+        <v>-3.716257693610219</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.262893747467384</v>
+        <v>1.274981875485776</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7595766999830047</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.217587397233414</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.653667532205341</v>
+        <v>-3.62344721215936</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.229290631939093</v>
+        <v>1.241378759957485</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.852387181433864</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.202546377995295</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.698057001534768</v>
+        <v>-3.667836681488787</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.213408320131923</v>
+        <v>1.225496448150315</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.8079977121044364</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.177786172322239</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.814598606640111</v>
+        <v>-3.78437828659413</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.161867386601509</v>
+        <v>1.173955514619901</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6612357869531147</v>
+        <v>0.6914561069990937</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.08480472574317</v>
+        <v>3.102936917770757</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.854522701222683</v>
+        <v>-3.824302381176702</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.151389044599147</v>
+        <v>1.16347717261754</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6612357869531147</v>
+        <v>0.6914561069990937</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.090296021573837</v>
+        <v>3.108428213601424</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.882303099124036</v>
+        <v>-3.852082779078055</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.151774087207145</v>
+        <v>1.163862215225537</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6334553890517616</v>
+        <v>0.6636757090977405</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.085124984601564</v>
+        <v>3.103257176629151</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.000683771854174</v>
+        <v>-3.970463451808194</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9427775381157431</v>
+        <v>0.9548656661341353</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.5964578569467643</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.883149993311632</v>
+        <v>2.901282185339219</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.109297850297505</v>
+        <v>-4.079077530251524</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.019481567457616</v>
+        <v>1.031569695476009</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.5964578569467643</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.003299654030837</v>
+        <v>3.021431846058424</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.073888812049362</v>
+        <v>-4.043668492003381</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.048158208859197</v>
+        <v>1.060246336877589</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.5964578569467643</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.01781268013316</v>
+        <v>3.035944872160747</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.035505149491211</v>
+        <v>-4.00528482944523</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.060931115224826</v>
+        <v>1.073019243243218</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6046211994589366</v>
+        <v>0.6348415195049155</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.038262319010419</v>
+        <v>3.056394511038007</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.858388819456045</v>
+        <v>-3.828168499410064</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.128506676084194</v>
+        <v>1.140594804102586</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6046211994589366</v>
+        <v>0.6348415195049155</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.034991347855721</v>
+        <v>3.053123539883309</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.903481064289591</v>
+        <v>-3.87326074424361</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.111153169912689</v>
+        <v>1.123241297931081</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5427251562895468</v>
+        <v>0.5729454763355257</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.998537113716001</v>
+        <v>3.016669305743588</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.724105643050823</v>
+        <v>-3.693885323004842</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.17669031371461</v>
+        <v>1.188778441733003</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6995019144602654</v>
+        <v>0.7297222345062444</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.086390143924846</v>
+        <v>3.104522335952434</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.769119856571429</v>
+        <v>-3.738899536525448</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.139492083637958</v>
+        <v>1.15158021165635</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6691530191456608</v>
+        <v>0.6993733391916398</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.048988262067673</v>
+        <v>3.067120454095261</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.036124366843865</v>
+        <v>-4.005904046797884</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.038381841867929</v>
+        <v>1.050469969886321</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4747899811027123</v>
+        <v>0.5050103011486913</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.93806200158085</v>
+        <v>2.956194193608437</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.137322148281037</v>
+        <v>-4.107101828235057</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9971066511895614</v>
+        <v>1.009194779207954</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4063811675573931</v>
+        <v>0.4366014876033721</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.89622063535016</v>
+        <v>2.914352827377747</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.130811181666725</v>
+        <v>-4.100590861620744</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9973109993896032</v>
+        <v>1.009399127407995</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4063811675573931</v>
+        <v>0.4366014876033721</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.893820596904476</v>
+        <v>2.911952788932064</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.111773053959427</v>
+        <v>-4.081552733913447</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.001450969680767</v>
+        <v>1.013539097699159</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3481975562261985</v>
+        <v>0.3784178762721775</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.855435149314005</v>
+        <v>2.873567341341592</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.164288856234248</v>
+        <v>-4.134068536188267</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.099739050405029</v>
+        <v>1.111827178423421</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3481975562261985</v>
+        <v>0.3784178762721775</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.974729550948195</v>
+        <v>2.992861742975783</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.178155617568166</v>
+        <v>-4.147935297522185</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.095025674857596</v>
+        <v>1.107113802875988</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3103396394923756</v>
+        <v>0.3405599595383546</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.952848129894035</v>
+        <v>2.970980321921622</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.137672625645821</v>
+        <v>-4.10745230559984</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.11722740202346</v>
+        <v>1.129315530041852</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3103396394923756</v>
+        <v>0.3405599595383546</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.958856660290961</v>
+        <v>2.976988852318548</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.989929655410819</v>
+        <v>-3.959709335364838</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.07427481139466</v>
+        <v>1.086362939413052</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4781469967272587</v>
+        <v>0.5083673167732378</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.95749129590909</v>
+        <v>2.975623487936677</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.073750876685517</v>
+        <v>-4.043530556639536</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.043539944416262</v>
+        <v>1.055628072434654</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4781469967272587</v>
+        <v>0.5083673167732378</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.960284917440571</v>
+        <v>2.978417109468158</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.067598170632732</v>
+        <v>-4.037377850586751</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.046663375229034</v>
+        <v>1.058751503247426</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.484299702780043</v>
+        <v>0.514520022826022</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.9646388894639</v>
+        <v>2.982771081491487</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.084407468783234</v>
+        <v>-4.054187148737253</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.039020132708943</v>
+        <v>1.051108260727336</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4674904046295414</v>
+        <v>0.4977107246755204</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.953633787313709</v>
+        <v>2.971765979341296</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.022109470007112</v>
+        <v>-3.991889149961132</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.130274886016213</v>
+        <v>1.142363014034605</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5127846689039834</v>
+        <v>0.5430049889499624</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.047145899675195</v>
+        <v>3.065278091702783</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.820319272341954</v>
+        <v>-3.790098952295974</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.013282966796403</v>
+        <v>1.025371094814795</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7108028610731378</v>
+        <v>0.7410231811191168</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.968248816690815</v>
+        <v>2.986381008718403</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.871205985028149</v>
+        <v>-3.840985664982168</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.063218514044101</v>
+        <v>1.075306642062493</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6599161483869433</v>
+        <v>0.6901364684329223</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.008007021401274</v>
+        <v>3.026139213428861</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.784595242378341</v>
+        <v>-3.754374922332361</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.112490547220067</v>
+        <v>1.124578675238459</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7385418795921016</v>
+        <v>0.7687621996380806</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.069810196240412</v>
+        <v>3.087942388267999</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.844804540383626</v>
+        <v>-3.814584220337645</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.086942808842625</v>
+        <v>1.099030936861017</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6783325815868171</v>
+        <v>0.7085529016327961</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.032220598261913</v>
+        <v>3.050352790289501</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.795617891699274</v>
+        <v>-3.765397571653294</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.105109086356294</v>
+        <v>1.117197214374686</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6783325815868171</v>
+        <v>0.7085529016327961</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.030712216301842</v>
+        <v>3.048844408329429</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.751244760060706</v>
+        <v>-3.721024440014725</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.122721206447158</v>
+        <v>1.13480933446555</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7227057132253857</v>
+        <v>0.7529260332713646</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.057198962720419</v>
+        <v>3.075331154748007</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.773725110919591</v>
+        <v>-3.74350479087361</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.108122860242194</v>
+        <v>1.120210988260587</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7227057132253857</v>
+        <v>0.7529260332713646</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.05159275685901</v>
+        <v>3.069724948886597</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.726069380358535</v>
+        <v>-3.695849060312555</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.133566909494421</v>
+        <v>1.145655037512813</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7703614437864413</v>
+        <v>0.8005817638324203</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.086567952223448</v>
+        <v>3.104700144251035</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.62555122185978</v>
+        <v>-3.5953309018138</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.178666546268648</v>
+        <v>1.19075467428704</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8708796022851959</v>
+        <v>0.9010999223311749</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.151771220697425</v>
+        <v>3.169903412725013</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.609645892427428</v>
+        <v>-3.579425572381448</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.171783350517461</v>
+        <v>1.183871478535853</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.791766941575957</v>
+        <v>0.8219872616219359</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.091058296747754</v>
+        <v>3.109190488775341</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.564807490819029</v>
+        <v>-3.53458717077305</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.193816413771449</v>
+        <v>1.205904541789841</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7963103745208264</v>
+        <v>0.8265306945668054</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.097882059125304</v>
+        <v>3.116014251152892</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.584305947061038</v>
+        <v>-3.554085627015058</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.190177970905724</v>
+        <v>1.202266098924116</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7482257332409221</v>
+        <v>0.7784460532869011</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.07319221398844</v>
+        <v>3.091324406016027</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.540103109975137</v>
+        <v>-3.509882789929157</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.213738708267921</v>
+        <v>1.225826836286313</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7924285703268226</v>
+        <v>0.8226488903728015</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.105593518767817</v>
+        <v>3.123725710795405</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.547662775812184</v>
+        <v>-3.517442455766204</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.20912484240235</v>
+        <v>1.221212970420742</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8472319743366419</v>
+        <v>0.8774522943826208</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.136885561642957</v>
+        <v>3.155017753670544</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.389371358272912</v>
+        <v>-3.359151038226932</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.323689174601099</v>
+        <v>1.335777302619491</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8472319743366419</v>
+        <v>0.8774522943826208</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.188133326825996</v>
+        <v>3.206265518853583</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.181729354638436</v>
+        <v>-3.151509034592456</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.405186680649142</v>
+        <v>1.417274808667534</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.054873977971118</v>
+        <v>1.085094298017097</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.311159233600935</v>
+        <v>3.329291425628522</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.130697261915908</v>
+        <v>-3.100476941869928</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.420547745976423</v>
+        <v>1.432635873994815</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.105906070693646</v>
+        <v>1.136126390739625</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.336726717472722</v>
+        <v>3.354858909500309</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.065473080788702</v>
+        <v>-3.035252760742722</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.463824822520011</v>
+        <v>1.475912950538403</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.171130251820852</v>
+        <v>1.201350571866831</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.39304863024175</v>
+        <v>3.411180822269337</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.028046060717568</v>
+        <v>-2.997825740671588</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.474756602847745</v>
+        <v>1.486844730866137</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.176381789850033</v>
+        <v>1.206602109896012</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.392160525358539</v>
+        <v>3.410292717386127</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.048157716752276</v>
+        <v>-3.017937396706297</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.467968732765101</v>
+        <v>1.480056860783493</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.187409134847453</v>
+        <v>1.217629454893432</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.400033724688231</v>
+        <v>3.418165916715818</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.019744453652393</v>
+        <v>-2.989524133606413</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.639891809026266</v>
+        <v>1.651979937044658</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.128433572101024</v>
+        <v>1.158653892147003</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.525206158061585</v>
+        <v>3.543338350089172</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.94496219262738</v>
+        <v>-2.9147418725814</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.789917622654088</v>
+        <v>1.80200575067248</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.203215833126037</v>
+        <v>1.233436153172015</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.690188423894409</v>
+        <v>3.708320615921997</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.918878108363572</v>
+        <v>-2.888657788317592</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.79205923237347</v>
+        <v>1.804147360391862</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.203215833126037</v>
+        <v>1.233436153172015</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.681896399908268</v>
+        <v>3.700028591935856</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.831000195254452</v>
+        <v>-2.800779875208472</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.825403593200898</v>
+        <v>1.83749172121929</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.319141475549388</v>
+        <v>1.349361795595367</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.749644980946059</v>
+        <v>3.767777172973646</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.822107733861168</v>
+        <v>-2.791887413815188</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.846514983485003</v>
+        <v>1.858603111503395</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.319141475549388</v>
+        <v>1.349361795595367</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.76719938667285</v>
+        <v>3.785331578700437</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.990583850831046</v>
+        <v>-2.960363530785066</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.770979584101635</v>
+        <v>1.783067712120027</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.291193639832807</v>
+        <v>1.321413959878786</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.742285732647486</v>
+        <v>3.760417924675073</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.544327658201606</v>
+        <v>-2.514107338155626</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.930751758341273</v>
+        <v>1.942839886359665</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.196474970163174</v>
+        <v>1.226695290209153</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.666724228033567</v>
+        <v>3.684856420061155</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.521606554518454</v>
+        <v>-2.491386234472474</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.930504222311439</v>
+        <v>1.942592350329831</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.196474970163174</v>
+        <v>1.226695290209153</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.657388250530472</v>
+        <v>3.67552044255806</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.650808367812496</v>
+        <v>-2.620588047766516</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.037729622844991</v>
+        <v>2.049817750863383</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.067273156869132</v>
+        <v>1.097493476915111</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.738773288405216</v>
+        <v>3.756905480432803</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.676682766286522</v>
+        <v>-2.646462446240542</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.064457685949027</v>
+        <v>2.076545813967419</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.112184765580873</v>
+        <v>1.142405085626852</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.802798076125907</v>
+        <v>3.820930268153495</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.669628076071348</v>
+        <v>-2.639407756025368</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.063954918024642</v>
+        <v>2.076043046043034</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.119239455796047</v>
+        <v>1.149459775842026</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.803706246244556</v>
+        <v>3.821838438272144</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.64267685174486</v>
+        <v>-2.61245653169888</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.084741561399978</v>
+        <v>2.09682968941837</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.134119801823766</v>
+        <v>1.164340121869745</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.82264060750593</v>
+        <v>3.840772799533517</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.664221079575647</v>
+        <v>-2.634000759529668</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.260227002412623</v>
+        <v>2.272315130431015</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.134119801823766</v>
+        <v>1.164340121869745</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.006743739650889</v>
+        <v>4.024875931678476</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.686629197380519</v>
+        <v>-2.65640887733454</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.243380450193667</v>
+        <v>2.25546857821206</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.134119801823766</v>
+        <v>1.164340121869745</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.998860434553882</v>
+        <v>4.016992626581469</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.71485343295812</v>
+        <v>-2.68463311291214</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.234144755512265</v>
+        <v>2.246232883530657</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.152096554275075</v>
+        <v>1.182316874321053</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.011700485574305</v>
+        <v>4.029832677601893</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.74995449124401</v>
+        <v>-2.69407403880067</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.276358049919756</v>
+        <v>2.298710230897092</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.185468895897491</v>
+        <v>1.304743991864445</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.087977608269602</v>
+        <v>4.159542665849775</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.838831122412484</v>
+        <v>-2.782950669969144</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.243698491997668</v>
+        <v>2.266050672975004</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.096592264729017</v>
+        <v>1.215867360695971</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.037542724113819</v>
+        <v>4.109107781693991</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.915161100013389</v>
+        <v>-2.85928064757005</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.21127831385108</v>
+        <v>2.233630494828416</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.096592264729017</v>
+        <v>1.215867360695971</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.035654537007594</v>
+        <v>4.107219594587766</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.008825044690931</v>
+        <v>-2.952944592247591</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.168632965582926</v>
+        <v>2.190985146560262</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.002928320051476</v>
+        <v>1.12220341601843</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.974276399803931</v>
+        <v>4.045841457384103</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.170393470218186</v>
+        <v>-3.114513017774846</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.102439605582176</v>
+        <v>2.124791786559512</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8761453962535964</v>
+        <v>0.9954204922205503</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.896640655735356</v>
+        <v>3.968205713315529</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.278694132088305</v>
+        <v>-3.222813679644966</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.072192747700047</v>
+        <v>2.094544928677383</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8761453962535964</v>
+        <v>0.9954204922205503</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.909714062601275</v>
+        <v>3.981279120181447</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.29649810380905</v>
+        <v>-3.24061765136571</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.057076355794689</v>
+        <v>2.079428536772025</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8056107733483953</v>
+        <v>0.9248858693153492</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.859398485641094</v>
+        <v>3.930963543221266</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.324398890918522</v>
+        <v>-3.268518438475183</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.044440082077903</v>
+        <v>2.066792263055238</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7710138492054605</v>
+        <v>0.8902889451724144</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.837164372282335</v>
+        <v>3.908729429862507</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.446924993621416</v>
+        <v>-3.391044541178077</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.992194084973943</v>
+        <v>2.014546265951279</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6484877465025666</v>
+        <v>0.7677628424695205</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.760413154637797</v>
+        <v>3.83197821221797</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.677439489807005</v>
+        <v>-3.621559037363665</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.966694246090212</v>
+        <v>1.989046427067548</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4179732503169779</v>
+        <v>0.5372483462839318</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.688810416516948</v>
+        <v>3.76037547409712</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.026184575031449</v>
+        <v>-3.970304122588109</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.967507931002281</v>
+        <v>1.989860111979617</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.428500392365034</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.763873363167456</v>
+        <v>3.835438420747629</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.180170992807589</v>
+        <v>-4.12429054036425</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.974893633037465</v>
+        <v>1.997245814014801</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.428500392365034</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.832853632313096</v>
+        <v>3.904418689893268</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.129649088979924</v>
+        <v>-4.073768636536584</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.981153596688652</v>
+        <v>2.003505777665988</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.428500392365034</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.818904834433217</v>
+        <v>3.890469892013389</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.382124242987648</v>
+        <v>-4.326243790544308</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.892034024140976</v>
+        <v>1.914386205118312</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.428500392365034</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.830775323488631</v>
+        <v>3.902340381068803</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.67501999946706</v>
+        <v>-4.61913954702372</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.776086256068155</v>
+        <v>1.798438437045491</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3092252963980801</v>
+        <v>0.428500392365034</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.831985858007575</v>
+        <v>3.903550915587747</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.861684127601868</v>
+        <v>-4.805803675158528</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.705542347041553</v>
+        <v>1.727894528018889</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2824863255735202</v>
+        <v>0.4017614215404741</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.82006421774016</v>
+        <v>3.891629275320333</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.00770481451583</v>
+        <v>-4.95182436207249</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.642211925012158</v>
+        <v>1.664564105989494</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2734032337796632</v>
+        <v>0.3926783297466171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.809692215400036</v>
+        <v>3.881257272980208</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.099418823625415</v>
+        <v>-5.043538371182075</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767730378067368</v>
+        <v>1.790082559044704</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2734032337796632</v>
+        <v>0.3926783297466171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.971896272099079</v>
+        <v>4.043461329679252</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.131070482685384</v>
+        <v>-5.075190030242045</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.749916352407194</v>
+        <v>1.77226853338453</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.268234776535223</v>
+        <v>0.3875098725021769</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.96364183571623</v>
+        <v>4.035206893296402</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.213005300954268</v>
+        <v>-5.157124848510928</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.727371842668132</v>
+        <v>1.749724023645468</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2583000309481428</v>
+        <v>0.3775751269150968</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.967910405932472</v>
+        <v>4.039475463512645</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.314981423202675</v>
+        <v>-5.259100970759335</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.695507032224672</v>
+        <v>1.717859213202008</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1563239086997352</v>
+        <v>0.2755990046666892</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.91565037103933</v>
+        <v>3.987215428619503</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.204975139725454</v>
+        <v>-5.149094687282114</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.731662432859736</v>
+        <v>1.754014613837072</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1795284806170104</v>
+        <v>0.2988035765839644</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.921726001433871</v>
+        <v>3.993291059014044</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.061915563984527</v>
+        <v>-5.006035111541188</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.793136273878081</v>
+        <v>1.815488454855416</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1875419072069897</v>
+        <v>0.3068170031739437</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.930784068109832</v>
+        <v>4.002349125690006</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.76046883851269</v>
+        <v>-4.70458838606935</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.920975846949352</v>
+        <v>1.943328027926688</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.488988632678827</v>
+        <v>0.6082637286457809</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.118912986275471</v>
+        <v>4.190478043855643</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.785059082747874</v>
+        <v>-4.729178630304534</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.912110927007989</v>
+        <v>1.934463107985325</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.488988632678827</v>
+        <v>0.6082637286457809</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.119884164028182</v>
+        <v>4.191449221608354</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.734020706741354</v>
+        <v>-4.678140254298014</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.933369181790352</v>
+        <v>1.955721362767688</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.488988632678827</v>
+        <v>0.6082637286457809</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.120727068407938</v>
+        <v>4.19229212598811</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.692881411874723</v>
+        <v>-4.637000959431383</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.96886299861115</v>
+        <v>1.991215179588486</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5301279275454578</v>
+        <v>0.6494030235124117</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.164448744202061</v>
+        <v>4.236013801782233</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.596246499856083</v>
+        <v>-4.540366047412743</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.823700959542541</v>
+        <v>1.846053140519877</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6267628395640977</v>
+        <v>0.7460379355310517</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.03861368753718</v>
+        <v>4.110178745117352</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.726827234386925</v>
+        <v>-4.670946781943585</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.774970709804168</v>
+        <v>1.797322890781504</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4961821050332552</v>
+        <v>0.6154572010002092</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.963767290892639</v>
+        <v>4.035332348472811</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.562330900195963</v>
+        <v>-4.506450447752623</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.825196062556635</v>
+        <v>1.847548243533971</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6606784392242171</v>
+        <v>0.7799535351911711</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.046891910483298</v>
+        <v>4.11845696806347</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.485232298654091</v>
+        <v>-4.429351846210751</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.855223213609814</v>
+        <v>1.87757539458715</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6606784392242171</v>
+        <v>0.7799535351911711</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.046079620919728</v>
+        <v>4.1176446784999</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.49561749354398</v>
+        <v>-4.43973704110064</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.86093791477893</v>
+        <v>1.883290095756266</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6502932443343278</v>
+        <v>0.7695683403012817</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.049717283110867</v>
+        <v>4.121282340691039</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.514205652266205</v>
+        <v>-4.458325199822865</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.924339657066466</v>
+        <v>1.946691838043802</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6317050856121025</v>
+        <v>0.7509801815790564</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.109401393653957</v>
+        <v>4.180966451234129</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.514504198962241</v>
+        <v>-4.458623746518901</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.92108924920635</v>
+        <v>1.943441430183686</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6314065389160666</v>
+        <v>0.7506816348830205</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.106091276454634</v>
+        <v>4.177656334034806</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.413681065271813</v>
+        <v>-4.357800612828473</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.965949397621912</v>
+        <v>1.988301578599248</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6438707544004204</v>
+        <v>0.7631458503673744</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.118100700684638</v>
+        <v>4.18966575826481</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.222899704519406</v>
+        <v>-4.167019252076066</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.042391195401418</v>
+        <v>2.064743376378754</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8346521151528278</v>
+        <v>0.9539272111197817</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.232698770614626</v>
+        <v>4.304263828194798</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.115936346669985</v>
+        <v>-4.060055894226645</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.065013384278783</v>
+        <v>2.087365565256119</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8931167231126292</v>
+        <v>1.012391819079583</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.247614381128103</v>
+        <v>4.319179438708275</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.060605758768222</v>
+        <v>-4.004725306324882</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.122112556051547</v>
+        <v>2.144464737028883</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9484473110143914</v>
+        <v>1.067722406981345</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.315779670481218</v>
+        <v>4.38734472806139</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.048551631855259</v>
+        <v>-3.99267117941192</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.12062077471817</v>
+        <v>2.142972955695505</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9605014379273542</v>
+        <v>1.079776533894308</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.316698714530434</v>
+        <v>4.388263772110606</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.08970675142348</v>
+        <v>-4.033826298980141</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.106039357075018</v>
+        <v>2.128391538052353</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9193463183591333</v>
+        <v>1.038621414326087</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.293886272973637</v>
+        <v>4.365451330553809</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.02165818873195</v>
+        <v>-3.965777736288612</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.146109808029512</v>
+        <v>2.168461989006847</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9873948810506631</v>
+        <v>1.106669977017617</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.347566436466437</v>
+        <v>4.41913149404661</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.253258581901451</v>
+        <v>-4.197378129458112</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.073672320935306</v>
+        <v>2.096024501912641</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9873948810506631</v>
+        <v>1.106669977017617</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.367769106640031</v>
+        <v>4.439334164220204</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.30331012743067</v>
+        <v>-4.247429674987332</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.0372579387905</v>
+        <v>2.059610119767835</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9873948810506631</v>
+        <v>1.106669977017617</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.351375342706914</v>
+        <v>4.422940400287086</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.478416960007115</v>
+        <v>-4.422536507563777</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.927467119353389</v>
+        <v>1.949819300330724</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9873948810506631</v>
+        <v>1.106669977017617</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.31162725630038</v>
+        <v>4.383192313880553</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.282316806576592</v>
+        <v>-4.226436354133254</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.012929799722538</v>
+        <v>2.035281980699873</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.183495034481186</v>
+        <v>1.30277013044814</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.436309967355634</v>
+        <v>4.507875024935807</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.129291414463307</v>
+        <v>-4.073410962019969</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.173310956140756</v>
+        <v>2.195663137118092</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.33652042659447</v>
+        <v>1.455795522561424</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.627296202196509</v>
+        <v>4.698861259776681</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.157598728336578</v>
+        <v>-4.10171827589324</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.349454255499741</v>
+        <v>2.371806436477076</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.33652042659447</v>
+        <v>1.455795522561424</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.814762427104801</v>
+        <v>4.886327484684974</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.3241919534501</v>
+        <v>-4.268311501006762</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.252219916808414</v>
+        <v>2.274572097785749</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.169927201480948</v>
+        <v>1.289202297447902</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.68420944339077</v>
+        <v>4.755774500970943</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.301156160088534</v>
+        <v>-4.245275707645196</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.265110636814758</v>
+        <v>2.287462817792093</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.169927201480948</v>
+        <v>1.289202297447902</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.687885846052488</v>
+        <v>4.75945090363266</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.271910179632838</v>
+        <v>-4.2160297271895</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.274427084120532</v>
+        <v>2.296779265097867</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.169927201480948</v>
+        <v>1.289202297447902</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.685503901175983</v>
+        <v>4.757068958756156</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.378835727510689</v>
+        <v>-4.322955275067351</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.228950104127026</v>
+        <v>2.251302285104362</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.063001653603096</v>
+        <v>1.18227674957005</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.618641811606907</v>
+        <v>4.69020686918708</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.523854286017937</v>
+        <v>-4.467973833574599</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.172371482867361</v>
+        <v>2.194723663844696</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9179830950958479</v>
+        <v>1.037258191062802</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.533059478645793</v>
+        <v>4.604624536225965</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.642196051802655</v>
+        <v>-4.586315599359317</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.224966015811227</v>
+        <v>2.247318196788562</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9286691336587379</v>
+        <v>1.047944229625692</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.639402341041279</v>
+        <v>4.710967398621452</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.693606474123363</v>
+        <v>-4.637726021680025</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.202187544008883</v>
+        <v>2.224539724986218</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9286691336587379</v>
+        <v>1.047944229625692</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.637188038167218</v>
+        <v>4.70875309574739</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.773025925331114</v>
+        <v>-4.717145472887776</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.170322891600072</v>
+        <v>2.192675072577407</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9286691336587379</v>
+        <v>1.047944229625692</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.637091166241508</v>
+        <v>4.708656223821681</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.868488923248332</v>
+        <v>-4.812608470804994</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.132131585991228</v>
+        <v>2.154483766968563</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9286691336587379</v>
+        <v>1.047944229625692</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.637085059799551</v>
+        <v>4.708650117379724</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.804113012397617</v>
+        <v>-4.748232559954279</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.155978346894125</v>
+        <v>2.17833052787146</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.993045044509453</v>
+        <v>1.112320140476407</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.673807002872591</v>
+        <v>4.745372060452763</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.859482174529811</v>
+        <v>-4.803601722086473</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.139564499788974</v>
+        <v>2.161916680766309</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.993045044509453</v>
+        <v>1.112320140476407</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.679540820620318</v>
+        <v>4.75110587820049</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.904919954360638</v>
+        <v>-4.8490395019173</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.120927751199575</v>
+        <v>2.14327993217691</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9502000538312934</v>
+        <v>1.069475149798248</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.653372189556354</v>
+        <v>4.724937247136526</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.81671312021306</v>
+        <v>-4.760832667769722</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.176084877708925</v>
+        <v>2.19843705868626</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9502000538312934</v>
+        <v>1.069475149798248</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.673246582406673</v>
+        <v>4.744811639986845</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.710678125007751</v>
+        <v>-4.654797672564412</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.202199576315777</v>
+        <v>2.224551757293112</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9502000538312934</v>
+        <v>1.069475149798248</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.656947282931401</v>
+        <v>4.728512340511573</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.527466461874655</v>
+        <v>-4.471586009431317</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.277915191033061</v>
+        <v>2.300267372010396</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9502000538312934</v>
+        <v>1.069475149798248</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.659378232395446</v>
+        <v>4.730943289975619</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.455745014860804</v>
+        <v>-4.399864562417466</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.27239495568649</v>
+        <v>2.294747136663825</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.021921500845144</v>
+        <v>1.141196596812098</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.668202286451645</v>
+        <v>4.739767344031819</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.433371989253098</v>
+        <v>-4.37749153680976</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.228259911850745</v>
+        <v>2.25061209282808</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.033177251958045</v>
+        <v>1.152452347925</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.621871483040558</v>
+        <v>4.693436540620731</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.466388285163843</v>
+        <v>-4.410507832720505</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.400251598371802</v>
+        <v>2.422603779349137</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9637398752912938</v>
+        <v>1.083014971258248</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.765407261925863</v>
+        <v>4.836972319506035</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.454860649514234</v>
+        <v>-4.398980197070896</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.396783878459894</v>
+        <v>2.41913605943723</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.022740533492656</v>
+        <v>1.142015629459611</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.79272888267493</v>
+        <v>4.864293940255102</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.552202150856603</v>
+        <v>-4.496321698413265</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.361515390444736</v>
+        <v>2.383867571422071</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9783203513271679</v>
+        <v>1.097595447294122</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.769744885897425</v>
+        <v>4.841309943477598</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.63805818019657</v>
+        <v>-4.582177727753232</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.328424060901587</v>
+        <v>2.350776241878922</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9359442821010329</v>
+        <v>1.055219378067987</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.745570326554582</v>
+        <v>4.817135384134755</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.646894977612689</v>
+        <v>-4.591014525169351</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.307308543755641</v>
+        <v>2.329660724732976</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9285021094596821</v>
+        <v>1.047777205426637</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.723524224790274</v>
+        <v>4.795089282370446</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.738277540178148</v>
+        <v>-4.68239708773481</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.280920029774507</v>
+        <v>2.303272210751842</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8371195468942239</v>
+        <v>0.9563946428611783</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.678859198296048</v>
+        <v>4.75042425587622</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.726570822191142</v>
+        <v>-4.670690369747803</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.387730974793578</v>
+        <v>2.410083155770913</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8488262648812303</v>
+        <v>0.9681013608481847</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.78801148691252</v>
+        <v>4.859576544492693</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.626907318107479</v>
+        <v>-4.571026865664141</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.430628715158448</v>
+        <v>2.452980896135783</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9120133480849167</v>
+        <v>1.031288444051871</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.828956075566137</v>
+        <v>4.900521133146309</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.637223416273831</v>
+        <v>-4.581342963830493</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.639407109169965</v>
+        <v>2.6617592901473</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9120133480849167</v>
+        <v>1.031288444051871</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.041860908844195</v>
+        <v>5.113425966424368</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.637129448256458</v>
+        <v>-4.58124899581312</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.638623363289004</v>
+        <v>2.660975544266339</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.041261492564676</v>
+        <v>5.112826550144848</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.644348272456303</v>
+        <v>-4.588467820012965</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.62996781955342</v>
+        <v>2.652320000530755</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.03549347850903</v>
+        <v>5.107058536089202</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.643399849338264</v>
+        <v>-4.587519396894926</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.630347188800635</v>
+        <v>2.65269936977797</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.03549347850903</v>
+        <v>5.107058536089202</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.800468307593889</v>
+        <v>-4.74458785515055</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.580247413479477</v>
+        <v>2.602599594456813</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.048221086490122</v>
+        <v>5.119786144070294</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.71707115842477</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.794476060805077</v>
+        <v>-4.738595608361739</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.58459031061939</v>
+        <v>2.606942491596725</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.050167084914509</v>
+        <v>5.121732142494682</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.538161642054</v>
+        <v>3.892247629344292</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.510629019593973</v>
+        <v>4.67479972748824</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.794476060805077</v>
+        <v>-4.738595608361739</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.58459031061939</v>
+        <v>2.606942491596725</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9123832094322347</v>
+        <v>1.031658305399189</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.503692816580341</v>
+        <v>4.667863524474607</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>105.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>155.9%</t>
+          <t>147.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.4%</t>
+          <t>-640.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-115.5%</t>
+          <t>-117.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-325.1%</t>
+          <t>-321.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-120.8%</t>
+          <t>-116.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.983192886917529</v>
+        <v>-9.013413206963508</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4327953657757102</v>
+        <v>-0.4448834937941015</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.50310546203936</v>
+        <v>-1.533325782085339</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.258974936081433</v>
+        <v>2.240842744053846</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.145706352616113</v>
+        <v>-9.175926672662092</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4966849622165874</v>
+        <v>-0.5087730902349792</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.600738892458046</v>
+        <v>-1.630959212504025</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.201510667668777</v>
+        <v>2.18337847564119</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.271743145984402</v>
+        <v>-9.301963466030381</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5444059509347885</v>
+        <v>-0.5564940789531803</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.575487269648304</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.219355369983738</v>
+        <v>2.20122317795615</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.214671374088471</v>
+        <v>-9.24489169413445</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5175869064900152</v>
+        <v>-0.5296750345084069</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.575487269648304</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.223345705670138</v>
+        <v>2.205213513642551</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.356343215812592</v>
+        <v>-9.386563535858571</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.575730870078405</v>
+        <v>-0.5878189980967967</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.575487269648304</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.221870478771397</v>
+        <v>2.20373828674381</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.306752371387757</v>
+        <v>-9.336972691433736</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5408411221435991</v>
+        <v>-0.5529292501619909</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.52589642522347</v>
+        <v>-1.556116745269449</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.266678395591169</v>
+        <v>2.248546203563582</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.157834036915901</v>
+        <v>-9.18805435696188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4943249220015393</v>
+        <v>-0.5064130500199311</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.494646834488297</v>
+        <v>-1.524867154534276</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.27237701638559</v>
+        <v>2.254244824358003</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.931988884196489</v>
+        <v>-8.96220920424247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.394407787877566</v>
+        <v>-0.4064959158959582</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.452720158901133</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.307112094774097</v>
+        <v>2.28897990274651</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.807410227858897</v>
+        <v>-8.837630547904878</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3434371807864705</v>
+        <v>-0.3555253088048627</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.452720158901133</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.308251239330156</v>
+        <v>2.290119047302569</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.782373546290387</v>
+        <v>-8.812593866336368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3307887339969589</v>
+        <v>-0.3428768620153511</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.427391071350398</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.326082466022705</v>
+        <v>2.307950273995118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.710240371002506</v>
+        <v>-8.740460691048487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2962017596431696</v>
+        <v>-0.3082898876615623</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.427391071350398</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.331816170261342</v>
+        <v>2.313683978233754</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.638873978392859</v>
+        <v>-8.669094298438839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2773924649931763</v>
+        <v>-0.2894805930115685</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.35602467874075</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.364898743433265</v>
+        <v>2.346766551405678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.545414944407634</v>
+        <v>-8.575635264453615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.249892332711994</v>
+        <v>-0.2619804607303862</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.35602467874075</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.355015262120357</v>
+        <v>2.33688307009277</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.534761762854203</v>
+        <v>-8.564982082900183</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.247465620589995</v>
+        <v>-0.2595537486083872</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.35602467874075</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.353180701620984</v>
+        <v>2.335048509593396</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.436854724177712</v>
+        <v>-8.467075044223693</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2086031200928598</v>
+        <v>-0.220691248111252</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.288038928880193</v>
+        <v>-1.318259248926172</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.393671836563857</v>
+        <v>2.37553964453627</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.412901183201754</v>
+        <v>-8.443121503247735</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1983531975569828</v>
+        <v>-0.210441325575375</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.264085387904236</v>
+        <v>-1.294305707950215</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.408712467294925</v>
+        <v>2.390580275267338</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.148841244878957</v>
+        <v>-8.179061564924938</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1059895383896161</v>
+        <v>-0.1180776664080083</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.00002544958144</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.553888114126851</v>
+        <v>2.535755922099263</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.441761621374119</v>
+        <v>-7.4719819414201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1740552773520183</v>
+        <v>0.1619671493336261</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.00002544958144</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.55110108046655</v>
+        <v>2.532968888438962</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.401577323007928</v>
+        <v>-7.431797643053909</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1904726205863359</v>
+        <v>0.1783844925679436</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9598411512152488</v>
+        <v>-0.9900614712612278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.575555283374106</v>
+        <v>2.557423091346518</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.238177452068566</v>
+        <v>-7.268397772114547</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2551993901828378</v>
+        <v>0.2431112621644456</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7964412802758863</v>
+        <v>-0.8266616003218653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.67296202715848</v>
+        <v>2.654829835130893</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.004696229838967</v>
+        <v>-7.034916549884948</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3565163079125293</v>
+        <v>0.3444281798941371</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5629600580462878</v>
+        <v>-0.5931803780922668</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.820975189334091</v>
+        <v>2.802842997306504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.855029838831452</v>
+        <v>-6.885250158877433</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4134906540025765</v>
+        <v>0.4014025259841842</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4700565668037519</v>
+        <v>-0.5002768868497308</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.873825073766654</v>
+        <v>2.855692881739067</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.722754365200566</v>
+        <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3676616294620856</v>
+        <v>0.3555735014436934</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3377810931728652</v>
+        <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.85445114395234</v>
+        <v>2.836318951924753</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.550893149635663</v>
+        <v>-6.581113469681644</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4392211763756833</v>
+        <v>0.427133048357291</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1659198776079623</v>
+        <v>-0.1961401976539413</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.960382933978919</v>
+        <v>2.942250741951332</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.465928482906344</v>
+        <v>-6.496148802952325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4861133842910697</v>
+        <v>0.4740252562726774</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.08095521087864277</v>
+        <v>-0.1111755309246217</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.024268075240169</v>
+        <v>3.006135883212582</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.571518472679449</v>
+        <v>-6.601738792725429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3159014587826094</v>
+        <v>0.3038133307642168</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1865452006517471</v>
+        <v>-0.2167655206977261</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832938151777088</v>
+        <v>2.814805959749501</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.503283888054021</v>
+        <v>-6.533504208100002</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3917396345098667</v>
+        <v>0.3796515064914745</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1681298777792111</v>
+        <v>-0.1983501978251901</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.892531687377696</v>
+        <v>2.874399495350109</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.355343846646422</v>
+        <v>-6.385564166692403</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3342948424344994</v>
+        <v>0.3222067144161072</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1478089618706536</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.788103428284423</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.302374324392433</v>
+        <v>-6.332594644438414</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3467686650826165</v>
+        <v>0.3346805370642243</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.09483943961666469</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.811171155383339</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.136586128432143</v>
+        <v>-6.166806448478123</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4061233313716395</v>
+        <v>0.3940352033532473</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.09483943961666469</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.804210543288245</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.103222921953374</v>
+        <v>-6.133443241999355</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4339309683442902</v>
+        <v>0.421842840325898</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.09483943961666469</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.818672897669388</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.994963784830852</v>
+        <v>-6.025184104876833</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4717667436524939</v>
+        <v>0.4596786156341017</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.09483943961666469</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.813205018128583</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.871672650013721</v>
+        <v>-5.901892970059702</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5185812915899231</v>
+        <v>0.5064931635715308</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02845169520046581</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.884677793029439</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.81897578288243</v>
+        <v>-5.849196102928411</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5473610166797651</v>
+        <v>0.5352728886613725</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.08114856233175699</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.923996891545539</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.575210340898986</v>
+        <v>-5.605430660944966</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6406479018201932</v>
+        <v>0.6285597738018009</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.08114856233175699</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.919777599892589</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.485434668522513</v>
+        <v>-5.515654988568494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6786824846907984</v>
+        <v>0.6665943566724057</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.142748007246067</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.958861580761191</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.235584274573439</v>
+        <v>-5.26580459461942</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.77136471725413</v>
+        <v>0.7592765892357378</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.142748007246067</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.951603655744893</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.059692182106007</v>
+        <v>-5.089912502151988</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8453206777617517</v>
+        <v>0.8332325497433595</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.142748007246067</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.955202779265542</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.888245719083543</v>
+        <v>-4.918466039129524</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9272267690252909</v>
+        <v>0.9151386410068985</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3141944702685301</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.071398163133574</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.808223431974422</v>
+        <v>-4.838443752020403</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9582561614852363</v>
+        <v>0.9461680334668439</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3942167573776511</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.118432013015343</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.744587689740488</v>
+        <v>-4.774808009786469</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9884052594331272</v>
+        <v>0.976317131414735</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4578524996115856</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.161308259410021</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.650890371524093</v>
+        <v>-4.681110691570074</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.007078445503481</v>
+        <v>0.9949903174850887</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4578524996115856</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.142502518193817</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.661392994589382</v>
+        <v>-4.691613314635362</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.004620472902243</v>
+        <v>0.9925323448838506</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4473498765462968</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.137944020979521</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.548906733920507</v>
+        <v>-4.579127053966488</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.053544291004613</v>
+        <v>1.04145616298622</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4473498765462968</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.141873334814341</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.531193047042642</v>
+        <v>-4.561413367088623</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.061308349673099</v>
+        <v>1.049220221654707</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4505312054432136</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.144460716069831</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.407718775729624</v>
+        <v>-4.437939095775604</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.1076961294183</v>
+        <v>1.095608001399907</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4505312054432136</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.141458787289825</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.187697977692613</v>
+        <v>-4.217918297738594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.197283485643718</v>
+        <v>1.185195357625326</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5917510505111938</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.227769731341227</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.054830288629335</v>
+        <v>-4.085050608675316</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.266324744070852</v>
+        <v>1.25423661605246</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5917510505111938</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.24366391414305</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.934657205264837</v>
+        <v>-3.964877525310817</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.315539821856954</v>
+        <v>1.303451693838561</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7119241338756928</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.316913608602052</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.79940384393486</v>
+        <v>-3.82962416398084</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.379729268950384</v>
+        <v>1.367641140931992</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8471774952056699</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.408153727961478</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.859278671292552</v>
+        <v>-3.889498991338533</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.341816829408733</v>
+        <v>1.329728701390341</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7873026678479778</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.358266322948288</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.739458440381715</v>
+        <v>-3.769678760427695</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.405034091007277</v>
+        <v>1.392945962988885</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7873026678479778</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.373555492182497</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.741928146843521</v>
+        <v>-3.772148466889501</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.311690407744996</v>
+        <v>1.299602279726604</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7848329613861715</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.279717867627855</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.81029833316753</v>
+        <v>-3.840518653213511</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.203604194700693</v>
+        <v>1.191516066682301</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7941086604223865</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.204545148534885</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.922170612793681</v>
+        <v>-3.952390932839662</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.149291991482124</v>
+        <v>1.137203863463732</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7941086604223865</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.194981857166777</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.977690688686271</v>
+        <v>-4.007911008732251</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.264114797817291</v>
+        <v>1.252026669798899</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7941086604223865</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.332012693858979</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.802216428893801</v>
+        <v>-3.832436748939782</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.338871733726066</v>
+        <v>1.326783605707674</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7941086604223865</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.336579925850767</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.794292054308887</v>
+        <v>-3.824512374354868</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.317783512321239</v>
+        <v>1.305695384302847</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7941086604223865</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.312321954611974</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.788013851739038</v>
+        <v>-3.818234171785019</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.248833106750629</v>
+        <v>1.236744978732236</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8003868629922355</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.244627189555333</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.728161232535315</v>
+        <v>-3.758381552581296</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.28294654086425</v>
+        <v>1.270858412845858</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8003868629922355</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.254799575987465</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.641917769508938</v>
+        <v>-3.672138089554918</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.312390196648662</v>
+        <v>1.300302068630269</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8003868629922355</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.249745846561325</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.687224588907918</v>
+        <v>-3.717444908953898</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.286043244333595</v>
+        <v>1.273955116315203</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7595766999830047</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.217035524200313</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.716257693610219</v>
+        <v>-3.7464780136562</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.274981875485776</v>
+        <v>1.262893747467384</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7595766999830047</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.217587397233414</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.62344721215936</v>
+        <v>-3.653667532205341</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.241378759957485</v>
+        <v>1.229290631939093</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.852387181433864</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.202546377995295</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.667836681488787</v>
+        <v>-3.698057001534768</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.225496448150315</v>
+        <v>1.213408320131923</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8079977121044364</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.177786172322239</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.78437828659413</v>
+        <v>-3.814598606640111</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.173955514619901</v>
+        <v>1.161867386601509</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6914561069990937</v>
+        <v>0.6612357869531147</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.102936917770757</v>
+        <v>3.08480472574317</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.824302381176702</v>
+        <v>-3.854522701222683</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.16347717261754</v>
+        <v>1.151389044599147</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6914561069990937</v>
+        <v>0.6612357869531147</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.108428213601424</v>
+        <v>3.090296021573837</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.852082779078055</v>
+        <v>-3.882303099124036</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.163862215225537</v>
+        <v>1.151774087207145</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6636757090977405</v>
+        <v>0.6334553890517616</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.103257176629151</v>
+        <v>3.085124984601564</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.970463451808194</v>
+        <v>-4.000683771854174</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9548656661341353</v>
+        <v>0.9427775381157431</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5964578569467643</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.901282185339219</v>
+        <v>2.883149993311632</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.079077530251524</v>
+        <v>-4.109297850297505</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.031569695476009</v>
+        <v>1.019481567457616</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5964578569467643</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.021431846058424</v>
+        <v>3.003299654030837</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.043668492003381</v>
+        <v>-4.073888812049362</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.060246336877589</v>
+        <v>1.048158208859197</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5964578569467643</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.035944872160747</v>
+        <v>3.01781268013316</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.00528482944523</v>
+        <v>-4.035505149491211</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.073019243243218</v>
+        <v>1.060931115224826</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6348415195049155</v>
+        <v>0.6046211994589366</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.056394511038007</v>
+        <v>3.038262319010419</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.828168499410064</v>
+        <v>-3.858388819456045</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.140594804102586</v>
+        <v>1.128506676084194</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6348415195049155</v>
+        <v>0.6046211994589366</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.053123539883309</v>
+        <v>3.034991347855721</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.87326074424361</v>
+        <v>-3.903481064289591</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.123241297931081</v>
+        <v>1.111153169912689</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5729454763355257</v>
+        <v>0.5427251562895468</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.016669305743588</v>
+        <v>2.998537113716001</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.693885323004842</v>
+        <v>-3.724105643050823</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.188778441733003</v>
+        <v>1.17669031371461</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7297222345062444</v>
+        <v>0.6995019144602654</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.104522335952434</v>
+        <v>3.086390143924846</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.738899536525448</v>
+        <v>-3.769119856571429</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.15158021165635</v>
+        <v>1.139492083637958</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6993733391916398</v>
+        <v>0.6691530191456608</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.067120454095261</v>
+        <v>3.048988262067673</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.005904046797884</v>
+        <v>-4.036124366843865</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.050469969886321</v>
+        <v>1.038381841867929</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5050103011486913</v>
+        <v>0.4747899811027123</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.956194193608437</v>
+        <v>2.93806200158085</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.107101828235057</v>
+        <v>-4.137322148281037</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.009194779207954</v>
+        <v>0.9971066511895614</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4366014876033721</v>
+        <v>0.4063811675573931</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.914352827377747</v>
+        <v>2.89622063535016</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.100590861620744</v>
+        <v>-4.130811181666725</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.009399127407995</v>
+        <v>0.9973109993896032</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4366014876033721</v>
+        <v>0.4063811675573931</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.911952788932064</v>
+        <v>2.893820596904476</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.081552733913447</v>
+        <v>-4.111773053959427</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.013539097699159</v>
+        <v>1.001450969680767</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3784178762721775</v>
+        <v>0.3481975562261985</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.873567341341592</v>
+        <v>2.855435149314005</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.134068536188267</v>
+        <v>-4.164288856234248</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.111827178423421</v>
+        <v>1.099739050405029</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3784178762721775</v>
+        <v>0.3481975562261985</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.992861742975783</v>
+        <v>2.974729550948195</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.147935297522185</v>
+        <v>-4.178155617568166</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.107113802875988</v>
+        <v>1.095025674857596</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3405599595383546</v>
+        <v>0.3103396394923756</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.970980321921622</v>
+        <v>2.952848129894035</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.10745230559984</v>
+        <v>-4.137672625645821</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.129315530041852</v>
+        <v>1.11722740202346</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3405599595383546</v>
+        <v>0.3103396394923756</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.976988852318548</v>
+        <v>2.958856660290961</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.959709335364838</v>
+        <v>-3.989929655410819</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.086362939413052</v>
+        <v>1.07427481139466</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5083673167732378</v>
+        <v>0.4781469967272587</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.975623487936677</v>
+        <v>2.95749129590909</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.043530556639536</v>
+        <v>-4.073750876685517</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.055628072434654</v>
+        <v>1.043539944416262</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5083673167732378</v>
+        <v>0.4781469967272587</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.978417109468158</v>
+        <v>2.960284917440571</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.037377850586751</v>
+        <v>-4.067598170632732</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.058751503247426</v>
+        <v>1.046663375229034</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.514520022826022</v>
+        <v>0.484299702780043</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.982771081491487</v>
+        <v>2.9646388894639</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.054187148737253</v>
+        <v>-4.084407468783234</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.051108260727336</v>
+        <v>1.039020132708943</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4977107246755204</v>
+        <v>0.4674904046295414</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.971765979341296</v>
+        <v>2.953633787313709</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.991889149961132</v>
+        <v>-4.022109470007112</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.142363014034605</v>
+        <v>1.130274886016213</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5430049889499624</v>
+        <v>0.5127846689039834</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.065278091702783</v>
+        <v>3.047145899675195</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.790098952295974</v>
+        <v>-3.820319272341954</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.025371094814795</v>
+        <v>1.013282966796403</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7410231811191168</v>
+        <v>0.7108028610731378</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.986381008718403</v>
+        <v>2.968248816690815</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.840985664982168</v>
+        <v>-3.871205985028149</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.075306642062493</v>
+        <v>1.063218514044101</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6901364684329223</v>
+        <v>0.6599161483869433</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.026139213428861</v>
+        <v>3.008007021401274</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.754374922332361</v>
+        <v>-3.784595242378341</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.124578675238459</v>
+        <v>1.112490547220067</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7687621996380806</v>
+        <v>0.7385418795921016</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.087942388267999</v>
+        <v>3.069810196240412</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.814584220337645</v>
+        <v>-3.844804540383626</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.099030936861017</v>
+        <v>1.086942808842625</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7085529016327961</v>
+        <v>0.6783325815868171</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.050352790289501</v>
+        <v>3.032220598261913</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.765397571653294</v>
+        <v>-3.795617891699274</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.117197214374686</v>
+        <v>1.105109086356294</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7085529016327961</v>
+        <v>0.6783325815868171</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.048844408329429</v>
+        <v>3.030712216301842</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.721024440014725</v>
+        <v>-3.751244760060706</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.13480933446555</v>
+        <v>1.122721206447158</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7529260332713646</v>
+        <v>0.7227057132253857</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.075331154748007</v>
+        <v>3.057198962720419</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.74350479087361</v>
+        <v>-3.773725110919591</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.120210988260587</v>
+        <v>1.108122860242194</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7529260332713646</v>
+        <v>0.7227057132253857</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.069724948886597</v>
+        <v>3.05159275685901</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.695849060312555</v>
+        <v>-3.726069380358535</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.145655037512813</v>
+        <v>1.133566909494421</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8005817638324203</v>
+        <v>0.7703614437864413</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.104700144251035</v>
+        <v>3.086567952223448</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.5953309018138</v>
+        <v>-3.62555122185978</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.19075467428704</v>
+        <v>1.178666546268648</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9010999223311749</v>
+        <v>0.8708796022851959</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.169903412725013</v>
+        <v>3.151771220697425</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.579425572381448</v>
+        <v>-3.609645892427428</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.183871478535853</v>
+        <v>1.171783350517461</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8219872616219359</v>
+        <v>0.791766941575957</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.109190488775341</v>
+        <v>3.091058296747754</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.53458717077305</v>
+        <v>-3.557674094709774</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.205904541789841</v>
+        <v>1.196669772215151</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8265306945668054</v>
+        <v>0.8655544368627434</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.116014251152892</v>
+        <v>3.139428496530455</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.554085627015058</v>
+        <v>-3.577172550951782</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.202266098924116</v>
+        <v>1.193031329349426</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7784460532869011</v>
+        <v>0.8174697955828391</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.091324406016027</v>
+        <v>3.11473865139359</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.509882789929157</v>
+        <v>-3.532969713865882</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.225826836286313</v>
+        <v>1.216592066711623</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8226488903728015</v>
+        <v>0.8616726326687395</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.123725710795405</v>
+        <v>3.147139956172968</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.517442455766204</v>
+        <v>-3.540529379702928</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.221212970420742</v>
+        <v>1.211978200846052</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8774522943826208</v>
+        <v>0.9164760366785588</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.155017753670544</v>
+        <v>3.178431999048106</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.359151038226932</v>
+        <v>-3.382237962163656</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.335777302619491</v>
+        <v>1.326542533044801</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8774522943826208</v>
+        <v>0.9164760366785588</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.206265518853583</v>
+        <v>3.229679764231146</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.151509034592456</v>
+        <v>-3.17459595852918</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.417274808667534</v>
+        <v>1.408040039092844</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.085094298017097</v>
+        <v>1.124118040313035</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.329291425628522</v>
+        <v>3.352705671006085</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.100476941869928</v>
+        <v>-3.123563865806652</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.432635873994815</v>
+        <v>1.423401104420126</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.136126390739625</v>
+        <v>1.175150133035563</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.354858909500309</v>
+        <v>3.378273154877871</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.035252760742722</v>
+        <v>-3.058339684679447</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.475912950538403</v>
+        <v>1.466678180963713</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.201350571866831</v>
+        <v>1.240374314162769</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.411180822269337</v>
+        <v>3.4345950676469</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.997825740671588</v>
+        <v>-3.020912664608313</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.486844730866137</v>
+        <v>1.477609961291447</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.206602109896012</v>
+        <v>1.24562585219195</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.410292717386127</v>
+        <v>3.43370696276369</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.017937396706297</v>
+        <v>-3.041024320643021</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.480056860783493</v>
+        <v>1.470822091208804</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.217629454893432</v>
+        <v>1.25665319718937</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.418165916715818</v>
+        <v>3.441580162093381</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.989524133606413</v>
+        <v>-3.012611057543138</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.651979937044658</v>
+        <v>1.642745167469968</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.158653892147003</v>
+        <v>1.197677634442941</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.543338350089172</v>
+        <v>3.566752595466735</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.9147418725814</v>
+        <v>-2.937828796518125</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.80200575067248</v>
+        <v>1.79277098109779</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.233436153172015</v>
+        <v>1.272459895467953</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.708320615921997</v>
+        <v>3.73173486129956</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.888657788317592</v>
+        <v>-2.911744712254317</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.804147360391862</v>
+        <v>1.794912590817172</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.233436153172015</v>
+        <v>1.272459895467953</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.700028591935856</v>
+        <v>3.723442837313419</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.800779875208472</v>
+        <v>-2.823866799145196</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.83749172121929</v>
+        <v>1.8282569516446</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.349361795595367</v>
+        <v>1.388385537891304</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.767777172973646</v>
+        <v>3.791191418351209</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.791887413815188</v>
+        <v>-2.831817185530809</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.858603111503395</v>
+        <v>1.842631202817147</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.349361795595367</v>
+        <v>1.388385537891304</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.785331578700437</v>
+        <v>3.808745824078</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.960363530785066</v>
+        <v>-3.000293302500686</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.783067712120027</v>
+        <v>1.767095803433779</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.321413959878786</v>
+        <v>1.360437702174724</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.760417924675073</v>
+        <v>3.783832170052635</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.514107338155626</v>
+        <v>-2.554037109871246</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.942839886359665</v>
+        <v>1.926867977673417</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.226695290209153</v>
+        <v>1.265719032505091</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.684856420061155</v>
+        <v>3.708270665438718</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.491386234472474</v>
+        <v>-2.531316006188094</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.942592350329831</v>
+        <v>1.926620441643583</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.226695290209153</v>
+        <v>1.265719032505091</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.67552044255806</v>
+        <v>3.698934687935622</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.620588047766516</v>
+        <v>-2.660517819482136</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.049817750863383</v>
+        <v>2.033845842177135</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.097493476915111</v>
+        <v>1.136517219211049</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.756905480432803</v>
+        <v>3.780319725810366</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.646462446240542</v>
+        <v>-2.686392217956162</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.076545813967419</v>
+        <v>2.060573905281171</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.142405085626852</v>
+        <v>1.18142882792279</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.820930268153495</v>
+        <v>3.844344513531057</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.639407756025368</v>
+        <v>-2.679337527740989</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.076043046043034</v>
+        <v>2.060071137356785</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.149459775842026</v>
+        <v>1.188483518137964</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.821838438272144</v>
+        <v>3.845252683649707</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.61245653169888</v>
+        <v>-2.652386303414501</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.09682968941837</v>
+        <v>2.080857780732122</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.164340121869745</v>
+        <v>1.203363864165683</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.840772799533517</v>
+        <v>3.86418704491108</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.634000759529668</v>
+        <v>-2.673930531245288</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.272315130431015</v>
+        <v>2.256343221744767</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.164340121869745</v>
+        <v>1.203363864165683</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.024875931678476</v>
+        <v>4.04829017705604</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.65640887733454</v>
+        <v>-2.69633864905016</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.25546857821206</v>
+        <v>2.239496669525812</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.164340121869745</v>
+        <v>1.203363864165683</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.016992626581469</v>
+        <v>4.040406871959033</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.68463311291214</v>
+        <v>-2.72456288462776</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.246232883530657</v>
+        <v>2.230260974844409</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.182316874321053</v>
+        <v>1.221340616616991</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.029832677601893</v>
+        <v>4.053246922979455</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.69407403880067</v>
+        <v>-2.73400381051629</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.298710230897092</v>
+        <v>2.282738322210844</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.304743991864445</v>
+        <v>1.343767734160383</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.159542665849775</v>
+        <v>4.182956911227337</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.782950669969144</v>
+        <v>-2.822880441684764</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.266050672975004</v>
+        <v>2.250078764288755</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.215867360695971</v>
+        <v>1.254891102991909</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.109107781693991</v>
+        <v>4.132522027071554</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.85928064757005</v>
+        <v>-2.89921041928567</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.233630494828416</v>
+        <v>2.217658586142168</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.215867360695971</v>
+        <v>1.254891102991909</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.107219594587766</v>
+        <v>4.130633839965329</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.952944592247591</v>
+        <v>-2.992874363963211</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.190985146560262</v>
+        <v>2.175013237874014</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.12220341601843</v>
+        <v>1.161227158314368</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.045841457384103</v>
+        <v>4.069255702761667</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.114513017774846</v>
+        <v>-3.154442789490466</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.124791786559512</v>
+        <v>2.108819877873264</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9954204922205503</v>
+        <v>1.034444234516488</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.968205713315529</v>
+        <v>3.991619958693091</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.222813679644966</v>
+        <v>-3.262743451360586</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.094544928677383</v>
+        <v>2.078573019991135</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9954204922205503</v>
+        <v>1.034444234516488</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.981279120181447</v>
+        <v>4.004693365559009</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.24061765136571</v>
+        <v>-3.28054742308133</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.079428536772025</v>
+        <v>2.063456628085778</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9248858693153492</v>
+        <v>0.9639096116112871</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.930963543221266</v>
+        <v>3.954377788598829</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.268518438475183</v>
+        <v>-3.308448210190803</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.066792263055238</v>
+        <v>2.05082035436899</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8902889451724144</v>
+        <v>0.9293126874683523</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.908729429862507</v>
+        <v>3.93214367524007</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.391044541178077</v>
+        <v>-3.430974312893697</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.014546265951279</v>
+        <v>1.998574357265031</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7677628424695205</v>
+        <v>0.8067865847654584</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.83197821221797</v>
+        <v>3.855392457595533</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.621559037363665</v>
+        <v>-3.661488809079286</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.989046427067548</v>
+        <v>1.973074518381299</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5372483462839318</v>
+        <v>0.5762720885798697</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.76037547409712</v>
+        <v>3.783789719474683</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.970304122588109</v>
+        <v>-4.010233894303729</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.989860111979617</v>
+        <v>1.973888203293369</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.428500392365034</v>
+        <v>0.4675241346609719</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.835438420747629</v>
+        <v>3.858852666125191</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.12429054036425</v>
+        <v>-4.16422031207987</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.997245814014801</v>
+        <v>1.981273905328552</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.428500392365034</v>
+        <v>0.4675241346609719</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.904418689893268</v>
+        <v>3.927832935270831</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.073768636536584</v>
+        <v>-4.113698408252204</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.003505777665988</v>
+        <v>1.98753386897974</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.428500392365034</v>
+        <v>0.4675241346609719</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.890469892013389</v>
+        <v>3.913884137390952</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.326243790544308</v>
+        <v>-4.366173562259928</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.914386205118312</v>
+        <v>1.898414296432064</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.428500392365034</v>
+        <v>0.4675241346609719</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.902340381068803</v>
+        <v>3.925754626446366</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.61913954702372</v>
+        <v>-4.65906931873934</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.798438437045491</v>
+        <v>1.782466528359243</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.428500392365034</v>
+        <v>0.4675241346609719</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.903550915587747</v>
+        <v>3.92696516096531</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.805803675158528</v>
+        <v>-4.845733446874148</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.727894528018889</v>
+        <v>1.711922619332641</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4017614215404741</v>
+        <v>0.440785163836412</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.891629275320333</v>
+        <v>3.915043520697895</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.95182436207249</v>
+        <v>-4.991754133788111</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.664564105989494</v>
+        <v>1.648592197303246</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3926783297466171</v>
+        <v>0.431702072042555</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.881257272980208</v>
+        <v>3.90467151835777</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.043538371182075</v>
+        <v>-5.083468142897695</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.790082559044704</v>
+        <v>1.774110650358456</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3926783297466171</v>
+        <v>0.431702072042555</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.043461329679252</v>
+        <v>4.066875575056815</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.075190030242045</v>
+        <v>-5.115119801957665</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.77226853338453</v>
+        <v>1.756296624698282</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3875098725021769</v>
+        <v>0.4265336147981148</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.035206893296402</v>
+        <v>4.058621138673964</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.157124848510928</v>
+        <v>-5.197054620226548</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.749724023645468</v>
+        <v>1.73375211495922</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3775751269150968</v>
+        <v>0.4165988692110346</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.039475463512645</v>
+        <v>4.062889708890208</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.259100970759335</v>
+        <v>-5.299030742474955</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.717859213202008</v>
+        <v>1.70188730451576</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2755990046666892</v>
+        <v>0.314622746962627</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.987215428619503</v>
+        <v>4.010629673997066</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.149094687282114</v>
+        <v>-5.189024458997734</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.754014613837072</v>
+        <v>1.738042705150824</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2988035765839644</v>
+        <v>0.3378273188799022</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.993291059014044</v>
+        <v>4.016705304391606</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.006035111541188</v>
+        <v>-5.045964883256808</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.815488454855416</v>
+        <v>1.799516546169168</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3068170031739437</v>
+        <v>0.3458407454698815</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.002349125690006</v>
+        <v>4.025763371067568</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.70458838606935</v>
+        <v>-4.74451815778497</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.943328027926688</v>
+        <v>1.927356119240439</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6082637286457809</v>
+        <v>0.6472874709417188</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.190478043855643</v>
+        <v>4.213892289233207</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.729178630304534</v>
+        <v>-4.769108402020154</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.934463107985325</v>
+        <v>1.918491199299076</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6082637286457809</v>
+        <v>0.6472874709417188</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.191449221608354</v>
+        <v>4.214863466985917</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.678140254298014</v>
+        <v>-4.718070026013634</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.955721362767688</v>
+        <v>1.93974945408144</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6082637286457809</v>
+        <v>0.6472874709417188</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.19229212598811</v>
+        <v>4.215706371365672</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.637000959431383</v>
+        <v>-4.676930731147003</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.991215179588486</v>
+        <v>1.975243270902238</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6494030235124117</v>
+        <v>0.6884267658083496</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.236013801782233</v>
+        <v>4.259428047159797</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.540366047412743</v>
+        <v>-4.580295819128363</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.846053140519877</v>
+        <v>1.830081231833629</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7460379355310517</v>
+        <v>0.7850616778269895</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.110178745117352</v>
+        <v>4.133592990494915</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.670946781943585</v>
+        <v>-4.710876553659205</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.797322890781504</v>
+        <v>1.781350982095256</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6154572010002092</v>
+        <v>0.654480943296147</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.035332348472811</v>
+        <v>4.058746593850374</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.506450447752623</v>
+        <v>-4.546380219468244</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.847548243533971</v>
+        <v>1.831576334847723</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7799535351911711</v>
+        <v>0.8189772774871089</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.11845696806347</v>
+        <v>4.141871213441033</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.429351846210751</v>
+        <v>-4.469281617926371</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.87757539458715</v>
+        <v>1.861603485900902</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7799535351911711</v>
+        <v>0.8189772774871089</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.1176446784999</v>
+        <v>4.141058923877463</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.43973704110064</v>
+        <v>-4.47966681281626</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.883290095756266</v>
+        <v>1.867318187070018</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7695683403012817</v>
+        <v>0.8085920825972196</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.121282340691039</v>
+        <v>4.144696586068601</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.458325199822865</v>
+        <v>-4.498254971538485</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.946691838043802</v>
+        <v>1.930719929357553</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7509801815790564</v>
+        <v>0.7900039238749943</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.180966451234129</v>
+        <v>4.204380696611691</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.458623746518901</v>
+        <v>-4.498553518234521</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.943441430183686</v>
+        <v>1.927469521497438</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7506816348830205</v>
+        <v>0.7897053771789584</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.177656334034806</v>
+        <v>4.201070579412368</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.357800612828473</v>
+        <v>-4.397730384544094</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.988301578599248</v>
+        <v>1.972329669913</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7631458503673744</v>
+        <v>0.8021695926633122</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.18966575826481</v>
+        <v>4.213080003642372</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.167019252076066</v>
+        <v>-4.206949023791687</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.064743376378754</v>
+        <v>2.048771467692506</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9539272111197817</v>
+        <v>0.9929509534157197</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.304263828194798</v>
+        <v>4.32767807357236</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.060055894226645</v>
+        <v>-4.099985665942265</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.087365565256119</v>
+        <v>2.071393656569871</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.012391819079583</v>
+        <v>1.051415561375521</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.319179438708275</v>
+        <v>4.342593684085838</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.004725306324882</v>
+        <v>-4.044655078040503</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.144464737028883</v>
+        <v>2.128492828342635</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.067722406981345</v>
+        <v>1.106746149277283</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.38734472806139</v>
+        <v>4.410758973438953</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.99267117941192</v>
+        <v>-4.03260095112754</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.142972955695505</v>
+        <v>2.127001047009258</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.079776533894308</v>
+        <v>1.118800276190246</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.388263772110606</v>
+        <v>4.411678017488168</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.033826298980141</v>
+        <v>-4.073756070695761</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.128391538052353</v>
+        <v>2.112419629366105</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.038621414326087</v>
+        <v>1.077645156622025</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.365451330553809</v>
+        <v>4.388865575931372</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.965777736288612</v>
+        <v>-4.005707508004231</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.168461989006847</v>
+        <v>2.152490080320599</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.106669977017617</v>
+        <v>1.145693719313555</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.41913149404661</v>
+        <v>4.442545739424173</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.197378129458112</v>
+        <v>-4.237307901173732</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.096024501912641</v>
+        <v>2.080052593226394</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.106669977017617</v>
+        <v>1.145693719313555</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.439334164220204</v>
+        <v>4.462748409597767</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.247429674987332</v>
+        <v>-4.287359446702951</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.059610119767835</v>
+        <v>2.043638211081588</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.106669977017617</v>
+        <v>1.145693719313555</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.422940400287086</v>
+        <v>4.446354645664648</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.422536507563777</v>
+        <v>-4.462466279279395</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.949819300330724</v>
+        <v>1.933847391644477</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.106669977017617</v>
+        <v>1.145693719313555</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.383192313880553</v>
+        <v>4.406606559258115</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.226436354133254</v>
+        <v>-4.266366125848872</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.035281980699873</v>
+        <v>2.019310072013626</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.30277013044814</v>
+        <v>1.341793872744078</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.507875024935807</v>
+        <v>4.531289270313369</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.073410962019969</v>
+        <v>-4.113340733735588</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.195663137118092</v>
+        <v>2.179691228431844</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.455795522561424</v>
+        <v>1.494819264857362</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.698861259776681</v>
+        <v>4.722275505154244</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.10171827589324</v>
+        <v>-4.141648047608858</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.371806436477076</v>
+        <v>2.355834527790829</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.455795522561424</v>
+        <v>1.494819264857362</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.886327484684974</v>
+        <v>4.909741730062536</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.268311501006762</v>
+        <v>-4.30824127272238</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.274572097785749</v>
+        <v>2.258600189099502</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.289202297447902</v>
+        <v>1.328226039743839</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.755774500970943</v>
+        <v>4.779188746348505</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.245275707645196</v>
+        <v>-4.285205479360815</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.287462817792093</v>
+        <v>2.271490909105846</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.289202297447902</v>
+        <v>1.328226039743839</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.75945090363266</v>
+        <v>4.782865149010223</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.2160297271895</v>
+        <v>-4.255959498905118</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.296779265097867</v>
+        <v>2.28080735641162</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.289202297447902</v>
+        <v>1.328226039743839</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.757068958756156</v>
+        <v>4.780483204133718</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.322955275067351</v>
+        <v>-4.362885046782969</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.251302285104362</v>
+        <v>2.235330376418115</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.18227674957005</v>
+        <v>1.221300491865988</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.69020686918708</v>
+        <v>4.713621114564642</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.467973833574599</v>
+        <v>-4.507903605290218</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.194723663844696</v>
+        <v>2.178751755158449</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.037258191062802</v>
+        <v>1.07628193335874</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.604624536225965</v>
+        <v>4.628038781603528</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.586315599359317</v>
+        <v>-4.626245371074935</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.247318196788562</v>
+        <v>2.231346288102315</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.047944229625692</v>
+        <v>1.08696797192163</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.710967398621452</v>
+        <v>4.734381643999015</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.637726021680025</v>
+        <v>-4.677655793395643</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.224539724986218</v>
+        <v>2.208567816299971</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.047944229625692</v>
+        <v>1.08696797192163</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.70875309574739</v>
+        <v>4.732167341124954</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.717145472887776</v>
+        <v>-4.757075244603395</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.192675072577407</v>
+        <v>2.17670316389116</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.047944229625692</v>
+        <v>1.08696797192163</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.708656223821681</v>
+        <v>4.732070469199243</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.812608470804994</v>
+        <v>-4.852538242520612</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.154483766968563</v>
+        <v>2.138511858282316</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.047944229625692</v>
+        <v>1.08696797192163</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.708650117379724</v>
+        <v>4.732064362757287</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.748232559954279</v>
+        <v>-4.788162331669898</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.17833052787146</v>
+        <v>2.162358619185213</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.112320140476407</v>
+        <v>1.151343882772345</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.745372060452763</v>
+        <v>4.768786305830326</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.803601722086473</v>
+        <v>-4.843531493802091</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.161916680766309</v>
+        <v>2.145944772080062</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.112320140476407</v>
+        <v>1.151343882772345</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.75110587820049</v>
+        <v>4.774520123578053</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.8490395019173</v>
+        <v>-4.888969273632918</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.14327993217691</v>
+        <v>2.127308023490663</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.069475149798248</v>
+        <v>1.108498892094185</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.724937247136526</v>
+        <v>4.748351492514089</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.760832667769722</v>
+        <v>-4.80076243948534</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.19843705868626</v>
+        <v>2.182465150000013</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.069475149798248</v>
+        <v>1.108498892094185</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.744811639986845</v>
+        <v>4.768225885364408</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.654797672564412</v>
+        <v>-4.694727444280031</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.224551757293112</v>
+        <v>2.208579848606865</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.069475149798248</v>
+        <v>1.108498892094185</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.728512340511573</v>
+        <v>4.751926585889136</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.471586009431317</v>
+        <v>-4.511515781146936</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.300267372010396</v>
+        <v>2.284295463324148</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.069475149798248</v>
+        <v>1.108498892094185</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.730943289975619</v>
+        <v>4.754357535353181</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.399864562417466</v>
+        <v>-4.439794334133085</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.294747136663825</v>
+        <v>2.278775227977578</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.141196596812098</v>
+        <v>1.180220339108036</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.739767344031819</v>
+        <v>4.763181589409381</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.37749153680976</v>
+        <v>-4.417421308525379</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.25061209282808</v>
+        <v>2.234640184141832</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.152452347925</v>
+        <v>1.191476090220938</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.693436540620731</v>
+        <v>4.716850785998294</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.410507832720505</v>
+        <v>-4.450437604436123</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.422603779349137</v>
+        <v>2.40663187066289</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.083014971258248</v>
+        <v>1.122038713554186</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.836972319506035</v>
+        <v>4.860386564883599</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.398980197070896</v>
+        <v>-4.438909968786515</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.41913605943723</v>
+        <v>2.403164150750983</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.142015629459611</v>
+        <v>1.181039371755549</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.864293940255102</v>
+        <v>4.887708185632665</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.496321698413265</v>
+        <v>-4.536251470128883</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.383867571422071</v>
+        <v>2.367895662735823</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.097595447294122</v>
+        <v>1.13661918959006</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.841309943477598</v>
+        <v>4.864724188855161</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.582177727753232</v>
+        <v>-4.62210749946885</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.350776241878922</v>
+        <v>2.334804333192675</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.055219378067987</v>
+        <v>1.094243120363925</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.817135384134755</v>
+        <v>4.840549629512318</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.591014525169351</v>
+        <v>-4.630944296884969</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.329660724732976</v>
+        <v>2.313688816046729</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.047777205426637</v>
+        <v>1.086800947722574</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.795089282370446</v>
+        <v>4.818503527748009</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.68239708773481</v>
+        <v>-4.722326859450428</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.303272210751842</v>
+        <v>2.287300302065595</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9563946428611783</v>
+        <v>0.9954183851571161</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.75042425587622</v>
+        <v>4.773838501253784</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.670690369747803</v>
+        <v>-4.710620141463422</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.410083155770913</v>
+        <v>2.394111247084666</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9681013608481847</v>
+        <v>1.007125103144122</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.859576544492693</v>
+        <v>4.882990789870256</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.571026865664141</v>
+        <v>-4.610956637379759</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.452980896135783</v>
+        <v>2.437008987449536</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.031288444051871</v>
+        <v>1.070312186347809</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.900521133146309</v>
+        <v>4.923935378523872</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.581342963830493</v>
+        <v>-4.621272735546111</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.6617592901473</v>
+        <v>2.645787381461053</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.031288444051871</v>
+        <v>1.070312186347809</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.113425966424368</v>
+        <v>5.13684021180193</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.58124899581312</v>
+        <v>-4.621178767528739</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.660975544266339</v>
+        <v>2.645003635580092</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.112826550144848</v>
+        <v>5.136240795522411</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.588467820012965</v>
+        <v>-4.628397591728583</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.652320000530755</v>
+        <v>2.636348091844508</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.107058536089202</v>
+        <v>5.130472781466764</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.587519396894926</v>
+        <v>-4.627449168610545</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.65269936977797</v>
+        <v>2.636727461091723</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.107058536089202</v>
+        <v>5.130472781466764</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.74458785515055</v>
+        <v>-4.784517626866169</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.602599594456813</v>
+        <v>2.586627685770566</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.119786144070294</v>
+        <v>5.143200389447856</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.738595608361739</v>
+        <v>-4.785915302588463</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.606942491596725</v>
+        <v>2.588014613906036</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.121732142494682</v>
+        <v>5.145146387872244</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.892247629344292</v>
+        <v>3.842115421351128</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.67479972748824</v>
+        <v>4.59414880563738</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.738595608361739</v>
+        <v>-4.785915302588463</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.606942491596725</v>
+        <v>2.588014613906036</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.031658305399189</v>
+        <v>1.070682047695127</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.667863524474607</v>
+        <v>4.587212602623747</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105.3%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.8%</t>
+          <t>138.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>423.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.2%</t>
+          <t>-623.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.4%</t>
+          <t>-111.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.0%</t>
+          <t>-332.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-116.9%</t>
+          <t>-104.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>112.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.050337425679063</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.4585373914417672</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.583096209218886</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.212096277612274</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.176374219047352</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.5062583801599683</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.557844586409143</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.229940979927234</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.119302447151421</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.4794393357151954</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.557844586409143</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.233931315613635</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.260974288875541</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.5375832993035852</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.557844586409143</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.232456088714893</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.211383444450707</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.5026935513687789</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.508253741984309</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.277264005534666</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.06246510997885</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.4561773512267195</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.477004151249136</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.282962626329087</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-8.83661995725944</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.3562602171027467</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.435077475661973</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.317697704717594</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.712041300921848</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.3052896100116511</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.435077475661973</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.318836849273652</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.687004619353338</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.2926411632221395</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.409748388111237</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.336668075966202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.614871444065457</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.2580541888683503</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.409748388111237</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.342401780204838</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.54350505145581</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.2392448942183565</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.338381995501589</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.375484353376762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.450046017470585</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.2117447619371746</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.338381995501589</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.365600872063854</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.439392835917154</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.2093180498151757</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.338381995501589</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.36376631156448</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.341485797240663</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.17045554931804</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.270396245641033</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.404257446507353</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.317532256264705</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.1602056267821634</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.246442704665075</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.419298077238421</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.053472317941909</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.06784196761479677</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9823827663422788</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.564473724070347</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.34639269443707</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.2122028481268377</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9823827663422788</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.561686690410046</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.30620839607088</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.2286201913611552</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.9421984679760881</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.586140893317602</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.142808525131517</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.2933469609576571</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.7787985970367256</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.683547637101976</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-6.909327302901919</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.3946638786873491</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.5453173748071271</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.831560799277588</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-6.759660911894404</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.4516382247773958</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.4524138835645911</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.88441068371015</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.627385438263517</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.4058092002369049</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.3201384099337045</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.865036753895837</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581113469681644</v>
+        <v>-6.455524222698615</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.427133048357291</v>
+        <v>0.4773687471505026</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.1482771943688016</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.970968543922415</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.496148802952325</v>
+        <v>-6.370559555969296</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4740252562726774</v>
+        <v>0.524260955065889</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.06331252763948203</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>3.034853685183666</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.601738792725429</v>
+        <v>-6.4761495457424</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3038133307642168</v>
+        <v>0.3540490295574288</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.1689025174125864</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.843523761720585</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.533504208100002</v>
+        <v>-6.407914961116973</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3796515064914745</v>
+        <v>0.429887205284686</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.1504871945400504</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.903117297321193</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.385564166692403</v>
+        <v>-6.259974919709373</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3222067144161072</v>
+        <v>0.3724424132093187</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1301662786314928</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.79868903822792</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.332594644438414</v>
+        <v>-6.207005397455385</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3346805370642243</v>
+        <v>0.3849162358574358</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.07719675637750395</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.821756765326835</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.166806448478123</v>
+        <v>-6.041217201495094</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3940352033532473</v>
+        <v>0.4442709021464593</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.07719675637750395</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.814796153231742</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.133443241999355</v>
+        <v>-6.007853995016325</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.421842840325898</v>
+        <v>0.4720785391191096</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.07719675637750395</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.829258507612885</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.025184104876833</v>
+        <v>-5.899594857893804</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4596786156341017</v>
+        <v>0.5099143144273133</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.07719675637750395</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.82379062807208</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.901892970059702</v>
+        <v>-5.776303723076673</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5064931635715308</v>
+        <v>0.5567288623647428</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.04609437843962655</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.895263402972935</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849196102928411</v>
+        <v>-5.723606855945381</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5352728886613725</v>
+        <v>0.5855085874545845</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.09879124557091773</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.934582501489035</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605430660944966</v>
+        <v>-5.479841413961937</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6285597738018009</v>
+        <v>0.6787954725950129</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.09879124557091773</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.930363209836086</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.515654988568494</v>
+        <v>-5.390065741585465</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6665943566724057</v>
+        <v>0.7168300554656177</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1603906904852277</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.969447190704688</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.26580459461942</v>
+        <v>-5.14021534763639</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7592765892357378</v>
+        <v>0.8095122880289498</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1603906904852277</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.96218926568839</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.089912502151988</v>
+        <v>-4.964323255168958</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8332325497433595</v>
+        <v>0.8834682485365712</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1603906904852277</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.965788389209039</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.918466039129524</v>
+        <v>-4.792876792146495</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9151386410068985</v>
+        <v>0.9653743398001102</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.3318371535076909</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.08198377307707</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838443752020403</v>
+        <v>-4.712854505037374</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9461680334668439</v>
+        <v>0.9964037322600556</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.4118594406168118</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.12901762295884</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774808009786469</v>
+        <v>-4.649218762803439</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.976317131414735</v>
+        <v>1.026552830207947</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4754951828507464</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.171893869353518</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.681110691570074</v>
+        <v>-4.555521444587044</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9949903174850887</v>
+        <v>1.0452260162783</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4754951828507464</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.153088128137314</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.691613314635362</v>
+        <v>-4.566024067652333</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9925323448838506</v>
+        <v>1.042768043677062</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4649925597854575</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.148529630923017</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.579127053966488</v>
+        <v>-4.453537806983459</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145616298622</v>
+        <v>1.091691861779432</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4649925597854575</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.152458944757838</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.561413367088623</v>
+        <v>-4.435824120105593</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.049220221654707</v>
+        <v>1.099455920447918</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4681738886823743</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.155046326013328</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437939095775604</v>
+        <v>-4.312349848792575</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.095608001399907</v>
+        <v>1.145843700193119</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4681738886823743</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.152044397233321</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217918297738594</v>
+        <v>-4.092329050755565</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.185195357625326</v>
+        <v>1.235431056418538</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.6093937337503545</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.238355341284723</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085050608675316</v>
+        <v>-3.959461361692286</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.25423661605246</v>
+        <v>1.304472314845672</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.6093937337503545</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.254249524086547</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964877525310817</v>
+        <v>-3.839288278327787</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.303451693838561</v>
+        <v>1.353687392631774</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.7295668171148535</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.327499218545548</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.82962416398084</v>
+        <v>-3.70403491699781</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.367641140931992</v>
+        <v>1.417876839725204</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.8648201784448306</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.418739337904974</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889498991338533</v>
+        <v>-3.763909744355503</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.329728701390341</v>
+        <v>1.379964400183553</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.8049453510871385</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.368851932891785</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769678760427695</v>
+        <v>-3.644089513444665</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.392945962988885</v>
+        <v>1.443181661782097</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.8049453510871385</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.384141102125994</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772148466889501</v>
+        <v>-3.646559219906471</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.299602279726604</v>
+        <v>1.349837978519816</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.8024756446253323</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.290303477571351</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840518653213511</v>
+        <v>-3.714929406230481</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191516066682301</v>
+        <v>1.241751765475513</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.8117513436615472</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.215130758478382</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.952390932839662</v>
+        <v>-3.826801685856632</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.137203863463732</v>
+        <v>1.187439562256944</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.8117513436615472</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.205567467110273</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.007911008732251</v>
+        <v>-3.882321761749221</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.252026669798899</v>
+        <v>1.302262368592111</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.8117513436615472</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.342598303802475</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.832436748939782</v>
+        <v>-3.706847501956752</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.326783605707674</v>
+        <v>1.377019304500886</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.8117513436615472</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.347165535794263</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.824512374354868</v>
+        <v>-3.698923127371838</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.305695384302847</v>
+        <v>1.355931083096059</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.8117513436615472</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.32290756455547</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.818234171785019</v>
+        <v>-3.692644924801989</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.236744978732236</v>
+        <v>1.286980677525448</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8180295462313962</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.255212799498829</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.758381552581296</v>
+        <v>-3.632792305598266</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.270858412845858</v>
+        <v>1.32109411163907</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8180295462313962</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.265385185930961</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.672138089554918</v>
+        <v>-3.546548842571888</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.300302068630269</v>
+        <v>1.350537767423481</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.8180295462313962</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.260331456504822</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.717444908953898</v>
+        <v>-3.591855661970868</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.273955116315203</v>
+        <v>1.324190815108415</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7772193832221654</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.227621134143809</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7464780136562</v>
+        <v>-3.62088876667317</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.262893747467384</v>
+        <v>1.313129446260596</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7772193832221654</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.228173007176911</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.653667532205341</v>
+        <v>-3.52807828522231</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.229290631939093</v>
+        <v>1.279526330732305</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.8700298646730248</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.213131987938792</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.698057001534768</v>
+        <v>-3.572467754551738</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.213408320131923</v>
+        <v>1.263644018925135</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.8256403953435971</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.188371782265736</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.814598606640111</v>
+        <v>-3.689009359657081</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.161867386601509</v>
+        <v>1.212103085394721</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6612357869531147</v>
+        <v>0.7090987902382544</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.08480472574317</v>
+        <v>3.113522527714253</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.854522701222683</v>
+        <v>-3.728933454239653</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.151389044599147</v>
+        <v>1.201624743392359</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6612357869531147</v>
+        <v>0.7090987902382544</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.090296021573837</v>
+        <v>3.119013823544921</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.882303099124036</v>
+        <v>-3.756713852141006</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.151774087207145</v>
+        <v>1.202009786000357</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6334553890517616</v>
+        <v>0.6813183923369013</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.085124984601564</v>
+        <v>3.113842786572648</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.000683771854174</v>
+        <v>-3.875094524871144</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9427775381157431</v>
+        <v>0.993013236908955</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.6141005401859251</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.883149993311632</v>
+        <v>2.911867795282715</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.109297850297505</v>
+        <v>-3.983708603314475</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.019481567457616</v>
+        <v>1.069717266250828</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.6141005401859251</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.003299654030837</v>
+        <v>3.032017456001921</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.073888812049362</v>
+        <v>-3.948299565066332</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.048158208859197</v>
+        <v>1.098393907652409</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5662375369007854</v>
+        <v>0.6141005401859251</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.01781268013316</v>
+        <v>3.046530482104244</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.035505149491211</v>
+        <v>-3.909915902508181</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.060931115224826</v>
+        <v>1.111166814018038</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6046211994589366</v>
+        <v>0.6524842027440763</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.038262319010419</v>
+        <v>3.066980120981504</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.858388819456045</v>
+        <v>-3.732799572473015</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.128506676084194</v>
+        <v>1.178742374877406</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6046211994589366</v>
+        <v>0.6524842027440763</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.034991347855721</v>
+        <v>3.063709149826805</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.903481064289591</v>
+        <v>-3.777891817306561</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.111153169912689</v>
+        <v>1.161388868705901</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5427251562895468</v>
+        <v>0.5905881595746865</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.998537113716001</v>
+        <v>3.027254915687084</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.724105643050823</v>
+        <v>-3.598516396067793</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.17669031371461</v>
+        <v>1.226926012507822</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6995019144602654</v>
+        <v>0.7473649177454051</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.086390143924846</v>
+        <v>3.11510794589593</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.769119856571429</v>
+        <v>-3.643530609588399</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.139492083637958</v>
+        <v>1.18972778243117</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6691530191456608</v>
+        <v>0.7170160224308005</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.048988262067673</v>
+        <v>3.077706064038757</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.036124366843865</v>
+        <v>-3.910535119860834</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.038381841867929</v>
+        <v>1.088617540661141</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4747899811027123</v>
+        <v>0.522652984387852</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.93806200158085</v>
+        <v>2.966779803551934</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.137322148281037</v>
+        <v>-4.011732901298007</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9971066511895614</v>
+        <v>1.047342349982773</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4063811675573931</v>
+        <v>0.4542441708425328</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.89622063535016</v>
+        <v>2.924938437321244</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.130811181666725</v>
+        <v>-4.005221934683695</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9973109993896032</v>
+        <v>1.047546698182815</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4063811675573931</v>
+        <v>0.4542441708425328</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.893820596904476</v>
+        <v>2.92253839887556</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.111773053959427</v>
+        <v>-3.986183806976397</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.001450969680767</v>
+        <v>1.051686668473979</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3481975562261985</v>
+        <v>0.3960605595113383</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.855435149314005</v>
+        <v>2.884152951285089</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.164288856234248</v>
+        <v>-4.038699609251218</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.099739050405029</v>
+        <v>1.149974749198241</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3481975562261985</v>
+        <v>0.3960605595113383</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.974729550948195</v>
+        <v>3.003447352919279</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.178155617568166</v>
+        <v>-4.052566370585136</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.095025674857596</v>
+        <v>1.145261373650808</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3103396394923756</v>
+        <v>0.3582026427775153</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.952848129894035</v>
+        <v>2.981565931865119</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.137672625645821</v>
+        <v>-4.012083378662791</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.11722740202346</v>
+        <v>1.167463100816672</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3103396394923756</v>
+        <v>0.3582026427775153</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.958856660290961</v>
+        <v>2.987574462262045</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.989929655410819</v>
+        <v>-3.864340408427788</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.07427481139466</v>
+        <v>1.124510510187872</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4781469967272587</v>
+        <v>0.5260100000123985</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.95749129590909</v>
+        <v>2.986209097880174</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.073750876685517</v>
+        <v>-3.948161629702486</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.043539944416262</v>
+        <v>1.093775643209474</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4781469967272587</v>
+        <v>0.5260100000123985</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.960284917440571</v>
+        <v>2.989002719411655</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.067598170632732</v>
+        <v>-3.942008923649702</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.046663375229034</v>
+        <v>1.096899074022246</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.484299702780043</v>
+        <v>0.5321627060651828</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.9646388894639</v>
+        <v>2.993356691434984</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.084407468783234</v>
+        <v>-3.958818221800203</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.039020132708943</v>
+        <v>1.089255831502156</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4674904046295414</v>
+        <v>0.5153534079146811</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.953633787313709</v>
+        <v>2.982351589284793</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.022109470007112</v>
+        <v>-3.896520223024082</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.130274886016213</v>
+        <v>1.180510584809425</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5127846689039834</v>
+        <v>0.5606476721891231</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.047145899675195</v>
+        <v>3.075863701646279</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.820319272341954</v>
+        <v>-3.694730025358924</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.013282966796403</v>
+        <v>1.063518665589615</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7108028610731378</v>
+        <v>0.7586658643582775</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.968248816690815</v>
+        <v>2.996966618661899</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.871205985028149</v>
+        <v>-3.745616738045118</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.063218514044101</v>
+        <v>1.113454212837313</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6599161483869433</v>
+        <v>0.7077791516720831</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.008007021401274</v>
+        <v>3.036724823372357</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.784595242378341</v>
+        <v>-3.659005995395311</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.112490547220067</v>
+        <v>1.162726246013279</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7385418795921016</v>
+        <v>0.7864048828772413</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.069810196240412</v>
+        <v>3.098527998211496</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.844804540383626</v>
+        <v>-3.719215293400596</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.086942808842625</v>
+        <v>1.137178507635837</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6783325815868171</v>
+        <v>0.7261955848719568</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.032220598261913</v>
+        <v>3.060938400232997</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.795617891699274</v>
+        <v>-3.670028644716244</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.105109086356294</v>
+        <v>1.155344785149506</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6783325815868171</v>
+        <v>0.7261955848719568</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.030712216301842</v>
+        <v>3.059430018272926</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.751244760060706</v>
+        <v>-3.625655513077676</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.122721206447158</v>
+        <v>1.17295690524037</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7227057132253857</v>
+        <v>0.7705687165105254</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.057198962720419</v>
+        <v>3.085916764691503</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.773725110919591</v>
+        <v>-3.64813586393656</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.108122860242194</v>
+        <v>1.158358559035407</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7227057132253857</v>
+        <v>0.7705687165105254</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.05159275685901</v>
+        <v>3.080310558830094</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.726069380358535</v>
+        <v>-3.600480133375505</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.133566909494421</v>
+        <v>1.183802608287634</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7703614437864413</v>
+        <v>0.818224447071581</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.086567952223448</v>
+        <v>3.115285754194531</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.62555122185978</v>
+        <v>-3.49996197487675</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.178666546268648</v>
+        <v>1.22890224506186</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8708796022851959</v>
+        <v>0.9187426055703356</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.151771220697425</v>
+        <v>3.180489022668509</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.609645892427428</v>
+        <v>-3.484056645444397</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.171783350517461</v>
+        <v>1.222019049310674</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.791766941575957</v>
+        <v>0.8396299448610967</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.091058296747754</v>
+        <v>3.119776098718838</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.557674094709774</v>
+        <v>-3.439218243835999</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.196669772215151</v>
+        <v>1.244052112564661</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8655544368627434</v>
+        <v>0.8441733778059661</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.139428496530455</v>
+        <v>3.126599861096388</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.577172550951782</v>
+        <v>-3.458716700078007</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.193031329349426</v>
+        <v>1.240413669698936</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8174697955828391</v>
+        <v>0.7960887365260618</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.11473865139359</v>
+        <v>3.101910015959524</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.532969713865882</v>
+        <v>-3.414513862992107</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.216592066711623</v>
+        <v>1.263974407061133</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8616726326687395</v>
+        <v>0.8402915736119623</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.147139956172968</v>
+        <v>3.134311320738901</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.540529379702928</v>
+        <v>-3.422073528829154</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.211978200846052</v>
+        <v>1.259360541195562</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9164760366785588</v>
+        <v>0.8950949776217816</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.178431999048106</v>
+        <v>3.16560336361404</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.382237962163656</v>
+        <v>-3.263782111289882</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.326542533044801</v>
+        <v>1.373924873394311</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9164760366785588</v>
+        <v>0.8950949776217816</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.229679764231146</v>
+        <v>3.21685112879708</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.17459595852918</v>
+        <v>-3.056140107655406</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.408040039092844</v>
+        <v>1.455422379442354</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.124118040313035</v>
+        <v>1.102736981256258</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.352705671006085</v>
+        <v>3.339877035572019</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.123563865806652</v>
+        <v>-3.005108014932877</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.423401104420126</v>
+        <v>1.470783444769636</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.175150133035563</v>
+        <v>1.153769073978786</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.378273154877871</v>
+        <v>3.365444519443805</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.058339684679447</v>
+        <v>-2.939883833805672</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.466678180963713</v>
+        <v>1.514060521313223</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.240374314162769</v>
+        <v>1.218993255105991</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.4345950676469</v>
+        <v>3.421766432212834</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.020912664608313</v>
+        <v>-2.902456813734538</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.477609961291447</v>
+        <v>1.524992301640957</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.24562585219195</v>
+        <v>1.224244793135173</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.43370696276369</v>
+        <v>3.420878327329623</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.041024320643021</v>
+        <v>-2.922568469769246</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.470822091208804</v>
+        <v>1.518204431558314</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.25665319718937</v>
+        <v>1.235272138132592</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.441580162093381</v>
+        <v>3.428751526659315</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.012611057543138</v>
+        <v>-2.894155206669363</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.642745167469968</v>
+        <v>1.690127507819478</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.197677634442941</v>
+        <v>1.176296575386164</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.566752595466735</v>
+        <v>3.553923960032669</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.937828796518125</v>
+        <v>-2.81937294564435</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.79277098109779</v>
+        <v>1.8401533214473</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.272459895467953</v>
+        <v>1.251078836411176</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.73173486129956</v>
+        <v>3.718906225865493</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.911744712254317</v>
+        <v>-2.793288861380542</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.794912590817172</v>
+        <v>1.842294931166682</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.272459895467953</v>
+        <v>1.251078836411176</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.723442837313419</v>
+        <v>3.710614201879352</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.823866799145196</v>
+        <v>-2.705410948271421</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.8282569516446</v>
+        <v>1.87563929199411</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.388385537891304</v>
+        <v>1.367004478834527</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.791191418351209</v>
+        <v>3.778362782917142</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.831817185530809</v>
+        <v>-2.696518486878138</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.842631202817147</v>
+        <v>1.896750682278215</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.388385537891304</v>
+        <v>1.367004478834527</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.808745824078</v>
+        <v>3.795917188643934</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.000293302500686</v>
+        <v>-2.864994603848016</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.767095803433779</v>
+        <v>1.821215282894848</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.360437702174724</v>
+        <v>1.339056643117946</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.783832170052635</v>
+        <v>3.771003534618569</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.554037109871246</v>
+        <v>-2.418738411218576</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.926867977673417</v>
+        <v>1.980987457134485</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.265719032505091</v>
+        <v>1.244337973448314</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.708270665438718</v>
+        <v>3.695442030004652</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.531316006188094</v>
+        <v>-2.396017307535423</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.926620441643583</v>
+        <v>1.980739921104651</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.265719032505091</v>
+        <v>1.244337973448314</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.698934687935622</v>
+        <v>3.686106052501556</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.660517819482136</v>
+        <v>-2.525219120829466</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.033845842177135</v>
+        <v>2.087965321638203</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.136517219211049</v>
+        <v>1.115136160154272</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.780319725810366</v>
+        <v>3.7674910903763</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.686392217956162</v>
+        <v>-2.551093519303492</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.060573905281171</v>
+        <v>2.114693384742239</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.18142882792279</v>
+        <v>1.160047768866013</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.844344513531057</v>
+        <v>3.831515878096991</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.679337527740989</v>
+        <v>-2.544038829088318</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.060071137356785</v>
+        <v>2.114190616817853</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.188483518137964</v>
+        <v>1.167102459081186</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.845252683649707</v>
+        <v>3.83242404821564</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.652386303414501</v>
+        <v>-2.51708760476183</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.080857780732122</v>
+        <v>2.134977260193191</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.203363864165683</v>
+        <v>1.181982805108906</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.86418704491108</v>
+        <v>3.851358409477013</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.673930531245288</v>
+        <v>-2.538631832592617</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.256343221744767</v>
+        <v>2.310462701205835</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.203363864165683</v>
+        <v>1.181982805108906</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.04829017705604</v>
+        <v>4.035461541621973</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.69633864905016</v>
+        <v>-2.561039950397489</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.239496669525812</v>
+        <v>2.29361614898688</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.203363864165683</v>
+        <v>1.181982805108906</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.040406871959033</v>
+        <v>4.027578236524966</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.72456288462776</v>
+        <v>-2.58926418597509</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.230260974844409</v>
+        <v>2.284380454305477</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.221340616616991</v>
+        <v>1.199959557560214</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.053246922979455</v>
+        <v>4.040418287545389</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.73400381051629</v>
+        <v>-2.59870511186362</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.282738322210844</v>
+        <v>2.336857801671912</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.343767734160383</v>
+        <v>1.322386675103606</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.182956911227337</v>
+        <v>4.170128275793271</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.822880441684764</v>
+        <v>-2.687581743032093</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.250078764288755</v>
+        <v>2.304198243749823</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.254891102991909</v>
+        <v>1.233510043935132</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.132522027071554</v>
+        <v>4.119693391637488</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.89921041928567</v>
+        <v>-2.763911720632999</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.217658586142168</v>
+        <v>2.271778065603236</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.254891102991909</v>
+        <v>1.233510043935132</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.130633839965329</v>
+        <v>4.117805204531263</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.992874363963211</v>
+        <v>-2.857575665310541</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.175013237874014</v>
+        <v>2.229132717335082</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.161227158314368</v>
+        <v>1.139846099257591</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.069255702761667</v>
+        <v>4.056427067327601</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.154442789490466</v>
+        <v>-3.019144090837796</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.108819877873264</v>
+        <v>2.162939357334333</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.034444234516488</v>
+        <v>1.013063175459711</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.991619958693091</v>
+        <v>3.978791323259025</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.262743451360586</v>
+        <v>-3.127444752707915</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.078573019991135</v>
+        <v>2.132692499452203</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.034444234516488</v>
+        <v>1.013063175459711</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.004693365559009</v>
+        <v>3.991864730124943</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.28054742308133</v>
+        <v>-3.145248724428659</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.063456628085778</v>
+        <v>2.117576107546846</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9639096116112871</v>
+        <v>0.94252855255451</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.954377788598829</v>
+        <v>3.941549153164763</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.308448210190803</v>
+        <v>-3.173149511538132</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.05082035436899</v>
+        <v>2.104939833830058</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9293126874683523</v>
+        <v>0.9079316284115752</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.93214367524007</v>
+        <v>3.919315039806004</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.430974312893697</v>
+        <v>-3.295675614241026</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.998574357265031</v>
+        <v>2.0526938367261</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8067865847654584</v>
+        <v>0.7854055257086813</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.855392457595533</v>
+        <v>3.842563822161466</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.661488809079286</v>
+        <v>-3.383840636789672</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.973074518381299</v>
+        <v>2.084133787297145</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5762720885798697</v>
+        <v>0.6972405031600357</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.783789719474683</v>
+        <v>3.856370768222783</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.010233894303729</v>
+        <v>-3.732585722014115</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.973888203293369</v>
+        <v>2.084947472209215</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4675241346609719</v>
+        <v>0.5884925492411379</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.858852666125191</v>
+        <v>3.931433714873291</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.16422031207987</v>
+        <v>-3.886572139790256</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.981273905328552</v>
+        <v>2.092333174244398</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4675241346609719</v>
+        <v>0.5884925492411379</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.927832935270831</v>
+        <v>4.000413984018931</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.113698408252204</v>
+        <v>-3.83605023596259</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.98753386897974</v>
+        <v>2.098593137895585</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4675241346609719</v>
+        <v>0.5884925492411379</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.913884137390952</v>
+        <v>3.986465186139052</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.366173562259928</v>
+        <v>-4.088525389970314</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.898414296432064</v>
+        <v>2.00947356534791</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4675241346609719</v>
+        <v>0.5884925492411379</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.925754626446366</v>
+        <v>3.998335675194466</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.65906931873934</v>
+        <v>-4.381421146449727</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.782466528359243</v>
+        <v>1.893525797275089</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4675241346609719</v>
+        <v>0.5884925492411379</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.92696516096531</v>
+        <v>3.99954620971341</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.845733446874148</v>
+        <v>-4.568085274584535</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.711922619332641</v>
+        <v>1.822981888248487</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.440785163836412</v>
+        <v>0.561753578416578</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.915043520697895</v>
+        <v>3.987624569445995</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.991754133788111</v>
+        <v>-4.714105961498497</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.648592197303246</v>
+        <v>1.759651466219091</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.431702072042555</v>
+        <v>0.552670486622721</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.90467151835777</v>
+        <v>3.97725256710587</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.083468142897695</v>
+        <v>-4.805819970608082</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.774110650358456</v>
+        <v>1.885169919274301</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.431702072042555</v>
+        <v>0.552670486622721</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.066875575056815</v>
+        <v>4.139456623804914</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.115119801957665</v>
+        <v>-4.837471629668052</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.756296624698282</v>
+        <v>1.867355893614127</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4265336147981148</v>
+        <v>0.5475020293782809</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.058621138673964</v>
+        <v>4.131202187422065</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.197054620226548</v>
+        <v>-4.919406447936935</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.73375211495922</v>
+        <v>1.844811383875065</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4165988692110346</v>
+        <v>0.5375672837912007</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.062889708890208</v>
+        <v>4.135470757638307</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.299030742474955</v>
+        <v>-5.021382570185343</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70188730451576</v>
+        <v>1.812946573431605</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.314622746962627</v>
+        <v>0.4355911615427931</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.010629673997066</v>
+        <v>4.083210722745165</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.189024458997734</v>
+        <v>-4.911376286708121</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.738042705150824</v>
+        <v>1.849101974066669</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3378273188799022</v>
+        <v>0.4587957334600683</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.016705304391606</v>
+        <v>4.089286353139705</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.045964883256808</v>
+        <v>-4.768316710967195</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.799516546169168</v>
+        <v>1.910575815085014</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3458407454698815</v>
+        <v>0.4668091600500476</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.025763371067568</v>
+        <v>4.098344419815668</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.74451815778497</v>
+        <v>-4.466869985495357</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.927356119240439</v>
+        <v>2.038415388156285</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6472874709417188</v>
+        <v>0.7682558855218848</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.213892289233207</v>
+        <v>4.286473337981306</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.769108402020154</v>
+        <v>-4.491460229730541</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.918491199299076</v>
+        <v>2.029550468214921</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6472874709417188</v>
+        <v>0.7682558855218848</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.214863466985917</v>
+        <v>4.287444515734016</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.718070026013634</v>
+        <v>-4.440421853724021</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.93974945408144</v>
+        <v>2.050808722997285</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6472874709417188</v>
+        <v>0.7682558855218848</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.215706371365672</v>
+        <v>4.288287420113772</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.676930731147003</v>
+        <v>-4.39928255885739</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.975243270902238</v>
+        <v>2.086302539818083</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6884267658083496</v>
+        <v>0.8093951803885157</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.259428047159797</v>
+        <v>4.332009095907896</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.580295819128363</v>
+        <v>-4.30264764683875</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.830081231833629</v>
+        <v>1.941140500749474</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7850616778269895</v>
+        <v>0.9060300924071556</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.133592990494915</v>
+        <v>4.206174039243015</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.710876553659205</v>
+        <v>-4.433228381369593</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.781350982095256</v>
+        <v>1.892410251011101</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.654480943296147</v>
+        <v>0.7754493578763131</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.058746593850374</v>
+        <v>4.131327642598473</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.546380219468244</v>
+        <v>-4.268732047178631</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.831576334847723</v>
+        <v>1.942635603763568</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8189772774871089</v>
+        <v>0.939945692067275</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.141871213441033</v>
+        <v>4.214452262189133</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.469281617926371</v>
+        <v>-4.191633445636758</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.861603485900902</v>
+        <v>1.972662754816747</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8189772774871089</v>
+        <v>0.939945692067275</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.141058923877463</v>
+        <v>4.213639972625563</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.47966681281626</v>
+        <v>-4.202018640526648</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.867318187070018</v>
+        <v>1.978377455985863</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8085920825972196</v>
+        <v>0.9295604971773856</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.144696586068601</v>
+        <v>4.217277634816702</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.498254971538485</v>
+        <v>-4.220606799248872</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.930719929357553</v>
+        <v>2.041779198273399</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7900039238749943</v>
+        <v>0.9109723384551602</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.204380696611691</v>
+        <v>4.276961745359792</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.498553518234521</v>
+        <v>-4.220905345944908</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.927469521497438</v>
+        <v>2.038528790413283</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7897053771789584</v>
+        <v>0.9106737917591243</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.201070579412368</v>
+        <v>4.273651628160469</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.397730384544094</v>
+        <v>-4.120082212254481</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.972329669913</v>
+        <v>2.083388938828845</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8021695926633122</v>
+        <v>0.9231380072434782</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.213080003642372</v>
+        <v>4.285661052390472</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.206949023791687</v>
+        <v>-3.929300851502073</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.048771467692506</v>
+        <v>2.159830736608352</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9929509534157197</v>
+        <v>1.113919367995885</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.32767807357236</v>
+        <v>4.40025912232046</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.099985665942265</v>
+        <v>-3.822337493652651</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.071393656569871</v>
+        <v>2.182452925485717</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.051415561375521</v>
+        <v>1.172383975955687</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.342593684085838</v>
+        <v>4.415174732833937</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.044655078040503</v>
+        <v>-3.767006905750889</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.128492828342635</v>
+        <v>2.23955209725848</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.106746149277283</v>
+        <v>1.227714563857449</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.410758973438953</v>
+        <v>4.483340022187052</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.03260095112754</v>
+        <v>-3.754952778837926</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.127001047009258</v>
+        <v>2.238060315925103</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.118800276190246</v>
+        <v>1.239768690770412</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.411678017488168</v>
+        <v>4.484259066236268</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.073756070695761</v>
+        <v>-3.796107898406147</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.112419629366105</v>
+        <v>2.22347889828195</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.077645156622025</v>
+        <v>1.198613571202191</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.388865575931372</v>
+        <v>4.461446624679471</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.005707508004231</v>
+        <v>-3.728059335714617</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.152490080320599</v>
+        <v>2.263549349236445</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.145693719313555</v>
+        <v>1.266662133893721</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.442545739424173</v>
+        <v>4.515126788172272</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.237307901173732</v>
+        <v>-3.959659728884119</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.080052593226394</v>
+        <v>2.191111862142239</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.145693719313555</v>
+        <v>1.266662133893721</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.462748409597767</v>
+        <v>4.535329458345866</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.287359446702951</v>
+        <v>-4.009711274413338</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.043638211081588</v>
+        <v>2.154697479997433</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.145693719313555</v>
+        <v>1.266662133893721</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.446354645664648</v>
+        <v>4.518935694412749</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.462466279279395</v>
+        <v>-4.184818106989782</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.933847391644477</v>
+        <v>2.044906660560322</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.145693719313555</v>
+        <v>1.266662133893721</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.406606559258115</v>
+        <v>4.479187608006215</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.266366125848872</v>
+        <v>-3.988717953559259</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.019310072013626</v>
+        <v>2.130369340929471</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.341793872744078</v>
+        <v>1.462762287324244</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.531289270313369</v>
+        <v>4.603870319061468</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.113340733735588</v>
+        <v>-3.835692561445975</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.179691228431844</v>
+        <v>2.290750497347689</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.494819264857362</v>
+        <v>1.615787679437528</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.722275505154244</v>
+        <v>4.794856553902344</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.141648047608858</v>
+        <v>-3.863999875319245</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.355834527790829</v>
+        <v>2.466893796706674</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.494819264857362</v>
+        <v>1.615787679437528</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.909741730062536</v>
+        <v>4.982322778810635</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.30824127272238</v>
+        <v>-4.030593100432768</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.258600189099502</v>
+        <v>2.369659458015347</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.328226039743839</v>
+        <v>1.449194454324005</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.779188746348505</v>
+        <v>4.851769795096605</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.285205479360815</v>
+        <v>-4.007557307071203</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.271490909105846</v>
+        <v>2.382550178021691</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.328226039743839</v>
+        <v>1.449194454324005</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.782865149010223</v>
+        <v>4.855446197758322</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.255959498905118</v>
+        <v>-3.978311326615506</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.28080735641162</v>
+        <v>2.391866625327465</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.328226039743839</v>
+        <v>1.449194454324005</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.780483204133718</v>
+        <v>4.853064252881818</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.362885046782969</v>
+        <v>-4.085236874493358</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.235330376418115</v>
+        <v>2.346389645333959</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.221300491865988</v>
+        <v>1.342268906446154</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.713621114564642</v>
+        <v>4.786202163312742</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.507903605290218</v>
+        <v>-4.230255433000607</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.178751755158449</v>
+        <v>2.289811024074294</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.07628193335874</v>
+        <v>1.197250347938905</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.628038781603528</v>
+        <v>4.700619830351627</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.626245371074935</v>
+        <v>-4.348597198785324</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.231346288102315</v>
+        <v>2.34240555701816</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.08696797192163</v>
+        <v>1.207936386501796</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.734381643999015</v>
+        <v>4.806962692747114</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.677655793395643</v>
+        <v>-4.400007621106032</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.208567816299971</v>
+        <v>2.319627085215815</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.08696797192163</v>
+        <v>1.207936386501796</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.732167341124954</v>
+        <v>4.804748389873053</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.757075244603395</v>
+        <v>-4.479427072313784</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.17670316389116</v>
+        <v>2.287762432807004</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.08696797192163</v>
+        <v>1.207936386501796</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.732070469199243</v>
+        <v>4.804651517947343</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.852538242520612</v>
+        <v>-4.574890070231001</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.138511858282316</v>
+        <v>2.249571127198161</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.08696797192163</v>
+        <v>1.207936386501796</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.732064362757287</v>
+        <v>4.804645411505386</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.788162331669898</v>
+        <v>-4.510514159380286</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.162358619185213</v>
+        <v>2.273417888101057</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.151343882772345</v>
+        <v>1.272312297352511</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.768786305830326</v>
+        <v>4.841367354578425</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.843531493802091</v>
+        <v>-4.56588332151248</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.145944772080062</v>
+        <v>2.257004040995906</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.151343882772345</v>
+        <v>1.272312297352511</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.774520123578053</v>
+        <v>4.847101172326152</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.888969273632918</v>
+        <v>-4.611321101343307</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.127308023490663</v>
+        <v>2.238367292406508</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.108498892094185</v>
+        <v>1.229467306674351</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.748351492514089</v>
+        <v>4.820932541262188</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.80076243948534</v>
+        <v>-4.523114267195729</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.182465150000013</v>
+        <v>2.293524418915858</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.108498892094185</v>
+        <v>1.229467306674351</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.768225885364408</v>
+        <v>4.840806934112507</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.694727444280031</v>
+        <v>-4.41707927199042</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.208579848606865</v>
+        <v>2.319639117522709</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.108498892094185</v>
+        <v>1.229467306674351</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.751926585889136</v>
+        <v>4.824507634637236</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.511515781146936</v>
+        <v>-4.233867608857325</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.284295463324148</v>
+        <v>2.395354732239993</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.108498892094185</v>
+        <v>1.229467306674351</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.754357535353181</v>
+        <v>4.826938584101281</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.439794334133085</v>
+        <v>-4.162146161843474</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.278775227977578</v>
+        <v>2.389834496893423</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.180220339108036</v>
+        <v>1.301188753688202</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.763181589409381</v>
+        <v>4.835762638157481</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.417421308525379</v>
+        <v>-4.139773136235767</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.234640184141832</v>
+        <v>2.345699453057677</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.191476090220938</v>
+        <v>1.312444504801103</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.716850785998294</v>
+        <v>4.789431834746393</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.450437604436123</v>
+        <v>-4.172789432146512</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.40663187066289</v>
+        <v>2.517691139578734</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.122038713554186</v>
+        <v>1.243007128134352</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.860386564883599</v>
+        <v>4.932967613631698</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.438909968786515</v>
+        <v>-4.161261796496904</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.403164150750983</v>
+        <v>2.514223419666827</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.181039371755549</v>
+        <v>1.302007786335714</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.887708185632665</v>
+        <v>4.960289234380764</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.536251470128883</v>
+        <v>-4.258603297839272</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.367895662735823</v>
+        <v>2.478954931651669</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.13661918959006</v>
+        <v>1.257587604170226</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.864724188855161</v>
+        <v>4.93730523760326</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.62210749946885</v>
+        <v>-4.344459327179239</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.334804333192675</v>
+        <v>2.44586360210852</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.094243120363925</v>
+        <v>1.215211534944091</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.840549629512318</v>
+        <v>4.913130678260417</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.630944296884969</v>
+        <v>-4.353296124595358</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.313688816046729</v>
+        <v>2.424748084962574</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.086800947722574</v>
+        <v>1.20776936230274</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.818503527748009</v>
+        <v>4.891084576496109</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.722326859450428</v>
+        <v>-4.444678687160817</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.287300302065595</v>
+        <v>2.39835957098144</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9954183851571161</v>
+        <v>1.116386799737282</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.773838501253784</v>
+        <v>4.846419550001883</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.710620141463422</v>
+        <v>-4.432971969173811</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.394111247084666</v>
+        <v>2.50517051600051</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.007125103144122</v>
+        <v>1.128093517724288</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.882990789870256</v>
+        <v>4.955571838618355</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.610956637379759</v>
+        <v>-4.333308465090148</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.437008987449536</v>
+        <v>2.54806825636538</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.070312186347809</v>
+        <v>1.191280600927975</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.923935378523872</v>
+        <v>4.996516427271971</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.621272735546111</v>
+        <v>-4.3436245632565</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.645787381461053</v>
+        <v>2.756846650376898</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.070312186347809</v>
+        <v>1.191280600927975</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.13684021180193</v>
+        <v>5.209421260550029</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.621178767528739</v>
+        <v>-4.343530595239128</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.645003635580092</v>
+        <v>2.756062904495936</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.136240795522411</v>
+        <v>5.20882184427051</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.628397591728583</v>
+        <v>-4.350749419438972</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.636348091844508</v>
+        <v>2.747407360760352</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.130472781466764</v>
+        <v>5.203053830214864</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.627449168610545</v>
+        <v>-4.349800996320933</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.636727461091723</v>
+        <v>2.747786730007568</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.130472781466764</v>
+        <v>5.203053830214864</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.784517626866169</v>
+        <v>-4.506869454576557</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.586627685770566</v>
+        <v>2.697686954686411</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.143200389447856</v>
+        <v>5.215781438195956</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.71707115842477</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.785915302588463</v>
+        <v>-4.500877207787745</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.588014613906036</v>
+        <v>2.702029851826323</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.145146387872244</v>
+        <v>5.217727436620343</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.842115421351128</v>
+        <v>3.802718424964672</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.59414880563738</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.785915302588463</v>
+        <v>-4.614769956276993</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.588014613906036</v>
+        <v>2.650126888448392</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.070682047695127</v>
+        <v>1.191650462275293</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.587212602623747</v>
+        <v>5.211381572638112</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240911.xlsx
+++ b/tame_output/ON/bt/strategyON_20240911.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.4%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.0%</t>
+          <t>-637.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-111.2%</t>
+          <t>-116.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-332.0%</t>
+          <t>-318.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-104.8%</t>
+          <t>-116.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.7%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.050337425679063</v>
+        <v>-9.175926672662092</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4585373914417672</v>
+        <v>-0.5087730902349792</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.583096209218886</v>
+        <v>-1.630959212504025</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.212096277612274</v>
+        <v>2.18337847564119</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.176374219047352</v>
+        <v>-9.301963466030381</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5062583801599683</v>
+        <v>-0.5564940789531803</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.557844586409143</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.229940979927234</v>
+        <v>2.20122317795615</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.119302447151421</v>
+        <v>-9.24489169413445</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4794393357151954</v>
+        <v>-0.5296750345084069</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.557844586409143</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.233931315613635</v>
+        <v>2.205213513642551</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.260974288875541</v>
+        <v>-9.386563535858571</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5375832993035852</v>
+        <v>-0.5878189980967967</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.557844586409143</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.232456088714893</v>
+        <v>2.20373828674381</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.211383444450707</v>
+        <v>-9.336972691433736</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5026935513687789</v>
+        <v>-0.5529292501619909</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.508253741984309</v>
+        <v>-1.556116745269449</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.277264005534666</v>
+        <v>2.248546203563582</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.06246510997885</v>
+        <v>-9.18805435696188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4561773512267195</v>
+        <v>-0.5064130500199311</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.477004151249136</v>
+        <v>-1.524867154534276</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.282962626329087</v>
+        <v>2.254244824358003</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.83661995725944</v>
+        <v>-8.96220920424247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3562602171027467</v>
+        <v>-0.4064959158959582</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.435077475661973</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.317697704717594</v>
+        <v>2.28897990274651</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.712041300921848</v>
+        <v>-8.837630547904878</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3052896100116511</v>
+        <v>-0.3555253088048627</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.435077475661973</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.318836849273652</v>
+        <v>2.290119047302569</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.687004619353338</v>
+        <v>-8.812593866336368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2926411632221395</v>
+        <v>-0.3428768620153511</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.409748388111237</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.336668075966202</v>
+        <v>2.307950273995118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.614871444065457</v>
+        <v>-8.740460691048487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2580541888683503</v>
+        <v>-0.3082898876615623</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.409748388111237</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.342401780204838</v>
+        <v>2.313683978233754</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.54350505145581</v>
+        <v>-8.669094298438839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2392448942183565</v>
+        <v>-0.2894805930115685</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.338381995501589</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.375484353376762</v>
+        <v>2.346766551405678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.450046017470585</v>
+        <v>-8.575635264453615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2117447619371746</v>
+        <v>-0.2619804607303862</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.338381995501589</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.365600872063854</v>
+        <v>2.33688307009277</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.439392835917154</v>
+        <v>-8.564982082900183</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2093180498151757</v>
+        <v>-0.2595537486083872</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.338381995501589</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.36376631156448</v>
+        <v>2.335048509593396</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.341485797240663</v>
+        <v>-8.467075044223693</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.17045554931804</v>
+        <v>-0.220691248111252</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.270396245641033</v>
+        <v>-1.318259248926172</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.404257446507353</v>
+        <v>2.37553964453627</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.317532256264705</v>
+        <v>-8.443121503247735</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1602056267821634</v>
+        <v>-0.210441325575375</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.246442704665075</v>
+        <v>-1.294305707950215</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.419298077238421</v>
+        <v>2.390580275267338</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.053472317941909</v>
+        <v>-8.179061564924938</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06784196761479677</v>
+        <v>-0.1180776664080083</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9823827663422788</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.564473724070347</v>
+        <v>2.535755922099263</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.34639269443707</v>
+        <v>-7.4719819414201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2122028481268377</v>
+        <v>0.1619671493336261</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9823827663422788</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.561686690410046</v>
+        <v>2.532968888438962</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.30620839607088</v>
+        <v>-7.431797643053909</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2286201913611552</v>
+        <v>0.1783844925679436</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9421984679760881</v>
+        <v>-0.9900614712612278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.586140893317602</v>
+        <v>2.557423091346518</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.142808525131517</v>
+        <v>-7.268397772114547</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2933469609576571</v>
+        <v>0.2431112621644456</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7787985970367256</v>
+        <v>-0.8266616003218653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.683547637101976</v>
+        <v>2.654829835130893</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.909327302901919</v>
+        <v>-7.034916549884948</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3946638786873491</v>
+        <v>0.3444281798941371</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5453173748071271</v>
+        <v>-0.5931803780922668</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.831560799277588</v>
+        <v>2.802842997306504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.759660911894404</v>
+        <v>-6.885250158877433</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4516382247773958</v>
+        <v>0.4014025259841842</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4524138835645911</v>
+        <v>-0.5002768868497308</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.88441068371015</v>
+        <v>2.855692881739067</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.627385438263517</v>
+        <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4058092002369049</v>
+        <v>0.3555735014436934</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3201384099337045</v>
+        <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.865036753895837</v>
+        <v>2.836318951924753</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.455524222698615</v>
+        <v>-6.581113469681644</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4773687471505026</v>
+        <v>0.427133048357291</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1482771943688016</v>
+        <v>-0.1961401976539413</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.970968543922415</v>
+        <v>2.942250741951332</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.370559555969296</v>
+        <v>-6.496148802952325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.524260955065889</v>
+        <v>0.4740252562726774</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06331252763948203</v>
+        <v>-0.1111755309246217</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.034853685183666</v>
+        <v>3.006135883212582</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.4761495457424</v>
+        <v>-6.601738792725429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3540490295574288</v>
+        <v>0.3038133307642168</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1689025174125864</v>
+        <v>-0.2167655206977261</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.843523761720585</v>
+        <v>2.814805959749501</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.407914961116973</v>
+        <v>-6.533504208100002</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.429887205284686</v>
+        <v>0.3796515064914745</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1504871945400504</v>
+        <v>-0.1983501978251901</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.903117297321193</v>
+        <v>2.874399495350109</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.259974919709373</v>
+        <v>-6.385564166692403</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3724424132093187</v>
+        <v>0.3222067144161072</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1301662786314928</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.79868903822792</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.207005397455385</v>
+        <v>-6.332594644438414</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3849162358574358</v>
+        <v>0.3346805370642243</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07719675637750395</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.821756765326835</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.041217201495094</v>
+        <v>-6.166806448478123</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4442709021464593</v>
+        <v>0.3940352033532473</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07719675637750395</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.814796153231742</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.007853995016325</v>
+        <v>-6.133443241999355</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4720785391191096</v>
+        <v>0.421842840325898</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07719675637750395</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.829258507612885</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.899594857893804</v>
+        <v>-6.025184104876833</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5099143144273133</v>
+        <v>0.4596786156341017</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07719675637750395</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.82379062807208</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.776303723076673</v>
+        <v>-5.901892970059702</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5567288623647428</v>
+        <v>0.5064931635715308</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04609437843962655</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.895263402972935</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.723606855945381</v>
+        <v>-5.849196102928411</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5855085874545845</v>
+        <v>0.5352728886613725</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09879124557091773</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.934582501489035</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.479841413961937</v>
+        <v>-5.605430660944966</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6787954725950129</v>
+        <v>0.6285597738018009</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09879124557091773</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.930363209836086</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.390065741585465</v>
+        <v>-5.515654988568494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7168300554656177</v>
+        <v>0.6665943566724057</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1603906904852277</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.969447190704688</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.14021534763639</v>
+        <v>-5.26580459461942</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8095122880289498</v>
+        <v>0.7592765892357378</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1603906904852277</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.96218926568839</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.964323255168958</v>
+        <v>-5.089912502151988</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8834682485365712</v>
+        <v>0.8332325497433595</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1603906904852277</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.965788389209039</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.792876792146495</v>
+        <v>-4.918466039129524</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9653743398001102</v>
+        <v>0.9151386410068985</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3318371535076909</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.08198377307707</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.712854505037374</v>
+        <v>-4.838443752020403</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9964037322600556</v>
+        <v>0.9461680334668439</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4118594406168118</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.12901762295884</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.649218762803439</v>
+        <v>-4.774808009786469</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.026552830207947</v>
+        <v>0.976317131414735</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4754951828507464</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.171893869353518</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.555521444587044</v>
+        <v>-4.681110691570074</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.0452260162783</v>
+        <v>0.9949903174850887</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4754951828507464</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.153088128137314</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.566024067652333</v>
+        <v>-4.691613314635362</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.042768043677062</v>
+        <v>0.9925323448838506</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4649925597854575</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.148529630923017</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.453537806983459</v>
+        <v>-4.579127053966488</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.091691861779432</v>
+        <v>1.04145616298622</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4649925597854575</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.152458944757838</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.435824120105593</v>
+        <v>-4.561413367088623</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.099455920447918</v>
+        <v>1.049220221654707</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4681738886823743</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.155046326013328</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.312349848792575</v>
+        <v>-4.437939095775604</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.145843700193119</v>
+        <v>1.095608001399907</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4681738886823743</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.152044397233321</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.092329050755565</v>
+        <v>-4.217918297738594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.235431056418538</v>
+        <v>1.185195357625326</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6093937337503545</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.238355341284723</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.959461361692286</v>
+        <v>-4.085050608675316</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.304472314845672</v>
+        <v>1.25423661605246</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6093937337503545</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.254249524086547</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.839288278327787</v>
+        <v>-3.964877525310817</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.353687392631774</v>
+        <v>1.303451693838561</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7295668171148535</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.327499218545548</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.70403491699781</v>
+        <v>-3.82962416398084</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.417876839725204</v>
+        <v>1.367641140931992</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8648201784448306</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.418739337904974</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.763909744355503</v>
+        <v>-3.889498991338533</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.379964400183553</v>
+        <v>1.329728701390341</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8049453510871385</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.368851932891785</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.644089513444665</v>
+        <v>-3.769678760427695</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443181661782097</v>
+        <v>1.392945962988885</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8049453510871385</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.384141102125994</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.646559219906471</v>
+        <v>-3.772148466889501</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.349837978519816</v>
+        <v>1.299602279726604</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8024756446253323</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.290303477571351</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.714929406230481</v>
+        <v>-3.840518653213511</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.241751765475513</v>
+        <v>1.191516066682301</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8117513436615472</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.215130758478382</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.826801685856632</v>
+        <v>-3.952390932839662</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.187439562256944</v>
+        <v>1.137203863463732</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8117513436615472</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.205567467110273</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.882321761749221</v>
+        <v>-4.007911008732251</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.302262368592111</v>
+        <v>1.252026669798899</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8117513436615472</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.342598303802475</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.706847501956752</v>
+        <v>-3.832436748939782</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.377019304500886</v>
+        <v>1.326783605707674</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8117513436615472</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.347165535794263</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.698923127371838</v>
+        <v>-3.824512374354868</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.355931083096059</v>
+        <v>1.305695384302847</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8117513436615472</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.32290756455547</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.692644924801989</v>
+        <v>-3.818234171785019</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.286980677525448</v>
+        <v>1.236744978732236</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8180295462313962</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.255212799498829</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.632792305598266</v>
+        <v>-3.758381552581296</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.32109411163907</v>
+        <v>1.270858412845858</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8180295462313962</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.265385185930961</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.546548842571888</v>
+        <v>-3.672138089554918</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.350537767423481</v>
+        <v>1.300302068630269</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8180295462313962</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.260331456504822</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.591855661970868</v>
+        <v>-3.717444908953898</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.324190815108415</v>
+        <v>1.273955116315203</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7772193832221654</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.227621134143809</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.62088876667317</v>
+        <v>-3.7464780136562</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.313129446260596</v>
+        <v>1.262893747467384</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7772193832221654</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.228173007176911</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.52807828522231</v>
+        <v>-3.653667532205341</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.279526330732305</v>
+        <v>1.229290631939093</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8700298646730248</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.213131987938792</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.572467754551738</v>
+        <v>-3.698057001534768</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.263644018925135</v>
+        <v>1.213408320131923</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8256403953435971</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.188371782265736</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.689009359657081</v>
+        <v>-3.814598606640111</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.212103085394721</v>
+        <v>1.161867386601509</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7090987902382544</v>
+        <v>0.6612357869531147</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.113522527714253</v>
+        <v>3.08480472574317</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.728933454239653</v>
+        <v>-3.854522701222683</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.201624743392359</v>
+        <v>1.151389044599147</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7090987902382544</v>
+        <v>0.6612357869531147</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.119013823544921</v>
+        <v>3.090296021573837</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.756713852141006</v>
+        <v>-3.882303099124036</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.202009786000357</v>
+        <v>1.151774087207145</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6813183923369013</v>
+        <v>0.6334553890517616</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.113842786572648</v>
+        <v>3.085124984601564</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.875094524871144</v>
+        <v>-4.000683771854174</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.993013236908955</v>
+        <v>0.9427775381157431</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6141005401859251</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.911867795282715</v>
+        <v>2.883149993311632</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.983708603314475</v>
+        <v>-4.109297850297505</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.069717266250828</v>
+        <v>1.019481567457616</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6141005401859251</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.032017456001921</v>
+        <v>3.003299654030837</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.948299565066332</v>
+        <v>-4.073888812049362</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.098393907652409</v>
+        <v>1.048158208859197</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6141005401859251</v>
+        <v>0.5662375369007854</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.046530482104244</v>
+        <v>3.01781268013316</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.909915902508181</v>
+        <v>-4.035505149491211</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.111166814018038</v>
+        <v>1.060931115224826</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6524842027440763</v>
+        <v>0.6046211994589366</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.066980120981504</v>
+        <v>3.038262319010419</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.732799572473015</v>
+        <v>-3.858388819456045</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.178742374877406</v>
+        <v>1.128506676084194</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6524842027440763</v>
+        <v>0.6046211994589366</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.063709149826805</v>
+        <v>3.034991347855721</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.777891817306561</v>
+        <v>-3.903481064289591</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.161388868705901</v>
+        <v>1.111153169912689</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5905881595746865</v>
+        <v>0.5427251562895468</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.027254915687084</v>
+        <v>2.998537113716001</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.598516396067793</v>
+        <v>-3.724105643050823</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.226926012507822</v>
+        <v>1.17669031371461</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7473649177454051</v>
+        <v>0.6995019144602654</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.11510794589593</v>
+        <v>3.086390143924846</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.643530609588399</v>
+        <v>-3.769119856571429</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.18972778243117</v>
+        <v>1.139492083637958</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7170160224308005</v>
+        <v>0.6691530191456608</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.077706064038757</v>
+        <v>3.048988262067673</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.910535119860834</v>
+        <v>-4.036124366843865</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.088617540661141</v>
+        <v>1.038381841867929</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.522652984387852</v>
+        <v>0.4747899811027123</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.966779803551934</v>
+        <v>2.93806200158085</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.011732901298007</v>
+        <v>-4.137322148281037</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.047342349982773</v>
+        <v>0.9971066511895614</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4542441708425328</v>
+        <v>0.4063811675573931</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.924938437321244</v>
+        <v>2.89622063535016</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.005221934683695</v>
+        <v>-4.130811181666725</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.047546698182815</v>
+        <v>0.9973109993896032</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4542441708425328</v>
+        <v>0.4063811675573931</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.92253839887556</v>
+        <v>2.893820596904476</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.986183806976397</v>
+        <v>-4.111773053959427</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.051686668473979</v>
+        <v>1.001450969680767</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3960605595113383</v>
+        <v>0.3481975562261985</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.884152951285089</v>
+        <v>2.855435149314005</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.038699609251218</v>
+        <v>-4.164288856234248</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.149974749198241</v>
+        <v>1.099739050405029</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3960605595113383</v>
+        <v>0.3481975562261985</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.003447352919279</v>
+        <v>2.974729550948195</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.052566370585136</v>
+        <v>-4.178155617568166</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.145261373650808</v>
+        <v>1.095025674857596</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3582026427775153</v>
+        <v>0.3103396394923756</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.981565931865119</v>
+        <v>2.952848129894035</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.012083378662791</v>
+        <v>-4.137672625645821</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.167463100816672</v>
+        <v>1.11722740202346</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3582026427775153</v>
+        <v>0.3103396394923756</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.987574462262045</v>
+        <v>2.958856660290961</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.864340408427788</v>
+        <v>-3.989929655410819</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.124510510187872</v>
+        <v>1.07427481139466</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5260100000123985</v>
+        <v>0.4781469967272587</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.986209097880174</v>
+        <v>2.95749129590909</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.948161629702486</v>
+        <v>-4.073750876685517</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.093775643209474</v>
+        <v>1.043539944416262</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5260100000123985</v>
+        <v>0.4781469967272587</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.989002719411655</v>
+        <v>2.960284917440571</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.942008923649702</v>
+        <v>-4.067598170632732</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.096899074022246</v>
+        <v>1.046663375229034</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5321627060651828</v>
+        <v>0.484299702780043</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.993356691434984</v>
+        <v>2.9646388894639</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.958818221800203</v>
+        <v>-4.084407468783234</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.089255831502156</v>
+        <v>1.039020132708943</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5153534079146811</v>
+        <v>0.4674904046295414</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.982351589284793</v>
+        <v>2.953633787313709</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.896520223024082</v>
+        <v>-4.022109470007112</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.180510584809425</v>
+        <v>1.130274886016213</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5606476721891231</v>
+        <v>0.5127846689039834</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.075863701646279</v>
+        <v>3.047145899675195</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.694730025358924</v>
+        <v>-3.820319272341954</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.063518665589615</v>
+        <v>1.013282966796403</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7586658643582775</v>
+        <v>0.7108028610731378</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.996966618661899</v>
+        <v>2.968248816690815</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.745616738045118</v>
+        <v>-3.871205985028149</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.113454212837313</v>
+        <v>1.063218514044101</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7077791516720831</v>
+        <v>0.6599161483869433</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.036724823372357</v>
+        <v>3.008007021401274</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.659005995395311</v>
+        <v>-3.784595242378341</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.162726246013279</v>
+        <v>1.112490547220067</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7864048828772413</v>
+        <v>0.7385418795921016</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.098527998211496</v>
+        <v>3.069810196240412</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.719215293400596</v>
+        <v>-3.844804540383626</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.137178507635837</v>
+        <v>1.086942808842625</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7261955848719568</v>
+        <v>0.6783325815868171</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.060938400232997</v>
+        <v>3.032220598261913</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.670028644716244</v>
+        <v>-3.795617891699274</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.155344785149506</v>
+        <v>1.105109086356294</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7261955848719568</v>
+        <v>0.6783325815868171</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.059430018272926</v>
+        <v>3.030712216301842</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.625655513077676</v>
+        <v>-3.751244760060706</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.17295690524037</v>
+        <v>1.122721206447158</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7705687165105254</v>
+        <v>0.7227057132253857</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.085916764691503</v>
+        <v>3.057198962720419</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.64813586393656</v>
+        <v>-3.773725110919591</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.158358559035407</v>
+        <v>1.108122860242194</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7705687165105254</v>
+        <v>0.7227057132253857</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.080310558830094</v>
+        <v>3.05159275685901</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.600480133375505</v>
+        <v>-3.726069380358535</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.183802608287634</v>
+        <v>1.133566909494421</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.818224447071581</v>
+        <v>0.7703614437864413</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.115285754194531</v>
+        <v>3.086567952223448</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.49996197487675</v>
+        <v>-3.62555122185978</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.22890224506186</v>
+        <v>1.178666546268648</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9187426055703356</v>
+        <v>0.8708796022851959</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.180489022668509</v>
+        <v>3.151771220697425</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.484056645444397</v>
+        <v>-3.609645892427428</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.222019049310674</v>
+        <v>1.171783350517461</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8396299448610967</v>
+        <v>0.791766941575957</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.119776098718838</v>
+        <v>3.091058296747754</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.439218243835999</v>
+        <v>-3.564807490819029</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.244052112564661</v>
+        <v>1.193816413771449</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8441733778059661</v>
+        <v>0.7963103745208264</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.126599861096388</v>
+        <v>3.097882059125304</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.458716700078007</v>
+        <v>-3.584305947061038</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.240413669698936</v>
+        <v>1.190177970905724</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7960887365260618</v>
+        <v>0.7482257332409221</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.101910015959524</v>
+        <v>3.07319221398844</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.414513862992107</v>
+        <v>-3.540103109975137</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.263974407061133</v>
+        <v>1.213738708267921</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8402915736119623</v>
+        <v>0.7924285703268226</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.134311320738901</v>
+        <v>3.105593518767817</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.422073528829154</v>
+        <v>-3.547662775812184</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.259360541195562</v>
+        <v>1.20912484240235</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8950949776217816</v>
+        <v>0.8472319743366419</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.16560336361404</v>
+        <v>3.136885561642957</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.263782111289882</v>
+        <v>-3.389371358272912</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.373924873394311</v>
+        <v>1.323689174601099</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8950949776217816</v>
+        <v>0.8472319743366419</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.21685112879708</v>
+        <v>3.188133326825996</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.056140107655406</v>
+        <v>-3.181729354638436</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.455422379442354</v>
+        <v>1.405186680649142</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.102736981256258</v>
+        <v>1.054873977971118</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.339877035572019</v>
+        <v>3.311159233600935</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.005108014932877</v>
+        <v>-3.130697261915908</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.470783444769636</v>
+        <v>1.420547745976423</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.153769073978786</v>
+        <v>1.105906070693646</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.365444519443805</v>
+        <v>3.336726717472722</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.939883833805672</v>
+        <v>-3.065473080788702</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.514060521313223</v>
+        <v>1.463824822520011</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.218993255105991</v>
+        <v>1.171130251820852</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.421766432212834</v>
+        <v>3.39304863024175</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.902456813734538</v>
+        <v>-3.028046060717568</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.524992301640957</v>
+        <v>1.474756602847745</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.224244793135173</v>
+        <v>1.176381789850033</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.420878327329623</v>
+        <v>3.392160525358539</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.922568469769246</v>
+        <v>-3.048157716752276</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.518204431558314</v>
+        <v>1.467968732765101</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.235272138132592</v>
+        <v>1.187409134847453</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.428751526659315</v>
+        <v>3.400033724688231</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.894155206669363</v>
+        <v>-3.019744453652393</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.690127507819478</v>
+        <v>1.639891809026266</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.176296575386164</v>
+        <v>1.128433572101024</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.553923960032669</v>
+        <v>3.525206158061585</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.81937294564435</v>
+        <v>-2.94496219262738</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.8401533214473</v>
+        <v>1.789917622654088</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.251078836411176</v>
+        <v>1.203215833126037</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.718906225865493</v>
+        <v>3.690188423894409</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.793288861380542</v>
+        <v>-2.918878108363572</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.842294931166682</v>
+        <v>1.79205923237347</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.251078836411176</v>
+        <v>1.203215833126037</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.710614201879352</v>
+        <v>3.681896399908268</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.705410948271421</v>
+        <v>-2.831000195254452</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.87563929199411</v>
+        <v>1.825403593200898</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.367004478834527</v>
+        <v>1.319141475549388</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.778362782917142</v>
+        <v>3.749644980946059</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.696518486878138</v>
+        <v>-2.822107733861168</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.896750682278215</v>
+        <v>1.846514983485003</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.367004478834527</v>
+        <v>1.319141475549388</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.795917188643934</v>
+        <v>3.76719938667285</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.864994603848016</v>
+        <v>-2.990583850831046</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.821215282894848</v>
+        <v>1.770979584101635</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.339056643117946</v>
+        <v>1.291193639832807</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.771003534618569</v>
+        <v>3.742285732647486</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.418738411218576</v>
+        <v>-2.544327658201606</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.980987457134485</v>
+        <v>1.930751758341273</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.244337973448314</v>
+        <v>1.196474970163174</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.695442030004652</v>
+        <v>3.666724228033567</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.396017307535423</v>
+        <v>-2.521606554518454</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.980739921104651</v>
+        <v>1.930504222311439</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.244337973448314</v>
+        <v>1.196474970163174</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.686106052501556</v>
+        <v>3.657388250530472</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.525219120829466</v>
+        <v>-2.650808367812496</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.087965321638203</v>
+        <v>2.037729622844991</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.115136160154272</v>
+        <v>1.067273156869132</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.7674910903763</v>
+        <v>3.738773288405216</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.551093519303492</v>
+        <v>-2.676682766286522</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.114693384742239</v>
+        <v>2.064457685949027</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.160047768866013</v>
+        <v>1.112184765580873</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.831515878096991</v>
+        <v>3.802798076125907</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.544038829088318</v>
+        <v>-2.669628076071348</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.114190616817853</v>
+        <v>2.063954918024642</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.167102459081186</v>
+        <v>1.119239455796047</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.83242404821564</v>
+        <v>3.803706246244556</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.51708760476183</v>
+        <v>-2.64267685174486</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.134977260193191</v>
+        <v>2.084741561399978</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181982805108906</v>
+        <v>1.134119801823766</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.851358409477013</v>
+        <v>3.82264060750593</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.538631832592617</v>
+        <v>-2.664221079575647</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.310462701205835</v>
+        <v>2.260227002412623</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181982805108906</v>
+        <v>1.134119801823766</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.035461541621973</v>
+        <v>4.006743739650889</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.561039950397489</v>
+        <v>-2.686629197380519</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.29361614898688</v>
+        <v>2.243380450193667</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181982805108906</v>
+        <v>1.134119801823766</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.027578236524966</v>
+        <v>3.998860434553882</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.58926418597509</v>
+        <v>-2.71485343295812</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.284380454305477</v>
+        <v>2.234144755512265</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.199959557560214</v>
+        <v>1.152096554275075</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.040418287545389</v>
+        <v>4.011700485574305</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.59870511186362</v>
+        <v>-2.72429435884665</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.336857801671912</v>
+        <v>2.2866221028787</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322386675103606</v>
+        <v>1.274523671818466</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.170128275793271</v>
+        <v>4.141410473822187</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.687581743032093</v>
+        <v>-2.813170990015124</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.304198243749823</v>
+        <v>2.253962544956611</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.233510043935132</v>
+        <v>1.185647040649992</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.119693391637488</v>
+        <v>4.090975589666404</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.763911720632999</v>
+        <v>-2.889500967616029</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.271778065603236</v>
+        <v>2.221542366810024</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.233510043935132</v>
+        <v>1.185647040649992</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.117805204531263</v>
+        <v>4.089087402560179</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.857575665310541</v>
+        <v>-2.983164912293571</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.229132717335082</v>
+        <v>2.17889701854187</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.139846099257591</v>
+        <v>1.091983095972451</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.056427067327601</v>
+        <v>4.027709265356516</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.019144090837796</v>
+        <v>-3.144733337820826</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.162939357334333</v>
+        <v>2.11270365854112</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.013063175459711</v>
+        <v>0.9652001721745714</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.978791323259025</v>
+        <v>3.950073521287941</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.127444752707915</v>
+        <v>-3.253033999690945</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.132692499452203</v>
+        <v>2.082456800658991</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.013063175459711</v>
+        <v>0.9652001721745714</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.991864730124943</v>
+        <v>3.96314692815386</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.145248724428659</v>
+        <v>-3.27083797141169</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.117576107546846</v>
+        <v>2.067340408753633</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.94252855255451</v>
+        <v>0.8946655492693703</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.941549153164763</v>
+        <v>3.912831351193679</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.173149511538132</v>
+        <v>-3.298738758521162</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.104939833830058</v>
+        <v>2.054704135036846</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9079316284115752</v>
+        <v>0.8600686251264354</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.919315039806004</v>
+        <v>3.89059723783492</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.295675614241026</v>
+        <v>-3.421264861224056</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.0526938367261</v>
+        <v>2.002458137932887</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7854055257086813</v>
+        <v>0.7375425224235416</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.842563822161466</v>
+        <v>3.813846020190383</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.383840636789672</v>
+        <v>-3.651779357409645</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.084133787297145</v>
+        <v>1.976958299049156</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6972405031600357</v>
+        <v>0.5070280262379528</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.856370768222783</v>
+        <v>3.742243282069533</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.732585722014115</v>
+        <v>-4.000524442634089</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.084947472209215</v>
+        <v>1.977771983961225</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5884925492411379</v>
+        <v>0.398280072319055</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.931433714873291</v>
+        <v>3.817306228720041</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.886572139790256</v>
+        <v>-4.154510860410229</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.092333174244398</v>
+        <v>1.985157685996409</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5884925492411379</v>
+        <v>0.398280072319055</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.000413984018931</v>
+        <v>3.886286497865681</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.83605023596259</v>
+        <v>-4.103988956582564</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.098593137895585</v>
+        <v>1.991417649647596</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5884925492411379</v>
+        <v>0.398280072319055</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.986465186139052</v>
+        <v>3.872337699985802</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.088525389970314</v>
+        <v>-4.356464110590288</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.00947356534791</v>
+        <v>1.90229807709992</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5884925492411379</v>
+        <v>0.398280072319055</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.998335675194466</v>
+        <v>3.884208189041216</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.381421146449727</v>
+        <v>-4.6493598670697</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.893525797275089</v>
+        <v>1.786350309027099</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5884925492411379</v>
+        <v>0.398280072319055</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.99954620971341</v>
+        <v>3.88541872356016</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.568085274584535</v>
+        <v>-4.836023995204508</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.822981888248487</v>
+        <v>1.715806400000497</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.561753578416578</v>
+        <v>0.3715411014944952</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.987624569445995</v>
+        <v>3.873497083292745</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.714105961498497</v>
+        <v>-4.98204468211847</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.759651466219091</v>
+        <v>1.652475977971102</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.552670486622721</v>
+        <v>0.3624580097006382</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.97725256710587</v>
+        <v>3.86312508095262</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.805819970608082</v>
+        <v>-5.073758691228056</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.885169919274301</v>
+        <v>1.777994431026312</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.552670486622721</v>
+        <v>0.3624580097006382</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.139456623804914</v>
+        <v>4.025329137651664</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.837471629668052</v>
+        <v>-5.105410350288025</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.867355893614127</v>
+        <v>1.760180405366138</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5475020293782809</v>
+        <v>0.357289552456198</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.131202187422065</v>
+        <v>4.017074701268815</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.919406447936935</v>
+        <v>-5.187345168556909</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.844811383875065</v>
+        <v>1.737635895627076</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5375672837912007</v>
+        <v>0.3473548068691178</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.135470757638307</v>
+        <v>4.021343271485057</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.021382570185343</v>
+        <v>-5.289321290805316</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.812946573431605</v>
+        <v>1.705771085183616</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4355911615427931</v>
+        <v>0.2453786846207102</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.083210722745165</v>
+        <v>3.969083236591915</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.911376286708121</v>
+        <v>-5.179315007328094</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.849101974066669</v>
+        <v>1.741926485818679</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4587957334600683</v>
+        <v>0.2685832565379854</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.089286353139705</v>
+        <v>3.975158866986456</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.768316710967195</v>
+        <v>-5.036255431587168</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.910575815085014</v>
+        <v>1.803400326837024</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4668091600500476</v>
+        <v>0.2765966831279647</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.098344419815668</v>
+        <v>3.984216933662418</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.466869985495357</v>
+        <v>-4.734808706115331</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.038415388156285</v>
+        <v>1.931239899908295</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7682558855218848</v>
+        <v>0.578043408599802</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.286473337981306</v>
+        <v>4.172345851828056</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.491460229730541</v>
+        <v>-4.759398950350515</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.029550468214921</v>
+        <v>1.922374979966932</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7682558855218848</v>
+        <v>0.578043408599802</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.287444515734016</v>
+        <v>4.173317029580767</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.440421853724021</v>
+        <v>-4.708360574343994</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.050808722997285</v>
+        <v>1.943633234749296</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7682558855218848</v>
+        <v>0.578043408599802</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.288287420113772</v>
+        <v>4.174159933960523</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.39928255885739</v>
+        <v>-4.667221279477364</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.086302539818083</v>
+        <v>1.979127051570094</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8093951803885157</v>
+        <v>0.6191827034664328</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.332009095907896</v>
+        <v>4.217881609754646</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.30264764683875</v>
+        <v>-4.570586367458723</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.941140500749474</v>
+        <v>1.833965012501484</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9060300924071556</v>
+        <v>0.7158176154850727</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.206174039243015</v>
+        <v>4.092046553089765</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.433228381369593</v>
+        <v>-4.701167101989566</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.892410251011101</v>
+        <v>1.785234762763111</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7754493578763131</v>
+        <v>0.5852368809542302</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.131327642598473</v>
+        <v>4.017200156445224</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.268732047178631</v>
+        <v>-4.536670767798604</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.942635603763568</v>
+        <v>1.835460115515579</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.939945692067275</v>
+        <v>0.7497332151451921</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.214452262189133</v>
+        <v>4.100324776035883</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.191633445636758</v>
+        <v>-4.459572166256732</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.972662754816747</v>
+        <v>1.865487266568757</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.939945692067275</v>
+        <v>0.7497332151451921</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.213639972625563</v>
+        <v>4.099512486472313</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.202018640526648</v>
+        <v>-4.469957361146621</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.978377455985863</v>
+        <v>1.871201967737874</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9295604971773856</v>
+        <v>0.7393480202553028</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.217277634816702</v>
+        <v>4.103150148663452</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.220606799248872</v>
+        <v>-4.488545519868846</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.041779198273399</v>
+        <v>1.934603710025409</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9109723384551602</v>
+        <v>0.7207598615330775</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.276961745359792</v>
+        <v>4.162834259206542</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.220905345944908</v>
+        <v>-4.488844066564882</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.038528790413283</v>
+        <v>1.931353302165293</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9106737917591243</v>
+        <v>0.7204613148370416</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.273651628160469</v>
+        <v>4.159524142007219</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.120082212254481</v>
+        <v>-4.388020932874454</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.083388938828845</v>
+        <v>1.976213450580856</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9231380072434782</v>
+        <v>0.7329255303213954</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.285661052390472</v>
+        <v>4.171533566237223</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.929300851502073</v>
+        <v>-4.197239572122047</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.159830736608352</v>
+        <v>2.052655248360362</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.113919367995885</v>
+        <v>0.9237068910738028</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.40025912232046</v>
+        <v>4.28613163616721</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.822337493652651</v>
+        <v>-4.090276214272626</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.182452925485717</v>
+        <v>2.075277437237727</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.172383975955687</v>
+        <v>0.9821714990336042</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.415174732833937</v>
+        <v>4.301047246680687</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.767006905750889</v>
+        <v>-4.034945626370863</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.23955209725848</v>
+        <v>2.132376609010491</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.227714563857449</v>
+        <v>1.037502086935366</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.483340022187052</v>
+        <v>4.369212536033803</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.754952778837926</v>
+        <v>-4.0228914994579</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.238060315925103</v>
+        <v>2.130884827677114</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.239768690770412</v>
+        <v>1.049556213848329</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.484259066236268</v>
+        <v>4.370131580083019</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.796107898406147</v>
+        <v>-4.064046619026121</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.22347889828195</v>
+        <v>2.116303410033961</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.198613571202191</v>
+        <v>1.008401094280108</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.461446624679471</v>
+        <v>4.347319138526222</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.728059335714617</v>
+        <v>-3.995998056334591</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.263549349236445</v>
+        <v>2.156373860988455</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.266662133893721</v>
+        <v>1.076449656971638</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.515126788172272</v>
+        <v>4.400999302019022</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.959659728884119</v>
+        <v>-4.227598449504092</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.191111862142239</v>
+        <v>2.083936373894249</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.266662133893721</v>
+        <v>1.076449656971638</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.535329458345866</v>
+        <v>4.421201972192616</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.009711274413338</v>
+        <v>-4.277649995033311</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.154697479997433</v>
+        <v>2.047521991749444</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.266662133893721</v>
+        <v>1.076449656971638</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.518935694412749</v>
+        <v>4.404808208259499</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.184818106989782</v>
+        <v>-4.452756827609756</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.044906660560322</v>
+        <v>1.937731172312333</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.266662133893721</v>
+        <v>1.076449656971638</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.479187608006215</v>
+        <v>4.365060121852965</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-3.988717953559259</v>
+        <v>-4.256656674179233</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.130369340929471</v>
+        <v>2.023193852681482</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.462762287324244</v>
+        <v>1.272549810402161</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.603870319061468</v>
+        <v>4.489742832908219</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.835692561445975</v>
+        <v>-4.029707765365543</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.290750497347689</v>
+        <v>2.213144415779862</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.615787679437528</v>
+        <v>1.499498719215851</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.794856553902344</v>
+        <v>4.725083177769338</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.863999875319245</v>
+        <v>-4.058015079238813</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.466893796706674</v>
+        <v>2.389287715138846</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.615787679437528</v>
+        <v>1.499498719215851</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.982322778810635</v>
+        <v>4.91254940267763</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.030593100432768</v>
+        <v>-4.224608304352335</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.369659458015347</v>
+        <v>2.29205337644752</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.449194454324005</v>
+        <v>1.332905494102329</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.851769795096605</v>
+        <v>4.781996418963599</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.007557307071203</v>
+        <v>-4.201572510990769</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.382550178021691</v>
+        <v>2.304944096453864</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.449194454324005</v>
+        <v>1.332905494102329</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.855446197758322</v>
+        <v>4.785672821625317</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.978311326615506</v>
+        <v>-4.172326530535073</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.391866625327465</v>
+        <v>2.314260543759638</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.449194454324005</v>
+        <v>1.332905494102329</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.853064252881818</v>
+        <v>4.783290876748811</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.085236874493358</v>
+        <v>-4.279252078412924</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.346389645333959</v>
+        <v>2.268783563766132</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.342268906446154</v>
+        <v>1.225979946224478</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.786202163312742</v>
+        <v>4.716428787179736</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.230255433000607</v>
+        <v>-4.424270636920173</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.289811024074294</v>
+        <v>2.212204942506467</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.197250347938905</v>
+        <v>1.080961387717229</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.700619830351627</v>
+        <v>4.630846454218621</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.348597198785324</v>
+        <v>-4.54261240270489</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.34240555701816</v>
+        <v>2.264799475450333</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.207936386501796</v>
+        <v>1.091647426280119</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.806962692747114</v>
+        <v>4.737189316614108</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.400007621106032</v>
+        <v>-4.594022825025598</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.319627085215815</v>
+        <v>2.242021003647989</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.207936386501796</v>
+        <v>1.091647426280119</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.804748389873053</v>
+        <v>4.734975013740047</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.479427072313784</v>
+        <v>-4.67344227623335</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.287762432807004</v>
+        <v>2.210156351239178</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.207936386501796</v>
+        <v>1.091647426280119</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.804651517947343</v>
+        <v>4.734878141814336</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.574890070231001</v>
+        <v>-4.768905274150567</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.249571127198161</v>
+        <v>2.171965045630334</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.207936386501796</v>
+        <v>1.091647426280119</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.804645411505386</v>
+        <v>4.73487203537238</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.510514159380286</v>
+        <v>-4.704529363299852</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.273417888101057</v>
+        <v>2.19581180653323</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.272312297352511</v>
+        <v>1.156023337130834</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.841367354578425</v>
+        <v>4.77159397844542</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.56588332151248</v>
+        <v>-4.759898525432046</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.257004040995906</v>
+        <v>2.17939795942808</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.272312297352511</v>
+        <v>1.156023337130834</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.847101172326152</v>
+        <v>4.777327796193147</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.611321101343307</v>
+        <v>-4.805336305262873</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.238367292406508</v>
+        <v>2.160761210838681</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.229467306674351</v>
+        <v>1.113178346452675</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.820932541262188</v>
+        <v>4.751159165129183</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.523114267195729</v>
+        <v>-4.717129471115295</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.293524418915858</v>
+        <v>2.215918337348032</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.229467306674351</v>
+        <v>1.113178346452675</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.840806934112507</v>
+        <v>4.771033557979502</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.41707927199042</v>
+        <v>-4.611094475909986</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.319639117522709</v>
+        <v>2.242033035954883</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.229467306674351</v>
+        <v>1.113178346452675</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.824507634637236</v>
+        <v>4.75473425850423</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.233867608857325</v>
+        <v>-4.427882812776891</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.395354732239993</v>
+        <v>2.317748650672167</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.229467306674351</v>
+        <v>1.113178346452675</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.826938584101281</v>
+        <v>4.757165207968275</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.162146161843474</v>
+        <v>-4.35616136576304</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.389834496893423</v>
+        <v>2.312228415325596</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.301188753688202</v>
+        <v>1.184899793466526</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.835762638157481</v>
+        <v>4.765989262024475</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.139773136235767</v>
+        <v>-4.333788340155333</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.345699453057677</v>
+        <v>2.26809337148985</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.312444504801103</v>
+        <v>1.196155544579427</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.789431834746393</v>
+        <v>4.719658458613387</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.172789432146512</v>
+        <v>-4.366804636066078</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.517691139578734</v>
+        <v>2.440085058010908</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.243007128134352</v>
+        <v>1.126718167912675</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.932967613631698</v>
+        <v>4.863194237498692</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.161261796496904</v>
+        <v>-4.35527700041647</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.514223419666827</v>
+        <v>2.436617338099</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.302007786335714</v>
+        <v>1.185718826114038</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.960289234380764</v>
+        <v>4.890515858247759</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.258603297839272</v>
+        <v>-4.452618501758838</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.478954931651669</v>
+        <v>2.401348850083842</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.257587604170226</v>
+        <v>1.14129864394855</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.93730523760326</v>
+        <v>4.867531861470254</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.344459327179239</v>
+        <v>-4.538474531098805</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.44586360210852</v>
+        <v>2.368257520540693</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.215211534944091</v>
+        <v>1.098922574722415</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.913130678260417</v>
+        <v>4.843357302127411</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.353296124595358</v>
+        <v>-4.547311328514924</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.424748084962574</v>
+        <v>2.347142003394747</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.20776936230274</v>
+        <v>1.091480402081064</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.891084576496109</v>
+        <v>4.821311200363103</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.444678687160817</v>
+        <v>-4.638693891080383</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.39835957098144</v>
+        <v>2.320753489413613</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.116386799737282</v>
+        <v>1.000097839515605</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.846419550001883</v>
+        <v>4.776646173868877</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.432971969173811</v>
+        <v>-4.626987173093377</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.50517051600051</v>
+        <v>2.427564434432684</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.128093517724288</v>
+        <v>1.011804557502612</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.955571838618355</v>
+        <v>4.885798462485349</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.333308465090148</v>
+        <v>-4.527323669009714</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.54806825636538</v>
+        <v>2.470462174797554</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.191280600927975</v>
+        <v>1.074991640706298</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.996516427271971</v>
+        <v>4.926743051138966</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.3436245632565</v>
+        <v>-4.537639767176066</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.756846650376898</v>
+        <v>2.679240568809071</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.191280600927975</v>
+        <v>1.074991640706298</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.209421260550029</v>
+        <v>5.139647884417024</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.343530595239128</v>
+        <v>-4.537545799158694</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.756062904495936</v>
+        <v>2.678456822928109</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.20882184427051</v>
+        <v>5.139048468137505</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.350749419438972</v>
+        <v>-4.544764623358538</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.747407360760352</v>
+        <v>2.669801279192526</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.203053830214864</v>
+        <v>5.133280454081858</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.349800996320933</v>
+        <v>-4.543816200240499</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.747786730007568</v>
+        <v>2.670180648439741</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.203053830214864</v>
+        <v>5.133280454081858</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.506869454576557</v>
+        <v>-4.700884658496124</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.697686954686411</v>
+        <v>2.620080873118583</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.215781438195956</v>
+        <v>5.14600806206295</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.500877207787745</v>
+        <v>-4.694892411707312</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.702029851826323</v>
+        <v>2.624423770258496</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.217727436620343</v>
+        <v>5.147954060487338</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.802718424964672</v>
+        <v>3.894698369899126</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.614769956276993</v>
+        <v>-4.756198619705964</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.650126888448392</v>
+        <v>2.593555423076804</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.191650462275293</v>
+        <v>1.075361502053616</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.211381572638112</v>
+        <v>5.141608196505107</v>
       </c>
     </row>
   </sheetData>
